--- a/financials/FRT/FRT_financials.xlsx
+++ b/financials/FRT/FRT_financials.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,27 +431,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -528,16 +540,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5929000000000</v>
+        <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>986000000000</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>1194000000000</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1119000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -775,16 +787,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>332658622131</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>290510499090</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>439160418458</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>440067475846</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1402,16 +1414,16 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>31681844</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>31681844</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>14902586</v>
       </c>
       <c r="E52" t="n">
-        <v>5599868</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -2237,10 +2249,18 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr"/>
-      <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" t="inlineStr"/>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2249,16 +2269,16 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>5929000000000</v>
+        <v>0</v>
       </c>
       <c r="C97" t="n">
-        <v>986000000000</v>
+        <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>1194000000000</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>1119000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -2770,27 +2790,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
@@ -3286,27 +3306,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2022</t>
         </is>

--- a/financials/FRT/FRT_financials.xlsx
+++ b/financials/FRT/FRT_financials.xlsx
@@ -1,120 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="#,##0;\(#,##0\);\-"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="0.00\x"/>
-    <numFmt numFmtId="167" formatCode="#,##0&quot; ngày&quot;"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0 &quot;ngày&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <b val="1"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
+      <name val="Tahoma"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF008000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <i val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
+      <name val="Tahoma"/>
       <sz val="10"/>
     </font>
     <font>
@@ -132,6 +60,13 @@
     <font>
       <name val="Tahoma"/>
       <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -162,37 +97,16 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
       <color rgb="00008000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Tahoma"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -214,19 +128,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -243,222 +148,148 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="18">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="37">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="20" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="170" fontId="22" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="21" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -466,3849 +297,3959 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E123"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="15" customWidth="1" style="15" min="2" max="2"/>
-    <col width="15" customWidth="1" style="15" min="3" max="3"/>
-    <col width="15" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" s="32" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="33" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="33" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="33" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="15">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>TÀI SẢN NGẮN HẠN</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n">
+      <c r="B2" s="4" t="n">
         <v>21787052185671</v>
       </c>
-      <c r="C2" s="35" t="n">
+      <c r="C2" s="4" t="n">
         <v>14026158730456</v>
       </c>
-      <c r="D2" s="35" t="n">
+      <c r="D2" s="4" t="n">
         <v>11415308018413</v>
       </c>
-      <c r="E2" s="35" t="n">
+      <c r="E2" s="4" t="n">
         <v>9326797408285</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="4" t="n">
         <v>2869851759629</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="4" t="n">
         <v>2097787236988</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="4" t="n">
         <v>960822549973</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="4" t="n">
         <v>745556075005</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="15">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Tiền</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="4" t="n">
         <v>385251759629</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="4" t="n">
         <v>475787236988</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="4" t="n">
         <v>514817562060</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="4" t="n">
         <v>450488205110</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="15">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Các khoản tương đương tiền</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="4" t="n">
         <v>2484600000000</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="4" t="n">
         <v>1622000000000</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="4" t="n">
         <v>446004987913</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="4" t="n">
         <v>295067869895</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
-        <v>5929000000000</v>
-      </c>
-      <c r="C6" s="35" t="n">
-        <v>986000000000</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>1194000000000</v>
-      </c>
-      <c r="E6" s="35" t="n">
-        <v>1119000000000</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="15">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="B7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="15">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="B8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Các khoản phải thu</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="4" t="n">
         <v>728878339921</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="4" t="n">
         <v>417127103606</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="4" t="n">
         <v>394464296948</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="4" t="n">
         <v>538346191905</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="15">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="4" t="n">
         <v>233091257926</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="4" t="n">
         <v>176150692098</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="4" t="n">
         <v>126026140388</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="4" t="n">
         <v>89622537320</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Trả trước người bán</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="4" t="n">
         <v>94792455388</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="4" t="n">
         <v>43997579646</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="4" t="n">
         <v>48902780339</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="4" t="n">
         <v>73767134666</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Phải thu nội bộ</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="B12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Phải thu hợp đồng xây dựng đang thực hiện</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="B13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Phải thu khác</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="4" t="n">
         <v>410499058289</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="4" t="n">
         <v>206546170984</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="4" t="n">
         <v>227411821380</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="4" t="n">
         <v>342099580137</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Dự phòng nợ khó đòi</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="4" t="n">
         <v>-9504431682</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="4" t="n">
         <v>-9567339122</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="4" t="n">
         <v>-7876445159</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="4" t="n">
         <v>-7143060218</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="4" t="n">
         <v>11926663463990</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="4" t="n">
         <v>10234733890772</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="4" t="n">
         <v>8426860753034</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="4" t="n">
         <v>6483827665529</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="15">
-      <c r="A17" s="34" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="4" t="n">
         <v>12012604661865</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="4" t="n">
         <v>10291473307238</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="4" t="n">
         <v>8470079480259</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="4" t="n">
         <v>6525562245058</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="15">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá hàng tồn kho</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="4" t="n">
         <v>-85941197875</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="4" t="n">
         <v>-56739416466</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="4" t="n">
         <v>-43218727225</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="4" t="n">
         <v>-41734579529</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>332658622131</v>
-      </c>
-      <c r="C19" s="35" t="n">
-        <v>290510499090</v>
-      </c>
-      <c r="D19" s="35" t="n">
-        <v>439160418458</v>
-      </c>
-      <c r="E19" s="35" t="n">
-        <v>440067475846</v>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="15">
-      <c r="A20" s="34" t="inlineStr">
+      <c r="B19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Chi phí trả trước ngắn hạn</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="4" t="n">
         <v>262782269911</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="4" t="n">
         <v>252093295842</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="4" t="n">
         <v>230547735063</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="4" t="n">
         <v>260931923787</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Thuế GTGT được khấu trừ</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="4" t="n">
         <v>47661947145</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="4" t="n">
         <v>16870747637</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="4" t="n">
         <v>186402495200</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="4" t="n">
         <v>157021246028</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Phải thu thuế khác</t>
         </is>
       </c>
-      <c r="B22" s="35" t="n">
+      <c r="B22" s="4" t="n">
         <v>22214405075</v>
       </c>
-      <c r="C22" s="35" t="n">
+      <c r="C22" s="4" t="n">
         <v>21546455611</v>
       </c>
-      <c r="D22" s="35" t="n">
+      <c r="D22" s="4" t="n">
         <v>22210188195</v>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="4" t="n">
         <v>22114306031</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="15">
-      <c r="A23" s="34" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" s="34" t="inlineStr">
+      <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>TÀI SẢN DÀI HẠN</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="4" t="n">
         <v>1927183984705</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="4" t="n">
         <v>1806391668645</v>
       </c>
-      <c r="D24" s="35" t="n">
+      <c r="D24" s="4" t="n">
         <v>1683141884191</v>
       </c>
-      <c r="E24" s="35" t="n">
+      <c r="E24" s="4" t="n">
         <v>1196999526761</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="15">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Phải thu dài hạn</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="4" t="n">
         <v>194450060810</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="4" t="n">
         <v>182805424079</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="4" t="n">
         <v>179315098485</v>
       </c>
-      <c r="E25" s="35" t="n">
+      <c r="E25" s="4" t="n">
         <v>170162186921</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" s="34" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng dài hạn</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="15">
-      <c r="A27" s="34" t="inlineStr">
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Phải thu nội bộ dài hạn</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E27" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="15">
-      <c r="A28" s="34" t="inlineStr">
+      <c r="B27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Phải thu dài hạn khác</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="4" t="n">
         <v>194450060810</v>
       </c>
-      <c r="C28" s="35" t="n">
+      <c r="C28" s="4" t="n">
         <v>182805424079</v>
       </c>
-      <c r="D28" s="35" t="n">
+      <c r="D28" s="4" t="n">
         <v>179315098485</v>
       </c>
-      <c r="E28" s="35" t="n">
+      <c r="E28" s="4" t="n">
         <v>170162186921</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="15">
-      <c r="A29" s="34" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Dự phòng phải thu dài hạn</t>
         </is>
       </c>
-      <c r="B29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="15">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Tài sản cố định</t>
         </is>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="4" t="n">
         <v>1574317843107</v>
       </c>
-      <c r="C30" s="35" t="n">
+      <c r="C30" s="4" t="n">
         <v>1445982801672</v>
       </c>
-      <c r="D30" s="35" t="n">
+      <c r="D30" s="4" t="n">
         <v>1307637254001</v>
       </c>
-      <c r="E30" s="35" t="n">
+      <c r="E30" s="4" t="n">
         <v>847269560047</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" s="34" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>GTCL TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n">
+      <c r="B31" s="4" t="n">
         <v>1196539820561</v>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="4" t="n">
         <v>1156676461871</v>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="4" t="n">
         <v>1079496087742</v>
       </c>
-      <c r="E31" s="35" t="n">
+      <c r="E31" s="4" t="n">
         <v>675128050014</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="15">
-      <c r="A32" s="34" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B32" s="35" t="n">
+      <c r="B32" s="4" t="n">
         <v>2285328752900</v>
       </c>
-      <c r="C32" s="35" t="n">
+      <c r="C32" s="4" t="n">
         <v>1915183739839</v>
       </c>
-      <c r="D32" s="35" t="n">
+      <c r="D32" s="4" t="n">
         <v>1608729339222</v>
       </c>
-      <c r="E32" s="35" t="n">
+      <c r="E32" s="4" t="n">
         <v>979182072742</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="15">
-      <c r="A33" s="34" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế TSCĐ hữu hình</t>
         </is>
       </c>
-      <c r="B33" s="35" t="n">
+      <c r="B33" s="4" t="n">
         <v>-1088788932339</v>
       </c>
-      <c r="C33" s="35" t="n">
+      <c r="C33" s="4" t="n">
         <v>-758507277968</v>
       </c>
-      <c r="D33" s="35" t="n">
+      <c r="D33" s="4" t="n">
         <v>-529233251480</v>
       </c>
-      <c r="E33" s="35" t="n">
+      <c r="E33" s="4" t="n">
         <v>-304054022728</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="15">
-      <c r="A34" s="34" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>GTCL tài sản thuê tài chính</t>
         </is>
       </c>
-      <c r="B34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="15">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="B34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá tài sản thuê tài chính</t>
         </is>
       </c>
-      <c r="B35" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="15">
-      <c r="A36" s="34" t="inlineStr">
+      <c r="B35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế tài sản thuê tài chính</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="15">
-      <c r="A37" s="34" t="inlineStr">
+      <c r="B36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>GTCL tài sản cố định vô hình</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n">
+      <c r="B37" s="4" t="n">
         <v>377778022546</v>
       </c>
-      <c r="C37" s="35" t="n">
+      <c r="C37" s="4" t="n">
         <v>289306339801</v>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="4" t="n">
         <v>228141166259</v>
       </c>
-      <c r="E37" s="35" t="n">
+      <c r="E37" s="4" t="n">
         <v>172141510033</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="15">
-      <c r="A38" s="34" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B38" s="35" t="n">
+      <c r="B38" s="4" t="n">
         <v>495746297007</v>
       </c>
-      <c r="C38" s="35" t="n">
+      <c r="C38" s="4" t="n">
         <v>348666597970</v>
       </c>
-      <c r="D38" s="35" t="n">
+      <c r="D38" s="4" t="n">
         <v>255220010970</v>
       </c>
-      <c r="E38" s="35" t="n">
+      <c r="E38" s="4" t="n">
         <v>183893578870</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="15">
-      <c r="A39" s="34" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế TSCĐ vô hình</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n">
+      <c r="B39" s="4" t="n">
         <v>-117968274461</v>
       </c>
-      <c r="C39" s="35" t="n">
+      <c r="C39" s="4" t="n">
         <v>-59360258169</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="4" t="n">
         <v>-27078844711</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="4" t="n">
         <v>-11752068837</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="15">
-      <c r="A40" s="34" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Xây dựng cơ bản đang dang dở (trước 2015)</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="15">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Giá trị ròng tài sản đầu tư</t>
         </is>
       </c>
-      <c r="B41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Nguyên giá tài sản đầu tư</t>
         </is>
       </c>
-      <c r="B42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="15">
-      <c r="A43" s="34" t="inlineStr">
+      <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Khấu hao lũy kế tài sản đầu tư</t>
         </is>
       </c>
-      <c r="B43" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="15">
-      <c r="A44" s="34" t="inlineStr">
+      <c r="B43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Đầu tư dài hạn</t>
         </is>
       </c>
-      <c r="B44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="15">
-      <c r="A45" s="34" t="inlineStr">
+      <c r="B44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Đầu tư vào các công ty con</t>
         </is>
       </c>
-      <c r="B45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="15">
-      <c r="A46" s="34" t="inlineStr">
+      <c r="B45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Đầu tư vào các công ty liên kết</t>
         </is>
       </c>
-      <c r="B46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="15">
-      <c r="A47" s="34" t="inlineStr">
+      <c r="B46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Đầu tư dài hạn khác</t>
         </is>
       </c>
-      <c r="B47" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="15">
-      <c r="A48" s="34" t="inlineStr">
+      <c r="B47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Dự phòng giảm giá đầu tư dài hạn</t>
         </is>
       </c>
-      <c r="B48" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="15">
-      <c r="A49" s="34" t="inlineStr">
+      <c r="B48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Lợi thế thương mại (trước 2015)</t>
         </is>
       </c>
-      <c r="B49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="15">
-      <c r="A50" s="34" t="inlineStr">
+      <c r="B49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B50" s="35" t="n">
+      <c r="B50" s="4" t="n">
         <v>157004126788</v>
       </c>
-      <c r="C50" s="35" t="n">
+      <c r="C50" s="4" t="n">
         <v>169373442894</v>
       </c>
-      <c r="D50" s="35" t="n">
+      <c r="D50" s="4" t="n">
         <v>195418574905</v>
       </c>
-      <c r="E50" s="35" t="n">
+      <c r="E50" s="4" t="n">
         <v>177772171793</v>
       </c>
     </row>
-    <row r="51" ht="15" customHeight="1" s="15">
-      <c r="A51" s="34" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Trả trước dài hạn</t>
         </is>
       </c>
-      <c r="B51" s="35" t="n">
+      <c r="B51" s="4" t="n">
         <v>157004126788</v>
       </c>
-      <c r="C51" s="35" t="n">
+      <c r="C51" s="4" t="n">
         <v>169373442894</v>
       </c>
-      <c r="D51" s="35" t="n">
+      <c r="D51" s="4" t="n">
         <v>195418574905</v>
       </c>
-      <c r="E51" s="35" t="n">
+      <c r="E51" s="4" t="n">
         <v>177766571925</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" s="15">
-      <c r="A52" s="34" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="35" t="n">
-        <v>5599868</v>
-      </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="15">
-      <c r="A53" s="34" t="inlineStr">
+      <c r="B52" s="4" t="n">
+        <v>31681844</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>31681844</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>14902586</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B53" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C53" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="15">
-      <c r="A54" s="34" t="inlineStr">
+      <c r="B53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B54" s="35" t="n">
+      <c r="B54" s="4" t="n">
         <v>23714236170376</v>
       </c>
-      <c r="C54" s="35" t="n">
+      <c r="C54" s="4" t="n">
         <v>15832550399101</v>
       </c>
-      <c r="D54" s="35" t="n">
+      <c r="D54" s="4" t="n">
         <v>13098449902604</v>
       </c>
-      <c r="E54" s="35" t="n">
+      <c r="E54" s="4" t="n">
         <v>10523796935046</v>
       </c>
     </row>
-    <row r="55" ht="15" customHeight="1" s="15">
-      <c r="A55" s="34" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B55" s="35" t="n">
+      <c r="B55" s="4" t="n">
         <v>18575165477143</v>
       </c>
-      <c r="C55" s="35" t="n">
+      <c r="C55" s="4" t="n">
         <v>13712736684773</v>
       </c>
-      <c r="D55" s="35" t="n">
+      <c r="D55" s="4" t="n">
         <v>11379279324447</v>
       </c>
-      <c r="E55" s="35" t="n">
+      <c r="E55" s="4" t="n">
         <v>8474461394877</v>
       </c>
     </row>
-    <row r="56" ht="15" customHeight="1" s="15">
-      <c r="A56" s="34" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B56" s="35" t="n">
+      <c r="B56" s="4" t="n">
         <v>18574474295299</v>
       </c>
-      <c r="C56" s="35" t="n">
+      <c r="C56" s="4" t="n">
         <v>13712183502929</v>
       </c>
-      <c r="D56" s="35" t="n">
+      <c r="D56" s="4" t="n">
         <v>11378723422861</v>
       </c>
-      <c r="E56" s="35" t="n">
+      <c r="E56" s="4" t="n">
         <v>8474374694877</v>
       </c>
     </row>
-    <row r="57" ht="15" customHeight="1" s="15">
-      <c r="A57" s="34" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B57" s="35" t="n">
+      <c r="B57" s="4" t="n">
         <v>10051507915817</v>
       </c>
-      <c r="C57" s="35" t="n">
+      <c r="C57" s="4" t="n">
         <v>8800349446066</v>
       </c>
-      <c r="D57" s="35" t="n">
+      <c r="D57" s="4" t="n">
         <v>8108271528775</v>
       </c>
-      <c r="E57" s="35" t="n">
+      <c r="E57" s="4" t="n">
         <v>5363331144812</v>
       </c>
     </row>
-    <row r="58" ht="15" customHeight="1" s="15">
-      <c r="A58" s="34" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B58" s="35" t="n">
+      <c r="B58" s="4" t="n">
         <v>5995965425047</v>
       </c>
-      <c r="C58" s="35" t="n">
+      <c r="C58" s="4" t="n">
         <v>3202439604461</v>
       </c>
-      <c r="D58" s="35" t="n">
+      <c r="D58" s="4" t="n">
         <v>2274331043145</v>
       </c>
-      <c r="E58" s="35" t="n">
+      <c r="E58" s="4" t="n">
         <v>2307356375016</v>
       </c>
     </row>
-    <row r="59" ht="15" customHeight="1" s="15">
-      <c r="A59" s="34" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>Người mua trả tiền trước</t>
         </is>
       </c>
-      <c r="B59" s="35" t="n">
+      <c r="B59" s="4" t="n">
         <v>61615375012</v>
       </c>
-      <c r="C59" s="35" t="n">
+      <c r="C59" s="4" t="n">
         <v>37870117550</v>
       </c>
-      <c r="D59" s="35" t="n">
+      <c r="D59" s="4" t="n">
         <v>23463598041</v>
       </c>
-      <c r="E59" s="35" t="n">
+      <c r="E59" s="4" t="n">
         <v>34974952041</v>
       </c>
     </row>
-    <row r="60" ht="15" customHeight="1" s="15">
-      <c r="A60" s="34" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
         <is>
           <t>Thuế và các khoản phải trả Nhà nước</t>
         </is>
       </c>
-      <c r="B60" s="35" t="n">
+      <c r="B60" s="4" t="n">
         <v>244716064984</v>
       </c>
-      <c r="C60" s="35" t="n">
+      <c r="C60" s="4" t="n">
         <v>124543935725</v>
       </c>
-      <c r="D60" s="35" t="n">
+      <c r="D60" s="4" t="n">
         <v>39713137523</v>
       </c>
-      <c r="E60" s="35" t="n">
+      <c r="E60" s="4" t="n">
         <v>3120462679</v>
       </c>
     </row>
-    <row r="61" ht="15" customHeight="1" s="15">
-      <c r="A61" s="34" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
         <is>
           <t>Phải trả người lao động</t>
         </is>
       </c>
-      <c r="B61" s="35" t="n">
+      <c r="B61" s="4" t="n">
         <v>1331638783393</v>
       </c>
-      <c r="C61" s="35" t="n">
+      <c r="C61" s="4" t="n">
         <v>1034444152158</v>
       </c>
-      <c r="D61" s="35" t="n">
+      <c r="D61" s="4" t="n">
         <v>669094486391</v>
       </c>
-      <c r="E61" s="35" t="n">
+      <c r="E61" s="4" t="n">
         <v>535694930652</v>
       </c>
     </row>
-    <row r="62" ht="15" customHeight="1" s="15">
-      <c r="A62" s="34" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
         <is>
           <t>Chi phí phải trả</t>
         </is>
       </c>
-      <c r="B62" s="35" t="n">
+      <c r="B62" s="4" t="n">
         <v>281753290017</v>
       </c>
-      <c r="C62" s="35" t="n">
+      <c r="C62" s="4" t="n">
         <v>194907134412</v>
       </c>
-      <c r="D62" s="35" t="n">
+      <c r="D62" s="4" t="n">
         <v>125947493296</v>
       </c>
-      <c r="E62" s="35" t="n">
+      <c r="E62" s="4" t="n">
         <v>103346666037</v>
       </c>
     </row>
-    <row r="63" ht="15" customHeight="1" s="15">
-      <c r="A63" s="34" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
         <is>
           <t>Phải trả nội bộ</t>
         </is>
       </c>
-      <c r="B63" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C63" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="15">
-      <c r="A64" s="34" t="inlineStr">
+      <c r="B63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>Phải trả về xây dựng cơ bản</t>
         </is>
       </c>
-      <c r="B64" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C64" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="15">
-      <c r="A65" s="34" t="inlineStr">
+      <c r="B64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>Phải trả khác</t>
         </is>
       </c>
-      <c r="B65" s="35" t="n">
+      <c r="B65" s="4" t="n">
         <v>94765132430</v>
       </c>
-      <c r="C65" s="35" t="n">
+      <c r="C65" s="4" t="n">
         <v>89015814529</v>
       </c>
-      <c r="D65" s="35" t="n">
+      <c r="D65" s="4" t="n">
         <v>113315953611</v>
       </c>
-      <c r="E65" s="35" t="n">
+      <c r="E65" s="4" t="n">
         <v>112206340770</v>
       </c>
     </row>
-    <row r="66" ht="15" customHeight="1" s="15">
-      <c r="A66" s="34" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>Dự phòng các khoản phải trả ngắn hạn</t>
         </is>
       </c>
-      <c r="B66" s="35" t="n">
+      <c r="B66" s="4" t="n">
         <v>5828163047</v>
       </c>
-      <c r="C66" s="35" t="n">
+      <c r="C66" s="4" t="n">
         <v>2956037244</v>
       </c>
-      <c r="D66" s="35" t="n">
+      <c r="D66" s="4" t="n">
         <v>303659660</v>
       </c>
-      <c r="E66" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="15">
-      <c r="A67" s="34" t="inlineStr">
+      <c r="E66" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>Quỹ khen thưởng, phúc lợi</t>
         </is>
       </c>
-      <c r="B67" s="35" t="n">
+      <c r="B67" s="4" t="n">
         <v>8178120854</v>
       </c>
-      <c r="C67" s="35" t="n">
+      <c r="C67" s="4" t="n">
         <v>5733824194</v>
       </c>
-      <c r="D67" s="35" t="n">
+      <c r="D67" s="4" t="n">
         <v>10677497597</v>
       </c>
-      <c r="E67" s="35" t="n">
+      <c r="E67" s="4" t="n">
         <v>14021497597</v>
       </c>
     </row>
-    <row r="68" ht="15" customHeight="1" s="15">
-      <c r="A68" s="34" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B68" s="35" t="n">
+      <c r="B68" s="4" t="n">
         <v>691181844</v>
       </c>
-      <c r="C68" s="35" t="n">
+      <c r="C68" s="4" t="n">
         <v>553181844</v>
       </c>
-      <c r="D68" s="35" t="n">
+      <c r="D68" s="4" t="n">
         <v>555901586</v>
       </c>
-      <c r="E68" s="35" t="n">
+      <c r="E68" s="4" t="n">
         <v>86700000</v>
       </c>
     </row>
-    <row r="69" ht="15" customHeight="1" s="15">
-      <c r="A69" s="34" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>Phải trả nhà cung cấp dài hạn</t>
         </is>
       </c>
-      <c r="B69" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C69" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" ht="15" customHeight="1" s="15">
-      <c r="A70" s="34" t="inlineStr">
+      <c r="B69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>Phải trả nội bộ dài hạn</t>
         </is>
       </c>
-      <c r="B70" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C70" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" ht="15" customHeight="1" s="15">
-      <c r="A71" s="34" t="inlineStr">
+      <c r="B70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>Phải trả dài hạn khác</t>
         </is>
       </c>
-      <c r="B71" s="35" t="n">
+      <c r="B71" s="4" t="n">
         <v>659500000</v>
       </c>
-      <c r="C71" s="35" t="n">
+      <c r="C71" s="4" t="n">
         <v>521500000</v>
       </c>
-      <c r="D71" s="35" t="n">
+      <c r="D71" s="4" t="n">
         <v>540999000</v>
       </c>
-      <c r="E71" s="35" t="n">
+      <c r="E71" s="4" t="n">
         <v>86700000</v>
       </c>
     </row>
-    <row r="72" ht="15" customHeight="1" s="15">
-      <c r="A72" s="34" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B72" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C72" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" ht="15" customHeight="1" s="15">
-      <c r="A73" s="34" t="inlineStr">
+      <c r="B72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B73" s="35" t="n">
+      <c r="B73" s="4" t="n">
         <v>31681844</v>
       </c>
-      <c r="C73" s="35" t="n">
+      <c r="C73" s="4" t="n">
         <v>31681844</v>
       </c>
-      <c r="D73" s="35" t="n">
+      <c r="D73" s="4" t="n">
         <v>14902586</v>
       </c>
-      <c r="E73" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" ht="15" customHeight="1" s="15">
-      <c r="A74" s="34" t="inlineStr">
+      <c r="E73" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>Dự phòng trợ cấp thôi việc</t>
         </is>
       </c>
-      <c r="B74" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C74" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" ht="15" customHeight="1" s="15">
-      <c r="A75" s="34" t="inlineStr">
+      <c r="B74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>Dự phòng các khoản nợ dài hạn</t>
         </is>
       </c>
-      <c r="B75" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C75" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" ht="15" customHeight="1" s="15">
-      <c r="A76" s="34" t="inlineStr">
+      <c r="B75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>Doanh thu chưa thực hiện</t>
         </is>
       </c>
-      <c r="B76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" ht="15" customHeight="1" s="15">
-      <c r="A77" s="34" t="inlineStr">
+      <c r="B76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>Quỹ phát triển khoa học công nghệ</t>
         </is>
       </c>
-      <c r="B77" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C77" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" ht="15" customHeight="1" s="15">
-      <c r="A78" s="34" t="inlineStr">
+      <c r="B77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B78" s="35" t="n">
+      <c r="B78" s="4" t="n">
         <v>5139070693233</v>
       </c>
-      <c r="C78" s="35" t="n">
+      <c r="C78" s="4" t="n">
         <v>2119813714328</v>
       </c>
-      <c r="D78" s="35" t="n">
+      <c r="D78" s="4" t="n">
         <v>1719170578157</v>
       </c>
-      <c r="E78" s="35" t="n">
+      <c r="E78" s="4" t="n">
         <v>2049335540169</v>
       </c>
     </row>
-    <row r="79" ht="15" customHeight="1" s="15">
-      <c r="A79" s="34" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>Vốn và các quỹ</t>
         </is>
       </c>
-      <c r="B79" s="35" t="n">
+      <c r="B79" s="4" t="n">
         <v>5139070693233</v>
       </c>
-      <c r="C79" s="35" t="n">
+      <c r="C79" s="4" t="n">
         <v>2119813714328</v>
       </c>
-      <c r="D79" s="35" t="n">
+      <c r="D79" s="4" t="n">
         <v>1719170578157</v>
       </c>
-      <c r="E79" s="35" t="n">
+      <c r="E79" s="4" t="n">
         <v>2049335540169</v>
       </c>
     </row>
-    <row r="80" ht="15" customHeight="1" s="15">
-      <c r="A80" s="34" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>Vốn góp</t>
         </is>
       </c>
-      <c r="B80" s="35" t="n">
+      <c r="B80" s="4" t="n">
         <v>1703017850000</v>
       </c>
-      <c r="C80" s="35" t="n">
+      <c r="C80" s="4" t="n">
         <v>1362423890000</v>
       </c>
-      <c r="D80" s="35" t="n">
+      <c r="D80" s="4" t="n">
         <v>1362423890000</v>
       </c>
-      <c r="E80" s="35" t="n">
+      <c r="E80" s="4" t="n">
         <v>1184725350000</v>
       </c>
     </row>
-    <row r="81" ht="15" customHeight="1" s="15">
-      <c r="A81" s="34" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>Thặng dư vốn cổ phần</t>
         </is>
       </c>
-      <c r="B81" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C81" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" ht="15" customHeight="1" s="15">
-      <c r="A82" s="34" t="inlineStr">
+      <c r="B81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>Vốn khác</t>
         </is>
       </c>
-      <c r="B82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" ht="15" customHeight="1" s="15">
-      <c r="A83" s="34" t="inlineStr">
+      <c r="B82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu quỹ</t>
         </is>
       </c>
-      <c r="B83" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C83" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" ht="15" customHeight="1" s="15">
-      <c r="A84" s="34" t="inlineStr">
+      <c r="B83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>Chênh lệch đánh giá lại tài sản</t>
         </is>
       </c>
-      <c r="B84" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C84" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" ht="15" customHeight="1" s="15">
-      <c r="A85" s="34" t="inlineStr">
+      <c r="B84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>Chênh lệch tỷ giá</t>
         </is>
       </c>
-      <c r="B85" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C85" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" ht="15" customHeight="1" s="15">
-      <c r="A86" s="34" t="inlineStr">
+      <c r="B85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>Quỹ đầu tư và phát triển</t>
         </is>
       </c>
-      <c r="B86" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C86" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" ht="15" customHeight="1" s="15">
-      <c r="A87" s="34" t="inlineStr">
+      <c r="B86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>Quỹ dự phòng tài chính</t>
         </is>
       </c>
-      <c r="B87" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C87" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" ht="15" customHeight="1" s="15">
-      <c r="A88" s="34" t="inlineStr">
+      <c r="B87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>Quỹ khác</t>
         </is>
       </c>
-      <c r="B88" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C88" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" ht="15" customHeight="1" s="15">
-      <c r="A89" s="34" t="inlineStr">
+      <c r="B88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>Lãi chưa phân phối</t>
         </is>
       </c>
-      <c r="B89" s="35" t="n">
+      <c r="B89" s="4" t="n">
         <v>2468442850502</v>
       </c>
-      <c r="C89" s="35" t="n">
+      <c r="C89" s="4" t="n">
         <v>549386390157</v>
       </c>
-      <c r="D89" s="35" t="n">
+      <c r="D89" s="4" t="n">
         <v>236832252322</v>
       </c>
-      <c r="E89" s="35" t="n">
+      <c r="E89" s="4" t="n">
         <v>823505616594</v>
       </c>
     </row>
-    <row r="90" ht="15" customHeight="1" s="15">
-      <c r="A90" s="34" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>Quỹ hỗ trợ sắp xếp doanh nghiệp</t>
         </is>
       </c>
-      <c r="B90" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C90" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" ht="15" customHeight="1" s="15">
-      <c r="A91" s="34" t="inlineStr">
+      <c r="B90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>Vốn Ngân sách nhà nước và quỹ khác</t>
         </is>
       </c>
-      <c r="B91" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C91" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" ht="15" customHeight="1" s="15">
-      <c r="A92" s="34" t="inlineStr">
+      <c r="B91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Quỹ khen thưởng, phúc lợi (trước 2010)</t>
         </is>
       </c>
-      <c r="B92" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C92" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" ht="15" customHeight="1" s="15">
-      <c r="A93" s="34" t="inlineStr">
+      <c r="B92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>Vốn ngân sách nhà nước và quỹ khác</t>
         </is>
       </c>
-      <c r="B93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E93" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" ht="15" customHeight="1" s="15">
-      <c r="A94" s="34" t="inlineStr">
+      <c r="B93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>Lợi ích của cổ đông thiểu số</t>
         </is>
       </c>
-      <c r="B94" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C94" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" ht="15" customHeight="1" s="15">
-      <c r="A95" s="34" t="inlineStr">
+      <c r="B94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>Tổng cộng nguồn vốn</t>
         </is>
       </c>
-      <c r="B95" s="35" t="n">
+      <c r="B95" s="4" t="n">
         <v>23714236170376</v>
       </c>
-      <c r="C95" s="35" t="n">
+      <c r="C95" s="4" t="n">
         <v>15832550399101</v>
       </c>
-      <c r="D95" s="35" t="n">
+      <c r="D95" s="4" t="n">
         <v>13098449902604</v>
       </c>
-      <c r="E95" s="35" t="n">
+      <c r="E95" s="4" t="n">
         <v>10523796935046</v>
       </c>
     </row>
-    <row r="96" ht="15" customHeight="1" s="15">
-      <c r="A96" s="34" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B96" s="36" t="n"/>
-      <c r="C96" s="36" t="n"/>
-      <c r="D96" s="36" t="n"/>
-      <c r="E96" s="36" t="n"/>
-    </row>
-    <row r="97" ht="15" customHeight="1" s="15">
-      <c r="A97" s="34" t="inlineStr">
+      <c r="B96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B97" s="35" t="n">
-        <v>5929000000000</v>
-      </c>
-      <c r="C97" s="35" t="n">
-        <v>986000000000</v>
-      </c>
-      <c r="D97" s="35" t="n">
-        <v>1194000000000</v>
-      </c>
-      <c r="E97" s="35" t="n">
-        <v>1119000000000</v>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="15">
-      <c r="A98" s="34" t="inlineStr">
+      <c r="B97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>Vốn kinh doanh ở các đơn vị trực thuộc</t>
         </is>
       </c>
-      <c r="B98" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C98" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" ht="15" customHeight="1" s="15">
-      <c r="A99" s="34" t="inlineStr">
+      <c r="B98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>Tài sản thiếu cần xử lý</t>
         </is>
       </c>
-      <c r="B99" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" ht="15" customHeight="1" s="15">
-      <c r="A100" s="34" t="inlineStr">
+      <c r="B99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>Phải thu cho vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B100" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C100" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="35" t="n">
+      <c r="B100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4" t="n">
         <v>40000000000</v>
       </c>
     </row>
-    <row r="101" ht="15" customHeight="1" s="15">
-      <c r="A101" s="34" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>Giao dịch mua bán lại trái phiếu Chính phủ</t>
         </is>
       </c>
-      <c r="B101" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C101" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" ht="15" customHeight="1" s="15">
-      <c r="A102" s="34" t="inlineStr">
+      <c r="B101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>Trả trước người bán dài hạn</t>
         </is>
       </c>
-      <c r="B102" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C102" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="15">
-      <c r="A103" s="34" t="inlineStr">
+      <c r="B102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Phải thu cho vay dài hạn</t>
         </is>
       </c>
-      <c r="B103" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C103" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" ht="15" customHeight="1" s="15">
-      <c r="A104" s="34" t="inlineStr">
+      <c r="B103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>Tài sản dở dang dài hạn</t>
         </is>
       </c>
-      <c r="B104" s="35" t="n">
+      <c r="B104" s="4" t="n">
         <v>1411954000</v>
       </c>
-      <c r="C104" s="35" t="n">
+      <c r="C104" s="4" t="n">
         <v>8230000000</v>
       </c>
-      <c r="D104" s="35" t="n">
+      <c r="D104" s="4" t="n">
         <v>770956800</v>
       </c>
-      <c r="E104" s="35" t="n">
+      <c r="E104" s="4" t="n">
         <v>1795608000</v>
       </c>
     </row>
-    <row r="105" ht="15" customHeight="1" s="15">
-      <c r="A105" s="34" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>Chi phí sản xuất, kinh doanh dở dang dài hạn</t>
         </is>
       </c>
-      <c r="B105" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C105" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" ht="15" customHeight="1" s="15">
-      <c r="A106" s="34" t="inlineStr">
+      <c r="B105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B106" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1" s="15">
-      <c r="A107" s="34" t="inlineStr">
+      <c r="B106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>Thiết bị, vật tư, phụ tùng thay thế dài hạn</t>
         </is>
       </c>
-      <c r="B107" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C107" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1" s="15">
-      <c r="A108" s="34" t="inlineStr">
+      <c r="B107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>Doanh thu chưa thực hiện ngắn hạn</t>
         </is>
       </c>
-      <c r="B108" s="35" t="n">
+      <c r="B108" s="4" t="n">
         <v>498506024698</v>
       </c>
-      <c r="C108" s="35" t="n">
+      <c r="C108" s="4" t="n">
         <v>219923436590</v>
       </c>
-      <c r="D108" s="35" t="n">
+      <c r="D108" s="4" t="n">
         <v>13605024822</v>
       </c>
-      <c r="E108" s="35" t="n">
+      <c r="E108" s="4" t="n">
         <v>322325273</v>
       </c>
     </row>
-    <row r="109" ht="15" customHeight="1" s="15">
-      <c r="A109" s="34" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>Quỹ bình ổn giá</t>
         </is>
       </c>
-      <c r="B109" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" ht="15" customHeight="1" s="15">
-      <c r="A110" s="34" t="inlineStr">
+      <c r="B109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>Giao dịch mua bán lại trái phiếu chính phủ</t>
         </is>
       </c>
-      <c r="B110" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" ht="15" customHeight="1" s="15">
-      <c r="A111" s="34" t="inlineStr">
+      <c r="B110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>Người mua trả tiền trước dài hạn</t>
         </is>
       </c>
-      <c r="B111" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" ht="15" customHeight="1" s="15">
-      <c r="A112" s="34" t="inlineStr">
+      <c r="B111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>Chi phí phải trả dài hạn</t>
         </is>
       </c>
-      <c r="B112" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E112" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" ht="15" customHeight="1" s="15">
-      <c r="A113" s="34" t="inlineStr">
+      <c r="B112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>Phải trả nội bộ về vốn kinh doanh</t>
         </is>
       </c>
-      <c r="B113" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" ht="15" customHeight="1" s="15">
-      <c r="A114" s="34" t="inlineStr">
+      <c r="B113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>Trái phiếu chuyển đổi</t>
         </is>
       </c>
-      <c r="B114" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" ht="15" customHeight="1" s="15">
-      <c r="A115" s="34" t="inlineStr">
+      <c r="B114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1" s="15">
-      <c r="A116" s="34" t="inlineStr">
+      <c r="B115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>Cổ phiếu phổ thông</t>
         </is>
       </c>
-      <c r="B116" s="35" t="n">
+      <c r="B116" s="4" t="n">
         <v>1703017850000</v>
       </c>
-      <c r="C116" s="35" t="n">
+      <c r="C116" s="4" t="n">
         <v>1362423890000</v>
       </c>
-      <c r="D116" s="35" t="n">
+      <c r="D116" s="4" t="n">
         <v>1362423890000</v>
       </c>
-      <c r="E116" s="35" t="n">
+      <c r="E116" s="4" t="n">
         <v>1184725350000</v>
       </c>
     </row>
-    <row r="117" ht="15" customHeight="1" s="15">
-      <c r="A117" s="34" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>Quyền chọn chuyển đổi trái phiếu</t>
         </is>
       </c>
-      <c r="B117" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E117" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" ht="15" customHeight="1" s="15">
-      <c r="A118" s="34" t="inlineStr">
+      <c r="B117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>LNST chưa phân phối lũy kế đến cuối kỳ trước</t>
         </is>
       </c>
-      <c r="B118" s="35" t="n">
+      <c r="B118" s="4" t="n">
         <v>197121393961</v>
       </c>
-      <c r="C118" s="35" t="n">
+      <c r="C118" s="4" t="n">
         <v>236975520956</v>
       </c>
-      <c r="D118" s="35" t="n">
+      <c r="D118" s="4" t="n">
         <v>586570809094</v>
       </c>
-      <c r="E118" s="35" t="n">
+      <c r="E118" s="4" t="n">
         <v>437992070152</v>
       </c>
     </row>
-    <row r="119" ht="15" customHeight="1" s="15">
-      <c r="A119" s="34" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>LNST chưa phân phối kỳ này</t>
         </is>
       </c>
-      <c r="B119" s="35" t="n">
+      <c r="B119" s="4" t="n">
         <v>2271321456541</v>
       </c>
-      <c r="C119" s="35" t="n">
+      <c r="C119" s="4" t="n">
         <v>312410869201</v>
       </c>
-      <c r="D119" s="35" t="n">
+      <c r="D119" s="4" t="n">
         <v>-349738556772</v>
       </c>
-      <c r="E119" s="35" t="n">
+      <c r="E119" s="4" t="n">
         <v>385513546442</v>
       </c>
     </row>
-    <row r="120" ht="15" customHeight="1" s="15">
-      <c r="A120" s="34" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>Xây dựng cơ bản đang dở dang</t>
         </is>
       </c>
-      <c r="B120" s="35" t="n">
+      <c r="B120" s="4" t="n">
         <v>1411954000</v>
       </c>
-      <c r="C120" s="35" t="n">
+      <c r="C120" s="4" t="n">
         <v>8230000000</v>
       </c>
-      <c r="D120" s="35" t="n">
+      <c r="D120" s="4" t="n">
         <v>770956800</v>
       </c>
-      <c r="E120" s="35" t="n">
+      <c r="E120" s="4" t="n">
         <v>1795608000</v>
       </c>
     </row>
-    <row r="121" ht="15" customHeight="1" s="15">
-      <c r="A121" s="34" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>Lợi thế thương mại</t>
         </is>
       </c>
-      <c r="B121" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" ht="15" customHeight="1" s="15">
-      <c r="A122" s="34" t="inlineStr">
+      <c r="B121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>Lợi ích cổ đông không kiểm soát</t>
         </is>
       </c>
-      <c r="B122" s="35" t="n">
+      <c r="B122" s="4" t="n">
         <v>967609992731</v>
       </c>
-      <c r="C122" s="35" t="n">
+      <c r="C122" s="4" t="n">
         <v>208003434171</v>
       </c>
-      <c r="D122" s="35" t="n">
+      <c r="D122" s="4" t="n">
         <v>119914435835</v>
       </c>
-      <c r="E122" s="35" t="n">
+      <c r="E122" s="4" t="n">
         <v>41104573575</v>
       </c>
     </row>
-    <row r="123" ht="15" customHeight="1" s="15">
-      <c r="A123" s="34" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>Nguồn kinh phí đã hình thành TSCĐ</t>
         </is>
       </c>
-      <c r="B123" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" s="35" t="n">
+      <c r="B123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="15" customWidth="1" style="15" min="2" max="2"/>
-    <col width="15" customWidth="1" style="15" min="3" max="3"/>
-    <col width="15" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" s="32" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="33" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="33" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="33" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="15">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Doanh thu bán hàng và cung cấp dịch vụ</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n">
+      <c r="B2" s="4" t="n">
         <v>51232049640567</v>
       </c>
-      <c r="C2" s="35" t="n">
+      <c r="C2" s="4" t="n">
         <v>40241629282059</v>
       </c>
-      <c r="D2" s="35" t="n">
+      <c r="D2" s="4" t="n">
         <v>31975613596365</v>
       </c>
-      <c r="E2" s="35" t="n">
+      <c r="E2" s="4" t="n">
         <v>30276710796279</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Các khoản giảm trừ doanh thu</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="4" t="n">
         <v>-149181195799</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="4" t="n">
         <v>-137136750875</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="4" t="n">
         <v>-125963979645</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="4" t="n">
         <v>-110910039609</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="15">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="4" t="n">
         <v>51082868444768</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="4" t="n">
         <v>40104492531184</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="4" t="n">
         <v>31849649616720</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="4" t="n">
         <v>30165800756670</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="15">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="4" t="n">
         <v>-41073163986683</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="4" t="n">
         <v>-32521431587237</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="4" t="n">
         <v>-26688006159054</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="4" t="n">
         <v>-25462623377413</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
+      <c r="B6" s="4" t="n">
         <v>10009704458085</v>
       </c>
-      <c r="C6" s="35" t="n">
+      <c r="C6" s="4" t="n">
         <v>7583060943947</v>
       </c>
-      <c r="D6" s="35" t="n">
+      <c r="D6" s="4" t="n">
         <v>5161643457666</v>
       </c>
-      <c r="E6" s="35" t="n">
+      <c r="E6" s="4" t="n">
         <v>4703177379257</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" s="34" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>Doanh thu hoạt động tài chính</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="4" t="n">
         <v>287764741779</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="4" t="n">
         <v>106913298138</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="4" t="n">
         <v>80257624527</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="4" t="n">
         <v>173746497842</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="15">
-      <c r="A8" s="34" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Chi phí tài chính</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="4" t="n">
         <v>-388683187751</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="4" t="n">
         <v>-253792623553</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="4" t="n">
         <v>-292262559450</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="4" t="n">
         <v>-256319530992</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="15">
-      <c r="A9" s="34" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="4" t="n">
         <v>-388595922369</v>
       </c>
-      <c r="C9" s="35" t="n">
+      <c r="C9" s="4" t="n">
         <v>-253428831252</v>
       </c>
-      <c r="D9" s="35" t="n">
+      <c r="D9" s="4" t="n">
         <v>-284917373606</v>
       </c>
-      <c r="E9" s="35" t="n">
+      <c r="E9" s="4" t="n">
         <v>-231527904809</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="15">
-      <c r="A10" s="34" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="4" t="n">
         <v>-7018206246026</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="4" t="n">
         <v>-5527210989725</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="4" t="n">
         <v>-4169668799072</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="4" t="n">
         <v>-3259297597681</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="4" t="n">
         <v>-1677744619772</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="4" t="n">
         <v>-1365833850070</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="4" t="n">
         <v>-1076478805719</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="4" t="n">
         <v>-887338884656</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="4" t="n">
         <v>1212835146315</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="4" t="n">
         <v>543136778737</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="4" t="n">
         <v>-296509082048</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="4" t="n">
         <v>473967863770</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Thu nhập khác</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="4" t="n">
         <v>29912692698</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="4" t="n">
         <v>24090237620</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="4" t="n">
         <v>22062244997</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="4" t="n">
         <v>16254109001</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Chi phí khác</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="4" t="n">
         <v>-23630336340</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="4" t="n">
         <v>-40269928171</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="4" t="n">
         <v>-19734846239</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="4" t="n">
         <v>-4598558802</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Thu nhập khác, ròng</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="4" t="n">
         <v>6282356358</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="4" t="n">
         <v>-16179690551</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="4" t="n">
         <v>2327398758</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="4" t="n">
         <v>11655550199</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ công ty liên doanh</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="15">
-      <c r="A17" s="34" t="inlineStr">
+      <c r="B16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) trước thuế</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
+      <c r="B17" s="4" t="n">
         <v>1219117502673</v>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="4" t="n">
         <v>526957088186</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="4" t="n">
         <v>-294181683290</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="4" t="n">
         <v>485623413969</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="15">
-      <c r="A18" s="34" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập doanh nghiệp - hiện thời</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
+      <c r="B18" s="4" t="n">
         <v>-234877775599</v>
       </c>
-      <c r="C18" s="35" t="n">
+      <c r="C18" s="4" t="n">
         <v>-118526676650</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="4" t="n">
         <v>-34994338768</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="4" t="n">
         <v>-86686691655</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập doanh nghiệp - hoãn lại</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="35" t="n">
+      <c r="B19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="n">
         <v>-16779258</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="4" t="n">
         <v>-20502454</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="4" t="n">
         <v>-862524906</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="15">
-      <c r="A20" s="34" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Chi phí thuế thu nhập doanh nghiệp</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="4" t="n">
         <v>-234877775599</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="4" t="n">
         <v>-118543455908</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="4" t="n">
         <v>-35014841222</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="4" t="n">
         <v>-87549216561</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="4" t="n">
         <v>984239727074</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="4" t="n">
         <v>408413632278</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="4" t="n">
         <v>-329196524512</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="4" t="n">
         <v>398074197408</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Lợi ích của cổ đông thiểu số</t>
         </is>
       </c>
-      <c r="B22" s="35" t="n">
+      <c r="B22" s="4" t="n">
         <v>189374783523</v>
       </c>
-      <c r="C22" s="35" t="n">
+      <c r="C22" s="4" t="n">
         <v>90897366661</v>
       </c>
-      <c r="D22" s="35" t="n">
+      <c r="D22" s="4" t="n">
         <v>16446964816</v>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="4" t="n">
         <v>7713342831</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="15">
-      <c r="A23" s="34" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="4" t="n">
         <v>794864943551</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="4" t="n">
         <v>317516265617</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="4" t="n">
         <v>-345643489328</v>
       </c>
-      <c r="E23" s="35" t="n">
+      <c r="E23" s="4" t="n">
         <v>390360854577</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Lãi cơ bản trên cổ phiếu (VND)</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n">
+      <c r="B24" s="4" t="n">
         <v>4653</v>
       </c>
-      <c r="C24" s="35" t="n">
+      <c r="C24" s="4" t="n">
         <v>2293</v>
       </c>
-      <c r="D24" s="35" t="n">
+      <c r="D24" s="4" t="n">
         <v>-2537</v>
       </c>
-      <c r="E24" s="35" t="n">
+      <c r="E24" s="4" t="n">
         <v>2865</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="15">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Lãi trên cổ phiếu pha loãng (VND)</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
+      <c r="B25" s="4" t="n">
         <v>4653</v>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="4" t="n">
         <v>2293</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="4" t="n">
         <v>-2537</v>
       </c>
-      <c r="E25" s="35" t="n">
+      <c r="E25" s="4" t="n">
         <v>2865</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" s="34" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ công ty liên doanh (từ năm 2015)</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="35" t="n">
+      <c r="B26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="15" customWidth="1" style="15" min="2" max="2"/>
-    <col width="15" customWidth="1" style="15" min="3" max="3"/>
-    <col width="15" customWidth="1" style="15" min="4" max="4"/>
-    <col width="15" customWidth="1" style="15" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="15">
-      <c r="A1" s="32" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>item</t>
         </is>
       </c>
-      <c r="B1" s="33" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="C1" s="33" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="D1" s="33" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="E1" s="33" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="15">
-      <c r="A2" s="34" t="inlineStr">
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận/(lỗ) trước thuế</t>
         </is>
       </c>
-      <c r="B2" s="35" t="n">
+      <c r="B2" s="4" t="n">
         <v>1219117502673</v>
       </c>
-      <c r="C2" s="35" t="n">
+      <c r="C2" s="4" t="n">
         <v>526957088186</v>
       </c>
-      <c r="D2" s="35" t="n">
+      <c r="D2" s="4" t="n">
         <v>-294181683290</v>
       </c>
-      <c r="E2" s="35" t="n">
+      <c r="E2" s="4" t="n">
         <v>485623413969</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="15">
-      <c r="A3" s="34" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Khấu hao TSCĐ và BĐSĐT</t>
         </is>
       </c>
-      <c r="B3" s="35" t="n">
+      <c r="B3" s="4" t="n">
         <v>402557018224</v>
       </c>
-      <c r="C3" s="35" t="n">
+      <c r="C3" s="4" t="n">
         <v>318442950010</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="4" t="n">
         <v>233071988505</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="4" t="n">
         <v>115286135177</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="15">
-      <c r="A4" s="34" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Chi phí dự phòng</t>
         </is>
       </c>
-      <c r="B4" s="35" t="n">
+      <c r="B4" s="4" t="n">
         <v>32010999772</v>
       </c>
-      <c r="C4" s="35" t="n">
+      <c r="C4" s="4" t="n">
         <v>17863960788</v>
       </c>
-      <c r="D4" s="35" t="n">
+      <c r="D4" s="4" t="n">
         <v>2521192297</v>
       </c>
-      <c r="E4" s="35" t="n">
+      <c r="E4" s="4" t="n">
         <v>-4485565669</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="15">
-      <c r="A5" s="34" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Lãi/lỗ chênh lệch tỷ giá hối đoái do đánh giá lại các khoản mục tiền tệ có gốc ngoại tệ</t>
         </is>
       </c>
-      <c r="B5" s="35" t="n">
+      <c r="B5" s="4" t="n">
         <v>-20360895</v>
       </c>
-      <c r="C5" s="35" t="n">
+      <c r="C5" s="4" t="n">
         <v>-158409220</v>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="4" t="n">
         <v>-74512931</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="4" t="n">
         <v>-42532911</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="15">
-      <c r="A6" s="34" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ thanh lý tài sản cố định</t>
         </is>
       </c>
-      <c r="B6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="15">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="B6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>(Lãi)/lỗ từ hoạt động đầu tư</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="4" t="n">
         <v>-267669594473</v>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="4" t="n">
         <v>-70652632259</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="4" t="n">
         <v>-50019830875</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="4" t="n">
         <v>-147853905457</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="15">
-      <c r="A8" s="34" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="4" t="n">
         <v>388595922369</v>
       </c>
-      <c r="C8" s="35" t="n">
+      <c r="C8" s="4" t="n">
         <v>253428831252</v>
       </c>
-      <c r="D8" s="35" t="n">
+      <c r="D8" s="4" t="n">
         <v>284917373606</v>
       </c>
-      <c r="E8" s="35" t="n">
+      <c r="E8" s="4" t="n">
         <v>231527904809</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="15">
-      <c r="A9" s="34" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Thu lãi và cổ tức</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="15">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="B9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận/(lỗ) từ hoạt động kinh doanh trước những thay đổi vốn lưu động</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="4" t="n">
         <v>1774591487670</v>
       </c>
-      <c r="C10" s="35" t="n">
+      <c r="C10" s="4" t="n">
         <v>1045881788757</v>
       </c>
-      <c r="D10" s="35" t="n">
+      <c r="D10" s="4" t="n">
         <v>176234527312</v>
       </c>
-      <c r="E10" s="35" t="n">
+      <c r="E10" s="4" t="n">
         <v>680055449918</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="15">
-      <c r="A11" s="34" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm các khoản phải thu</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="4" t="n">
         <v>-289450397420</v>
       </c>
-      <c r="C11" s="35" t="n">
+      <c r="C11" s="4" t="n">
         <v>136390770666</v>
       </c>
-      <c r="D11" s="35" t="n">
+      <c r="D11" s="4" t="n">
         <v>27356978357</v>
       </c>
-      <c r="E11" s="35" t="n">
+      <c r="E11" s="4" t="n">
         <v>-93023120614</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="15">
-      <c r="A12" s="34" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm hàng tồn kho</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="4" t="n">
         <v>-1721131354627</v>
       </c>
-      <c r="C12" s="35" t="n">
+      <c r="C12" s="4" t="n">
         <v>-1821393826979</v>
       </c>
-      <c r="D12" s="35" t="n">
+      <c r="D12" s="4" t="n">
         <v>-1944517235201</v>
       </c>
-      <c r="E12" s="35" t="n">
+      <c r="E12" s="4" t="n">
         <v>-1549588422248</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="15">
-      <c r="A13" s="34" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Tăng/(giảm) các khoản phải trả</t>
         </is>
       </c>
-      <c r="B13" s="35" t="n">
+      <c r="B13" s="4" t="n">
         <v>3488987404115</v>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="4" t="n">
         <v>1535573066662</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="4" t="n">
         <v>175960973788</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="4" t="n">
         <v>36245882912</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="15">
-      <c r="A14" s="34" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm chi phí trả trước</t>
         </is>
       </c>
-      <c r="B14" s="35" t="n">
+      <c r="B14" s="4" t="n">
         <v>1680342037</v>
       </c>
-      <c r="C14" s="35" t="n">
+      <c r="C14" s="4" t="n">
         <v>4499571232</v>
       </c>
-      <c r="D14" s="35" t="n">
+      <c r="D14" s="4" t="n">
         <v>12732185744</v>
       </c>
-      <c r="E14" s="35" t="n">
+      <c r="E14" s="4" t="n">
         <v>-226194254906</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="15">
-      <c r="A15" s="34" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Tiền lãi vay đã trả</t>
         </is>
       </c>
-      <c r="B15" s="35" t="n">
+      <c r="B15" s="4" t="n">
         <v>-393209707585</v>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="4" t="n">
         <v>-224960303416</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="4" t="n">
         <v>-301416254867</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="4" t="n">
         <v>-218989646740</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="15">
-      <c r="A16" s="34" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Thuế thu nhập doanh nghiệp đã nộp</t>
         </is>
       </c>
-      <c r="B16" s="35" t="n">
+      <c r="B16" s="4" t="n">
         <v>-114141221156</v>
       </c>
-      <c r="C16" s="35" t="n">
+      <c r="C16" s="4" t="n">
         <v>-38914311552</v>
       </c>
-      <c r="D16" s="35" t="n">
+      <c r="D16" s="4" t="n">
         <v>-111047856</v>
       </c>
-      <c r="E16" s="35" t="n">
+      <c r="E16" s="4" t="n">
         <v>-135411036538</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="15">
-      <c r="A17" s="34" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Tiền thu khác từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="15">
-      <c r="A18" s="34" t="inlineStr">
+      <c r="B17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>Tiền chi khác cho hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B18" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C18" s="35" t="n">
+      <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
         <v>-10000000000</v>
       </c>
-      <c r="D18" s="35" t="n">
+      <c r="D18" s="4" t="n">
         <v>-3344000000</v>
       </c>
-      <c r="E18" s="35" t="n">
+      <c r="E18" s="4" t="n">
         <v>-787133000</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="15">
-      <c r="A19" s="34" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền tệ ròng từ các hoạt động sản xuất kinh doanh</t>
         </is>
       </c>
-      <c r="B19" s="35" t="n">
+      <c r="B19" s="4" t="n">
         <v>2747326553034</v>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="4" t="n">
         <v>627076755370</v>
       </c>
-      <c r="D19" s="35" t="n">
+      <c r="D19" s="4" t="n">
         <v>-1857103872723</v>
       </c>
-      <c r="E19" s="35" t="n">
+      <c r="E19" s="4" t="n">
         <v>-1507692281216</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="15">
-      <c r="A20" s="34" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Tiền chi để mua sắm, xây dựng TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B20" s="35" t="n">
+      <c r="B20" s="4" t="n">
         <v>-534361131923</v>
       </c>
-      <c r="C20" s="35" t="n">
+      <c r="C20" s="4" t="n">
         <v>-489745872056</v>
       </c>
-      <c r="D20" s="35" t="n">
+      <c r="D20" s="4" t="n">
         <v>-705276095241</v>
       </c>
-      <c r="E20" s="35" t="n">
+      <c r="E20" s="4" t="n">
         <v>-518166901951</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="15">
-      <c r="A21" s="34" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Tiền thu từ thanh lý, nhượng bán TSCĐ và các tài sản dài hạn khác</t>
         </is>
       </c>
-      <c r="B21" s="35" t="n">
+      <c r="B21" s="4" t="n">
         <v>10150000</v>
       </c>
-      <c r="C21" s="35" t="n">
+      <c r="C21" s="4" t="n">
         <v>22192000</v>
       </c>
-      <c r="D21" s="35" t="n">
+      <c r="D21" s="4" t="n">
         <v>38832000</v>
       </c>
-      <c r="E21" s="35" t="n">
+      <c r="E21" s="4" t="n">
         <v>239047620</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="15">
-      <c r="A22" s="34" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>Tiền chi cho vay, mua các công cụ nợ của đơn vị khác</t>
         </is>
       </c>
-      <c r="B22" s="35" t="n">
+      <c r="B22" s="4" t="n">
         <v>-9601000000000</v>
       </c>
-      <c r="C22" s="35" t="n">
+      <c r="C22" s="4" t="n">
         <v>-2206000000000</v>
       </c>
-      <c r="D22" s="35" t="n">
+      <c r="D22" s="4" t="n">
         <v>-2551000000000</v>
       </c>
-      <c r="E22" s="35" t="n">
+      <c r="E22" s="4" t="n">
         <v>-6940000000000</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="15">
-      <c r="A23" s="34" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>Tiền thu hồi cho vay, bán lại các công cụ nợ của đơn vị khác</t>
         </is>
       </c>
-      <c r="B23" s="35" t="n">
+      <c r="B23" s="4" t="n">
         <v>4658000000000</v>
       </c>
-      <c r="C23" s="35" t="n">
+      <c r="C23" s="4" t="n">
         <v>2414000000000</v>
       </c>
-      <c r="D23" s="35" t="n">
+      <c r="D23" s="4" t="n">
         <v>2516000000000</v>
       </c>
-      <c r="E23" s="35" t="n">
+      <c r="E23" s="4" t="n">
         <v>9161500000000</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="15">
-      <c r="A24" s="34" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Tiền chi đầu tư góp vốn vào đơn vị khác</t>
         </is>
       </c>
-      <c r="B24" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="35" t="n">
+      <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>-2461794466</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="15">
-      <c r="A25" s="34" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>Tiền thu hồi đầu tư góp vốn vào đơn vị khác</t>
         </is>
       </c>
-      <c r="B25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="15">
-      <c r="A26" s="34" t="inlineStr">
+      <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Tiền thu lãi cho vay, cổ tức và lợi nhuận được chia</t>
         </is>
       </c>
-      <c r="B26" s="35" t="n">
+      <c r="B26" s="4" t="n">
         <v>213448572393</v>
       </c>
-      <c r="C26" s="35" t="n">
+      <c r="C26" s="4" t="n">
         <v>102089454700</v>
       </c>
-      <c r="D26" s="35" t="n">
+      <c r="D26" s="4" t="n">
         <v>68561151538</v>
       </c>
-      <c r="E26" s="35" t="n">
+      <c r="E26" s="4" t="n">
         <v>158973736193</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="15">
-      <c r="A27" s="34" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động đầu tư</t>
         </is>
       </c>
-      <c r="B27" s="35" t="n">
+      <c r="B27" s="4" t="n">
         <v>-5263902409530</v>
       </c>
-      <c r="C27" s="35" t="n">
+      <c r="C27" s="4" t="n">
         <v>-179634225356</v>
       </c>
-      <c r="D27" s="35" t="n">
+      <c r="D27" s="4" t="n">
         <v>-671676111703</v>
       </c>
-      <c r="E27" s="35" t="n">
+      <c r="E27" s="4" t="n">
         <v>1860084087396</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="15">
-      <c r="A28" s="34" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>Tiền thu từ phát hành cổ phiếu, nhận vốn góp của chủ sở hữu</t>
         </is>
       </c>
-      <c r="B28" s="35" t="n">
+      <c r="B28" s="4" t="n">
         <v>2037461548491</v>
       </c>
-      <c r="C28" s="35" t="n">
+      <c r="C28" s="4" t="n">
         <v>51569080000</v>
       </c>
-      <c r="D28" s="35" t="n">
+      <c r="D28" s="4" t="n">
         <v>58267830000</v>
       </c>
-      <c r="E28" s="35" t="n">
+      <c r="E28" s="4" t="n">
         <v>11478000000</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="15">
-      <c r="A29" s="34" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Tiền chi trả vốn góp cho các chủ sở hữu, mua lại cổ phiếu của doanh nghiệp đã phát hành</t>
         </is>
       </c>
-      <c r="B29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="15">
-      <c r="A30" s="34" t="inlineStr">
+      <c r="B29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Tiền thu được các khoản đi vay</t>
         </is>
       </c>
-      <c r="B30" s="35" t="n">
+      <c r="B30" s="4" t="n">
         <v>24716406311275</v>
       </c>
-      <c r="C30" s="35" t="n">
+      <c r="C30" s="4" t="n">
         <v>18698414695683</v>
       </c>
-      <c r="D30" s="35" t="n">
+      <c r="D30" s="4" t="n">
         <v>16941931226074</v>
       </c>
-      <c r="E30" s="35" t="n">
+      <c r="E30" s="4" t="n">
         <v>13421852950456</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="15">
-      <c r="A31" s="34" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
         <is>
           <t>Tiền trả nợ gốc vay</t>
         </is>
       </c>
-      <c r="B31" s="35" t="n">
+      <c r="B31" s="4" t="n">
         <v>-23465247841524</v>
       </c>
-      <c r="C31" s="35" t="n">
+      <c r="C31" s="4" t="n">
         <v>-18006336778392</v>
       </c>
-      <c r="D31" s="35" t="n">
+      <c r="D31" s="4" t="n">
         <v>-14196990842111</v>
       </c>
-      <c r="E31" s="35" t="n">
+      <c r="E31" s="4" t="n">
         <v>-14105927868424</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="15">
-      <c r="A32" s="34" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>Tiền trả nợ gốc thuê tài chính</t>
         </is>
       </c>
-      <c r="B32" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="15">
-      <c r="A33" s="34" t="inlineStr">
+      <c r="B32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Cổ tức, lợi nhuận đã trả cho chủ sở hữu</t>
         </is>
       </c>
-      <c r="B33" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" s="35" t="n">
+      <c r="B33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="n">
         <v>-54283249510</v>
       </c>
-      <c r="D33" s="35" t="n">
+      <c r="D33" s="4" t="n">
         <v>-59236267500</v>
       </c>
-      <c r="E33" s="35" t="n">
+      <c r="E33" s="4" t="n">
         <v>-39490896000</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="15">
-      <c r="A34" s="34" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Tiền lãi đã nhận</t>
         </is>
       </c>
-      <c r="B34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="15">
-      <c r="A35" s="34" t="inlineStr">
+      <c r="B34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần từ hoạt động tài chính</t>
         </is>
       </c>
-      <c r="B35" s="35" t="n">
+      <c r="B35" s="4" t="n">
         <v>3288620018242</v>
       </c>
-      <c r="C35" s="35" t="n">
+      <c r="C35" s="4" t="n">
         <v>689363747781</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="4" t="n">
         <v>2743971946463</v>
       </c>
-      <c r="E35" s="35" t="n">
+      <c r="E35" s="4" t="n">
         <v>-712087813968</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="15">
-      <c r="A36" s="34" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>Lưu chuyển tiền thuần trong kỳ</t>
         </is>
       </c>
-      <c r="B36" s="35" t="n">
+      <c r="B36" s="4" t="n">
         <v>772044161746</v>
       </c>
-      <c r="C36" s="35" t="n">
+      <c r="C36" s="4" t="n">
         <v>1136806277795</v>
       </c>
-      <c r="D36" s="35" t="n">
+      <c r="D36" s="4" t="n">
         <v>215191962037</v>
       </c>
-      <c r="E36" s="35" t="n">
+      <c r="E36" s="4" t="n">
         <v>-359696007788</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="15">
-      <c r="A37" s="34" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền đầu kỳ</t>
         </is>
       </c>
-      <c r="B37" s="35" t="n">
+      <c r="B37" s="4" t="n">
         <v>2097787236988</v>
       </c>
-      <c r="C37" s="35" t="n">
+      <c r="C37" s="4" t="n">
         <v>960822549973</v>
       </c>
-      <c r="D37" s="35" t="n">
+      <c r="D37" s="4" t="n">
         <v>745556075005</v>
       </c>
-      <c r="E37" s="35" t="n">
+      <c r="E37" s="4" t="n">
         <v>1105209549882</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="15">
-      <c r="A38" s="34" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>Ảnh hưởng của thay đổi tỷ giá hối đoái quy đổi ngoại tệ</t>
         </is>
       </c>
-      <c r="B38" s="35" t="n">
+      <c r="B38" s="4" t="n">
         <v>20360895</v>
       </c>
-      <c r="C38" s="35" t="n">
+      <c r="C38" s="4" t="n">
         <v>158409220</v>
       </c>
-      <c r="D38" s="35" t="n">
+      <c r="D38" s="4" t="n">
         <v>74512931</v>
       </c>
-      <c r="E38" s="35" t="n">
+      <c r="E38" s="4" t="n">
         <v>42532911</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="15">
-      <c r="A39" s="34" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền cuối kỳ</t>
         </is>
       </c>
-      <c r="B39" s="35" t="n">
+      <c r="B39" s="4" t="n">
         <v>2869851759629</v>
       </c>
-      <c r="C39" s="35" t="n">
+      <c r="C39" s="4" t="n">
         <v>2097787236988</v>
       </c>
-      <c r="D39" s="35" t="n">
+      <c r="D39" s="4" t="n">
         <v>960822549973</v>
       </c>
-      <c r="E39" s="35" t="n">
+      <c r="E39" s="4" t="n">
         <v>745556075005</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="15">
-      <c r="A40" s="34" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Phân bổ lợi thế thương mại</t>
         </is>
       </c>
-      <c r="B40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="15">
-      <c r="A41" s="34" t="inlineStr">
+      <c r="B40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>Các khoản điều chỉnh khác</t>
         </is>
       </c>
-      <c r="B41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="35" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="15">
-      <c r="A42" s="34" t="inlineStr">
+      <c r="B41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>(Tăng)/giảm chứng khoán kinh doanh</t>
         </is>
       </c>
-      <c r="B42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="35" t="n">
+      <c r="B42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -4321,1038 +4262,1045 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" style="15" min="1" max="1"/>
-    <col width="14" customWidth="1" style="15" min="2" max="2"/>
-    <col width="14" customWidth="1" style="15" min="3" max="3"/>
-    <col width="14" customWidth="1" style="15" min="4" max="4"/>
-    <col width="14" customWidth="1" style="15" min="5" max="5"/>
-    <col width="3" customWidth="1" style="15" min="6" max="6"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1" s="15">
-      <c r="A1" s="17" t="inlineStr">
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>CHỈ SỐ TÀI CHÍNH — FRT</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1" s="15">
-      <c r="A2" s="19" t="inlineStr">
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>I. CHỈ SỐ TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="21" t="n"/>
-      <c r="E4" s="21" t="n"/>
+      <c r="B4" s="8" t="n"/>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
+      <c r="E4" s="8" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="10">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="C5" s="23">
+      <c r="C5" s="10">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="10">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="10">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>1. Khả năng sinh lời</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="14">
         <f>IFERROR(C$54/((C$39+B$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="14">
         <f>IFERROR(D$54/((D$39+C$39)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="14">
         <f>IFERROR(E$54/((E$39+D$39)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>ROA (LNST / Tổng tài sản bình quân)</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="14">
         <f>IFERROR(C$53/((C$40+B$40)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="14">
         <f>IFERROR(D$53/((D$40+C$40)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="14">
         <f>IFERROR(E$53/((E$40+D$40)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="14">
         <f>IFERROR((C$54-B$54)/ABS(B$54),"n/a")</f>
         <v/>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="14">
         <f>IFERROR((D$54-C$54)/ABS(C$54),"n/a")</f>
         <v/>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="14">
         <f>IFERROR((E$54-D$54)/ABS(D$54),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="14">
         <f>IFERROR((C$46-B$46)/ABS(B$46),"n/a")</f>
         <v/>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="14">
         <f>IFERROR((D$46-C$46)/ABS(C$46),"n/a")</f>
         <v/>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="14">
         <f>IFERROR((E$46-D$46)/ABS(D$46),"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>2. Biên lợi nhuận</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="14">
         <f>IFERROR(B$48/B$46,"n/a")</f>
         <v/>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="14">
         <f>IFERROR(C$48/C$46,"n/a")</f>
         <v/>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="14">
         <f>IFERROR(D$48/D$46,"n/a")</f>
         <v/>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="14">
         <f>IFERROR(E$48/E$46,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
         <is>
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="14">
         <f>IFERROR(B$53/B$46,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="14">
         <f>IFERROR(C$53/C$46,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="14">
         <f>IFERROR(D$53/D$46,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="14">
         <f>IFERROR(E$53/E$46,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
         </is>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="15">
         <f>IFERROR((B$44+B$45)/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="15">
         <f>IFERROR((C$44+C$45)/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="15">
         <f>IFERROR((D$44+D$45)/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="15">
         <f>IFERROR((E$44+E$45)/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="15">
         <f>IFERROR(B$45/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="15">
         <f>IFERROR(C$45/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="15">
         <f>IFERROR(D$45/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="15">
         <f>IFERROR(E$45/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="15">
         <f>IFERROR(B$44/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="15">
         <f>IFERROR(C$44/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="15">
         <f>IFERROR(D$44/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E19" s="28">
+      <c r="E19" s="15">
         <f>IFERROR(E$44/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Nợ phải trả/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="15">
         <f>IFERROR(B$41/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="15">
         <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="15">
         <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="28">
+      <c r="E20" s="15">
         <f>IFERROR(E$41/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="15">
         <f>IFERROR(B$43/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="15">
         <f>IFERROR(C$43/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="15">
         <f>IFERROR(D$43/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="15">
         <f>IFERROR(E$43/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="15">
         <f>IFERROR(B$42/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="15">
         <f>IFERROR(C$42/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="15">
         <f>IFERROR(D$42/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E22" s="28">
+      <c r="E22" s="15">
         <f>IFERROR(E$42/E$39,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>4. Chi phí &amp; khả năng trả lãi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B25" s="27">
+      <c r="B25" s="14">
         <f>IFERROR((ABS(B$49)+ABS(B$50))/B$48,"n/a")</f>
         <v/>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="14">
         <f>IFERROR((ABS(C$49)+ABS(C$50))/C$48,"n/a")</f>
         <v/>
       </c>
-      <c r="D25" s="27">
+      <c r="D25" s="14">
         <f>IFERROR((ABS(D$49)+ABS(D$50))/D$48,"n/a")</f>
         <v/>
       </c>
-      <c r="E25" s="27">
+      <c r="E25" s="14">
         <f>IFERROR((ABS(E$49)+ABS(E$50))/E$48,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
         <is>
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B26" s="27">
+      <c r="B26" s="14">
         <f>IFERROR(ABS(B$52)/B$51,"n/a")</f>
         <v/>
       </c>
-      <c r="C26" s="27">
+      <c r="C26" s="14">
         <f>IFERROR(ABS(C$52)/C$51,"n/a")</f>
         <v/>
       </c>
-      <c r="D26" s="27">
+      <c r="D26" s="14">
         <f>IFERROR(ABS(D$52)/D$51,"n/a")</f>
         <v/>
       </c>
-      <c r="E26" s="27">
+      <c r="E26" s="14">
         <f>IFERROR(ABS(E$52)/E$51,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>5. Chu kỳ hoạt động vốn lưu động</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>Số ngày phải trả (DPO)</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="16">
         <f>IFERROR(((C$56+B$56)/2)/ABS(C$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="16">
         <f>IFERROR(((D$56+C$56)/2)/ABS(D$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="16">
         <f>IFERROR(((E$56+D$56)/2)/ABS(E$47)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Số ngày phải thu (DSO)</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="16">
         <f>IFERROR(((C$55+B$55)/2)/C$46*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="16">
         <f>IFERROR(((D$55+C$55)/2)/D$46*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="16">
         <f>IFERROR(((E$55+D$55)/2)/E$46*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>Số ngày tồn kho (DIO)</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="13" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="16">
         <f>IFERROR(((C$57+B$57)/2)/ABS(C$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="16">
         <f>IFERROR(((D$57+C$57)/2)/ABS(D$47)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="16">
         <f>IFERROR(((E$57+D$57)/2)/ABS(E$47)*365,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>6. Cơ cấu tài sản</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="14">
         <f>IFERROR(B$58/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C34" s="27">
+      <c r="C34" s="14">
         <f>IFERROR(C$58/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D34" s="27">
+      <c r="D34" s="14">
         <f>IFERROR(D$58/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E34" s="27">
+      <c r="E34" s="14">
         <f>IFERROR(E$58/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B35" s="27">
+      <c r="B35" s="14">
         <f>IFERROR(B$57/B$40,"n/a")</f>
         <v/>
       </c>
-      <c r="C35" s="27">
+      <c r="C35" s="14">
         <f>IFERROR(C$57/C$40,"n/a")</f>
         <v/>
       </c>
-      <c r="D35" s="27">
+      <c r="D35" s="14">
         <f>IFERROR(D$57/D$40,"n/a")</f>
         <v/>
       </c>
-      <c r="E35" s="27">
+      <c r="E35" s="14">
         <f>IFERROR(E$57/E$40,"n/a")</f>
         <v/>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
         </is>
       </c>
-      <c r="B37" s="21" t="n"/>
-      <c r="C37" s="21" t="n"/>
-      <c r="D37" s="21" t="n"/>
-      <c r="E37" s="21" t="n"/>
+      <c r="B37" s="8" t="n"/>
+      <c r="C37" s="8" t="n"/>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="22" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>Khoản mục</t>
         </is>
       </c>
-      <c r="B38" s="23">
+      <c r="B38" s="10">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="10">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="10">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="10">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="29" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B40" s="31">
+      <c r="B40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="31">
+      <c r="C40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="31">
+      <c r="D40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="31">
+      <c r="E40" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="3" t="inlineStr">
         <is>
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="3" t="inlineStr">
         <is>
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B43" s="31">
+      <c r="B43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B45" s="31">
+      <c r="B45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B46" s="31">
+      <c r="B46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="31">
+      <c r="C46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="31">
+      <c r="D46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="31">
+      <c r="E46" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B47" s="31">
+      <c r="B47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="31">
+      <c r="C47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="31">
+      <c r="D47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="31">
+      <c r="E47" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29" t="inlineStr">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B48" s="31">
+      <c r="B48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="31">
+      <c r="C48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="31">
+      <c r="D48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="31">
+      <c r="E48" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29" t="inlineStr">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B49" s="31">
+      <c r="B49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C49" s="31">
+      <c r="C49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D49" s="31">
+      <c r="D49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E49" s="31">
+      <c r="E49" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="29" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B52" s="31">
+      <c r="B52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C52" s="31">
+      <c r="C52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D52" s="31">
+      <c r="D52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E52" s="31">
+      <c r="E52" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="3" t="inlineStr">
         <is>
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B53" s="31">
+      <c r="B53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E53" s="31">
+      <c r="E53" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B54" s="31">
+      <c r="B54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="17">
         <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B55" s="31">
+      <c r="B55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C55" s="31">
+      <c r="C55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D55" s="31">
+      <c r="D55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E55" s="31">
+      <c r="E55" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" s="3" t="inlineStr">
         <is>
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="3" t="inlineStr">
         <is>
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B57" s="31">
+      <c r="B57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="A58" s="3" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B58" s="31">
+      <c r="B58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C58" s="31">
+      <c r="C58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D58" s="31">
+      <c r="D58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E58" s="31">
+      <c r="E58" s="17">
         <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
         <v/>
       </c>
@@ -5362,78 +5310,6 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B7:E7">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:E8">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:E9">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:E10">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:E13">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B14:E14">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17:E17">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B20:E20">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B26:E26">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/FRT/FRT_financials.xlsx
+++ b/financials/FRT/FRT_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,11 +546,11 @@
   <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,22 +561,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>9326797408285</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>11415308018413</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>14026158730456</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>21787052185671</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>14026158730456</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>11415308018413</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>9326797408285</v>
       </c>
     </row>
     <row r="3">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>745556075005</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>2097787236988</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>2869851759629</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>2097787236988</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>745556075005</v>
       </c>
     </row>
     <row r="4">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>450488205110</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>514817562060</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>475787236988</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>385251759629</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>475787236988</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>514817562060</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>450488205110</v>
       </c>
     </row>
     <row r="5">
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>295067869895</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>446004987913</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>1622000000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>2484600000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1622000000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>446004987913</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>295067869895</v>
       </c>
     </row>
     <row r="6">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>538346191905</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>394464296948</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>417127103606</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>728878339921</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>417127103606</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>394464296948</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>538346191905</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>89622537320</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>126026140388</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>176150692098</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>233091257926</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>176150692098</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>126026140388</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>89622537320</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>73767134666</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>48902780339</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>43997579646</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>94792455388</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>43997579646</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>48902780339</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>73767134666</v>
       </c>
     </row>
     <row r="12">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>342099580137</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>227411821380</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>206546170984</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>410499058289</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>206546170984</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>227411821380</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>342099580137</v>
       </c>
     </row>
     <row r="15">
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-7143060218</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-7876445159</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-9567339122</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-9504431682</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-9567339122</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-7876445159</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-7143060218</v>
       </c>
     </row>
     <row r="16">
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>6483827665529</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>8426860753034</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>10234733890772</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>11926663463990</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>10234733890772</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>8426860753034</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>6483827665529</v>
       </c>
     </row>
     <row r="17">
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>6525562245058</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>8470079480259</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>10291473307238</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>12012604661865</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>10291473307238</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>8470079480259</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>6525562245058</v>
       </c>
     </row>
     <row r="18">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-41734579529</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-43218727225</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-56739416466</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-85941197875</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-56739416466</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-43218727225</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-41734579529</v>
       </c>
     </row>
     <row r="19">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>260931923787</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>230547735063</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>252093295842</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>262782269911</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>252093295842</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>230547735063</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>260931923787</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>157021246028</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>186402495200</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>16870747637</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>47661947145</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>16870747637</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>186402495200</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>157021246028</v>
       </c>
     </row>
     <row r="22">
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>22114306031</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>22210188195</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>21546455611</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>22214405075</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>21546455611</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>22210188195</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>22114306031</v>
       </c>
     </row>
     <row r="23">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>1196999526761</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1683141884191</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1806391668645</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>1927183984705</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1806391668645</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1683141884191</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1196999526761</v>
       </c>
     </row>
     <row r="25">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>170162186921</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>179315098485</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>182805424079</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>194450060810</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>182805424079</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>179315098485</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>170162186921</v>
       </c>
     </row>
     <row r="26">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>170162186921</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>179315098485</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>182805424079</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>194450060810</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>182805424079</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>179315098485</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>170162186921</v>
       </c>
     </row>
     <row r="29">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>847269560047</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>1307637254001</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1445982801672</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>1574317843107</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1445982801672</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1307637254001</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>847269560047</v>
       </c>
     </row>
     <row r="31">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>675128050014</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1079496087742</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1156676461871</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>1196539820561</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1156676461871</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1079496087742</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>675128050014</v>
       </c>
     </row>
     <row r="32">
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>979182072742</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1608729339222</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1915183739839</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>2285328752900</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>1915183739839</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1608729339222</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>979182072742</v>
       </c>
     </row>
     <row r="33">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-304054022728</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-529233251480</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-758507277968</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-1088788932339</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-758507277968</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-529233251480</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-304054022728</v>
       </c>
     </row>
     <row r="34">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>172141510033</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>228141166259</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>289306339801</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>377778022546</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>289306339801</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>228141166259</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>172141510033</v>
       </c>
     </row>
     <row r="38">
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>183893578870</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>255220010970</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>348666597970</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>495746297007</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>348666597970</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>255220010970</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>183893578870</v>
       </c>
     </row>
     <row r="39">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>-11752068837</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-27078844711</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-59360258169</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>-117968274461</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>-59360258169</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-27078844711</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-11752068837</v>
       </c>
     </row>
     <row r="40">
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>177772171793</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>195418574905</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>169373442894</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>157004126788</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>169373442894</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>195418574905</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>177772171793</v>
       </c>
     </row>
     <row r="51">
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>177766571925</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>195418574905</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>169373442894</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>157004126788</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>169373442894</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>195418574905</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>177766571925</v>
       </c>
     </row>
     <row r="52">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>14902586</v>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>31681844</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="E52" s="4" t="n">
         <v>31681844</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>14902586</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1575,16 +1575,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>10523796935046</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>13098449902604</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>15832550399101</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>23714236170376</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>15832550399101</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>13098449902604</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>10523796935046</v>
       </c>
     </row>
     <row r="55">
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>8474461394877</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>11379279324447</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>13712736684773</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>18575165477143</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>13712736684773</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>11379279324447</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>8474461394877</v>
       </c>
     </row>
     <row r="56">
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>8474374694877</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>11378723422861</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>13712183502929</v>
+      </c>
+      <c r="E56" s="4" t="n">
         <v>18574474295299</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>13712183502929</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>11378723422861</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>8474374694877</v>
       </c>
     </row>
     <row r="57">
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>5363331144812</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>8108271528775</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>8800349446066</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>10051507915817</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>8800349446066</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>8108271528775</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>5363331144812</v>
       </c>
     </row>
     <row r="58">
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>2307356375016</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>2274331043145</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>3202439604461</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>5995965425047</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>3202439604461</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>2274331043145</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>2307356375016</v>
       </c>
     </row>
     <row r="59">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>34974952041</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>23463598041</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>37870117550</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>61615375012</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>37870117550</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>23463598041</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>34974952041</v>
       </c>
     </row>
     <row r="60">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>3120462679</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>39713137523</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>124543935725</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>244716064984</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>124543935725</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>39713137523</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>3120462679</v>
       </c>
     </row>
     <row r="61">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>535694930652</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>669094486391</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1034444152158</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>1331638783393</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>1034444152158</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>669094486391</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>535694930652</v>
       </c>
     </row>
     <row r="62">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>103346666037</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>125947493296</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>194907134412</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>281753290017</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>194907134412</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>125947493296</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>103346666037</v>
       </c>
     </row>
     <row r="63">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>112206340770</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>113315953611</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>89015814529</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>94765132430</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>89015814529</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>113315953611</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>112206340770</v>
       </c>
     </row>
     <row r="66">
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>303659660</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>2956037244</v>
+      </c>
+      <c r="E66" s="4" t="n">
         <v>5828163047</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>2956037244</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>303659660</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>14021497597</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>10677497597</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>5733824194</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>8178120854</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>5733824194</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>10677497597</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>14021497597</v>
       </c>
     </row>
     <row r="68">
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>86700000</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>555901586</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>553181844</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>691181844</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>553181844</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>555901586</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>86700000</v>
       </c>
     </row>
     <row r="69">
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>86700000</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>540999000</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>521500000</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>659500000</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>521500000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>540999000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>86700000</v>
       </c>
     </row>
     <row r="72">
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>14902586</v>
+      </c>
+      <c r="D73" s="4" t="n">
         <v>31681844</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="E73" s="4" t="n">
         <v>31681844</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>14902586</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>2049335540169</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>1719170578157</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>2119813714328</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>5139070693233</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>2119813714328</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>1719170578157</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>2049335540169</v>
       </c>
     </row>
     <row r="79">
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>2049335540169</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>1719170578157</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>2119813714328</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>5139070693233</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>2119813714328</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>1719170578157</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>2049335540169</v>
       </c>
     </row>
     <row r="80">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
-        <v>1703017850000</v>
+        <v>1184725350000</v>
       </c>
       <c r="C80" s="4" t="n">
         <v>1362423890000</v>
@@ -2078,7 +2078,7 @@
         <v>1362423890000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1184725350000</v>
+        <v>1703017850000</v>
       </c>
     </row>
     <row r="81">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>823505616594</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>236832252322</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>549386390157</v>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>2468442850502</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>549386390157</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>236832252322</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>823505616594</v>
       </c>
     </row>
     <row r="90">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
+        <v>10523796935046</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>13098449902604</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>15832550399101</v>
+      </c>
+      <c r="E95" s="4" t="n">
         <v>23714236170376</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>15832550399101</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>13098449902604</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>10523796935046</v>
       </c>
     </row>
     <row r="96">
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>0</v>
+        <v>40000000000</v>
       </c>
       <c r="C100" s="4" t="n">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>40000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
+        <v>1795608000</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>770956800</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>8230000000</v>
+      </c>
+      <c r="E104" s="4" t="n">
         <v>1411954000</v>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>8230000000</v>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>770956800</v>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>1795608000</v>
       </c>
     </row>
     <row r="105">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
+        <v>322325273</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>13605024822</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>219923436590</v>
+      </c>
+      <c r="E108" s="4" t="n">
         <v>498506024698</v>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>219923436590</v>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>13605024822</v>
-      </c>
-      <c r="E108" s="4" t="n">
-        <v>322325273</v>
       </c>
     </row>
     <row r="109">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1703017850000</v>
+        <v>1184725350000</v>
       </c>
       <c r="C116" s="4" t="n">
         <v>1362423890000</v>
@@ -2762,7 +2762,7 @@
         <v>1362423890000</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1184725350000</v>
+        <v>1703017850000</v>
       </c>
     </row>
     <row r="117">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
+        <v>437992070152</v>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>586570809094</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>236975520956</v>
+      </c>
+      <c r="E118" s="4" t="n">
         <v>197121393961</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>236975520956</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>586570809094</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>437992070152</v>
       </c>
     </row>
     <row r="119">
@@ -2810,16 +2810,16 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>385513546442</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>-349738556772</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>312410869201</v>
+      </c>
+      <c r="E119" s="4" t="n">
         <v>2271321456541</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>312410869201</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>-349738556772</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>385513546442</v>
       </c>
     </row>
     <row r="120">
@@ -2829,16 +2829,16 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
+        <v>1795608000</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>770956800</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>8230000000</v>
+      </c>
+      <c r="E120" s="4" t="n">
         <v>1411954000</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>8230000000</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>770956800</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>1795608000</v>
       </c>
     </row>
     <row r="121">
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
+        <v>41104573575</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>119914435835</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>208003434171</v>
+      </c>
+      <c r="E122" s="4" t="n">
         <v>967609992731</v>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>208003434171</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>119914435835</v>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>41104573575</v>
       </c>
     </row>
     <row r="123">
@@ -2912,11 +2912,11 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2927,22 +2927,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>30276710796279</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>31975613596365</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>40241629282059</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>51232049640567</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>40241629282059</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>31975613596365</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>30276710796279</v>
       </c>
     </row>
     <row r="3">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-110910039609</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-125963979645</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-137136750875</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>-149181195799</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-137136750875</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-125963979645</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-110910039609</v>
       </c>
     </row>
     <row r="4">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>30165800756670</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>31849649616720</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>40104492531184</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>51082868444768</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>40104492531184</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>31849649616720</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>30165800756670</v>
       </c>
     </row>
     <row r="5">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-25462623377413</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-26688006159054</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-32521431587237</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-41073163986683</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-32521431587237</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-26688006159054</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-25462623377413</v>
       </c>
     </row>
     <row r="6">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>4703177379257</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>5161643457666</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>7583060943947</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>10009704458085</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>7583060943947</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>5161643457666</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>4703177379257</v>
       </c>
     </row>
     <row r="7">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>173746497842</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>80257624527</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>106913298138</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>287764741779</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>106913298138</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80257624527</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>173746497842</v>
       </c>
     </row>
     <row r="8">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-256319530992</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-292262559450</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-253792623553</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>-388683187751</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-253792623553</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-292262559450</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-256319530992</v>
       </c>
     </row>
     <row r="9">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>-231527904809</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-284917373606</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-253428831252</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>-388595922369</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-253428831252</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-284917373606</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-231527904809</v>
       </c>
     </row>
     <row r="10">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-3259297597681</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-4169668799072</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-5527210989725</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-7018206246026</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-5527210989725</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-4169668799072</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-3259297597681</v>
       </c>
     </row>
     <row r="11">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-887338884656</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-1076478805719</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-1365833850070</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-1677744619772</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-1365833850070</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-1076478805719</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-887338884656</v>
       </c>
     </row>
     <row r="12">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>473967863770</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-296509082048</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>543136778737</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>1212835146315</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>543136778737</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-296509082048</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>473967863770</v>
       </c>
     </row>
     <row r="13">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>16254109001</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>22062244997</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>24090237620</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>29912692698</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>24090237620</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>22062244997</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>16254109001</v>
       </c>
     </row>
     <row r="14">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-4598558802</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-19734846239</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-40269928171</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-23630336340</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-40269928171</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-19734846239</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-4598558802</v>
       </c>
     </row>
     <row r="15">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>11655550199</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>2327398758</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-16179690551</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>6282356358</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-16179690551</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>2327398758</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>11655550199</v>
       </c>
     </row>
     <row r="16">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>485623413969</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-294181683290</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>526957088186</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>1219117502673</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>526957088186</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>-294181683290</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>485623413969</v>
       </c>
     </row>
     <row r="18">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-86686691655</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-34994338768</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-118526676650</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-234877775599</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-118526676650</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-34994338768</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-86686691655</v>
       </c>
     </row>
     <row r="19">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>0</v>
+        <v>-862524906</v>
       </c>
       <c r="C19" s="4" t="n">
+        <v>-20502454</v>
+      </c>
+      <c r="D19" s="4" t="n">
         <v>-16779258</v>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>-20502454</v>
-      </c>
       <c r="E19" s="4" t="n">
-        <v>-862524906</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-87549216561</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-35014841222</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-118543455908</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-234877775599</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-118543455908</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-35014841222</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-87549216561</v>
       </c>
     </row>
     <row r="21">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>398074197408</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-329196524512</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>408413632278</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>984239727074</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>408413632278</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>-329196524512</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>398074197408</v>
       </c>
     </row>
     <row r="22">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>7713342831</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>16446964816</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>90897366661</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>189374783523</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>90897366661</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>16446964816</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>7713342831</v>
       </c>
     </row>
     <row r="23">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>390360854577</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>-345643489328</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>317516265617</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>794864943551</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>317516265617</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>-345643489328</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>390360854577</v>
       </c>
     </row>
     <row r="24">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>2865</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>2293</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>4653</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>2293</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-2537</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>2865</v>
       </c>
     </row>
     <row r="25">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>2865</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>2293</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>4653</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>2293</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>-2537</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>2865</v>
       </c>
     </row>
     <row r="26">
@@ -3435,11 +3435,11 @@
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="89" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3450,22 +3450,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>485623413969</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>-294181683290</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>526957088186</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>1219117502673</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>526957088186</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>-294181683290</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>485623413969</v>
       </c>
     </row>
     <row r="3">
@@ -3495,16 +3495,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>115286135177</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>233071988505</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>318442950010</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>402557018224</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>318442950010</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>233071988505</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>115286135177</v>
       </c>
     </row>
     <row r="4">
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>-4485565669</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2521192297</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>17863960788</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>32010999772</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>17863960788</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2521192297</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>-4485565669</v>
       </c>
     </row>
     <row r="5">
@@ -3533,16 +3533,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-42532911</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-74512931</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-158409220</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-20360895</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-158409220</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-74512931</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-42532911</v>
       </c>
     </row>
     <row r="6">
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-147853905457</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-50019830875</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-70652632259</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-267669594473</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-70652632259</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-50019830875</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-147853905457</v>
       </c>
     </row>
     <row r="8">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>231527904809</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>284917373606</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>253428831252</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>388595922369</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>253428831252</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>284917373606</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>231527904809</v>
       </c>
     </row>
     <row r="9">
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>680055449918</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>176234527312</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>1045881788757</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>1774591487670</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1045881788757</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>176234527312</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>680055449918</v>
       </c>
     </row>
     <row r="11">
@@ -3647,16 +3647,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-93023120614</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>27356978357</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>136390770666</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-289450397420</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>136390770666</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>27356978357</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-93023120614</v>
       </c>
     </row>
     <row r="12">
@@ -3666,16 +3666,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-1549588422248</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-1944517235201</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-1821393826979</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-1721131354627</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-1821393826979</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-1944517235201</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-1549588422248</v>
       </c>
     </row>
     <row r="13">
@@ -3685,16 +3685,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>36245882912</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>175960973788</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>1535573066662</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>3488987404115</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1535573066662</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>175960973788</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>36245882912</v>
       </c>
     </row>
     <row r="14">
@@ -3704,16 +3704,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-226194254906</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>12732185744</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>4499571232</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>1680342037</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>4499571232</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>12732185744</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-226194254906</v>
       </c>
     </row>
     <row r="15">
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-218989646740</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-301416254867</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-224960303416</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-393209707585</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-224960303416</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-301416254867</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-218989646740</v>
       </c>
     </row>
     <row r="16">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>-135411036538</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-111047856</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-38914311552</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>-114141221156</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>-38914311552</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-111047856</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-135411036538</v>
       </c>
     </row>
     <row r="17">
@@ -3780,16 +3780,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0</v>
+        <v>-787133000</v>
       </c>
       <c r="C18" s="4" t="n">
+        <v>-3344000000</v>
+      </c>
+      <c r="D18" s="4" t="n">
         <v>-10000000000</v>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>-3344000000</v>
-      </c>
       <c r="E18" s="4" t="n">
-        <v>-787133000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>-1507692281216</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-1857103872723</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>627076755370</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>2747326553034</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>627076755370</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-1857103872723</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-1507692281216</v>
       </c>
     </row>
     <row r="20">
@@ -3818,16 +3818,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-518166901951</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-705276095241</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-489745872056</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-534361131923</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-489745872056</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-705276095241</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-518166901951</v>
       </c>
     </row>
     <row r="21">
@@ -3837,16 +3837,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>239047620</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>38832000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>22192000</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>10150000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>22192000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>38832000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>239047620</v>
       </c>
     </row>
     <row r="22">
@@ -3856,16 +3856,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-6940000000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-2551000000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-2206000000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>-9601000000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-2206000000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-2551000000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-6940000000000</v>
       </c>
     </row>
     <row r="23">
@@ -3875,16 +3875,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>9161500000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2516000000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>2414000000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>4658000000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>2414000000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>2516000000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>9161500000000</v>
       </c>
     </row>
     <row r="24">
@@ -3894,7 +3894,7 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>0</v>
+        <v>-2461794466</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0</v>
@@ -3903,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-2461794466</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>158973736193</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>68561151538</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>102089454700</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>213448572393</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>102089454700</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>68561151538</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>158973736193</v>
       </c>
     </row>
     <row r="27">
@@ -3951,16 +3951,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>1860084087396</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-671676111703</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-179634225356</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>-5263902409530</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-179634225356</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-671676111703</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1860084087396</v>
       </c>
     </row>
     <row r="28">
@@ -3970,16 +3970,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>11478000000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>58267830000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>51569080000</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>2037461548491</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>51569080000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>58267830000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>11478000000</v>
       </c>
     </row>
     <row r="29">
@@ -4008,16 +4008,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>13421852950456</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>16941931226074</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>18698414695683</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>24716406311275</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>18698414695683</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>16941931226074</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>13421852950456</v>
       </c>
     </row>
     <row r="31">
@@ -4027,16 +4027,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>-14105927868424</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-14196990842111</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-18006336778392</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>-23465247841524</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-18006336778392</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-14196990842111</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-14105927868424</v>
       </c>
     </row>
     <row r="32">
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>0</v>
+        <v>-39490896000</v>
       </c>
       <c r="C33" s="4" t="n">
+        <v>-59236267500</v>
+      </c>
+      <c r="D33" s="4" t="n">
         <v>-54283249510</v>
       </c>
-      <c r="D33" s="4" t="n">
-        <v>-59236267500</v>
-      </c>
       <c r="E33" s="4" t="n">
-        <v>-39490896000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>-712087813968</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>2743971946463</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>689363747781</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>3288620018242</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>689363747781</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>2743971946463</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-712087813968</v>
       </c>
     </row>
     <row r="36">
@@ -4122,16 +4122,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>-359696007788</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>215191962037</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>1136806277795</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>772044161746</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>1136806277795</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>215191962037</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>-359696007788</v>
       </c>
     </row>
     <row r="37">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>1105209549882</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>745556075005</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>2097787236988</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>745556075005</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>1105209549882</v>
       </c>
     </row>
     <row r="38">
@@ -4160,16 +4160,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>42532911</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>74512931</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>158409220</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>20360895</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>158409220</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>74512931</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>42532911</v>
       </c>
     </row>
     <row r="39">
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>745556075005</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>2097787236988</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>2869851759629</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>2097787236988</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>745556075005</v>
       </c>
     </row>
     <row r="40">
@@ -4262,11 +4262,11 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4277,12 +4277,8 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="6" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
@@ -4303,19 +4299,19 @@
         </is>
       </c>
       <c r="B5" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C5" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D5" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E5" s="10">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>
@@ -4829,19 +4825,19 @@
         </is>
       </c>
       <c r="B38" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C38" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D38" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E38" s="10">
         <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C38" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D38" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>'balance_sheet'!B1</f>
         <v/>
       </c>
     </row>

--- a/financials/FRT/FRT_financials.xlsx
+++ b/financials/FRT/FRT_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,11 +546,11 @@
   <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,22 +561,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -587,16 +587,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>21787052185671</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>14026158730456</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>11415308018413</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>9326797408285</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>11415308018413</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>14026158730456</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>21787052185671</v>
       </c>
     </row>
     <row r="3">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>2869851759629</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>2097787236988</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>745556075005</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>2097787236988</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>2869851759629</v>
       </c>
     </row>
     <row r="4">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>385251759629</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>475787236988</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>514817562060</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>450488205110</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>514817562060</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>475787236988</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>385251759629</v>
       </c>
     </row>
     <row r="5">
@@ -644,16 +644,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>2484600000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1622000000000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>446004987913</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>295067869895</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>446004987913</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1622000000000</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>2484600000000</v>
       </c>
     </row>
     <row r="6">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>728878339921</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>417127103606</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>394464296948</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>538346191905</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>394464296948</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>417127103606</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>728878339921</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>233091257926</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>176150692098</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>126026140388</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>89622537320</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>126026140388</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>176150692098</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>233091257926</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +758,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>94792455388</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>43997579646</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>48902780339</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>73767134666</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>48902780339</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>43997579646</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>94792455388</v>
       </c>
     </row>
     <row r="12">
@@ -815,16 +815,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>410499058289</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>206546170984</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>227411821380</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>342099580137</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>227411821380</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>206546170984</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>410499058289</v>
       </c>
     </row>
     <row r="15">
@@ -834,16 +834,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-9504431682</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-9567339122</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-7876445159</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-7143060218</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-7876445159</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-9567339122</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-9504431682</v>
       </c>
     </row>
     <row r="16">
@@ -853,16 +853,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>11926663463990</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>10234733890772</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>8426860753034</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>6483827665529</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>8426860753034</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>10234733890772</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>11926663463990</v>
       </c>
     </row>
     <row r="17">
@@ -872,16 +872,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>12012604661865</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>10291473307238</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>8470079480259</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>6525562245058</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>8470079480259</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>10291473307238</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>12012604661865</v>
       </c>
     </row>
     <row r="18">
@@ -891,16 +891,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-85941197875</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-56739416466</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-43218727225</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-41734579529</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-43218727225</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-56739416466</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-85941197875</v>
       </c>
     </row>
     <row r="19">
@@ -929,16 +929,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>262782269911</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>252093295842</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>230547735063</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>260931923787</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>230547735063</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>252093295842</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>262782269911</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +948,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>47661947145</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>16870747637</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>186402495200</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>157021246028</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>186402495200</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>16870747637</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>47661947145</v>
       </c>
     </row>
     <row r="22">
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>22214405075</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>21546455611</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>22210188195</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>22114306031</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>22210188195</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>21546455611</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>22214405075</v>
       </c>
     </row>
     <row r="23">
@@ -1005,16 +1005,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>1927183984705</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>1806391668645</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>1683141884191</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>1196999526761</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1683141884191</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1806391668645</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1927183984705</v>
       </c>
     </row>
     <row r="25">
@@ -1024,16 +1024,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>194450060810</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>182805424079</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>179315098485</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>170162186921</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>179315098485</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>182805424079</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>194450060810</v>
       </c>
     </row>
     <row r="26">
@@ -1081,16 +1081,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>194450060810</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>182805424079</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>179315098485</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>170162186921</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>179315098485</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>182805424079</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>194450060810</v>
       </c>
     </row>
     <row r="29">
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>1574317843107</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>1445982801672</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>1307637254001</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>847269560047</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1307637254001</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1445982801672</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>1574317843107</v>
       </c>
     </row>
     <row r="31">
@@ -1138,16 +1138,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>1196539820561</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>1156676461871</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>1079496087742</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>675128050014</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1079496087742</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1156676461871</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>1196539820561</v>
       </c>
     </row>
     <row r="32">
@@ -1157,16 +1157,16 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>2285328752900</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1915183739839</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1608729339222</v>
+      </c>
+      <c r="E32" s="4" t="n">
         <v>979182072742</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>1608729339222</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1915183739839</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>2285328752900</v>
       </c>
     </row>
     <row r="33">
@@ -1176,16 +1176,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-1088788932339</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-758507277968</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-529233251480</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-304054022728</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-529233251480</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-758507277968</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-1088788932339</v>
       </c>
     </row>
     <row r="34">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>377778022546</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>289306339801</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>228141166259</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>172141510033</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>228141166259</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>289306339801</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>377778022546</v>
       </c>
     </row>
     <row r="38">
@@ -1271,16 +1271,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>495746297007</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>348666597970</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>255220010970</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>183893578870</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>255220010970</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>348666597970</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>495746297007</v>
       </c>
     </row>
     <row r="39">
@@ -1290,16 +1290,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>-117968274461</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-59360258169</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-27078844711</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>-11752068837</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>-27078844711</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-59360258169</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-117968274461</v>
       </c>
     </row>
     <row r="40">
@@ -1499,16 +1499,16 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>157004126788</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>169373442894</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>195418574905</v>
+      </c>
+      <c r="E50" s="4" t="n">
         <v>177772171793</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>195418574905</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>169373442894</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>157004126788</v>
       </c>
     </row>
     <row r="51">
@@ -1518,16 +1518,16 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>157004126788</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>169373442894</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>195418574905</v>
+      </c>
+      <c r="E51" s="4" t="n">
         <v>177766571925</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>195418574905</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>169373442894</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>157004126788</v>
       </c>
     </row>
     <row r="52">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>0</v>
+        <v>31681844</v>
       </c>
       <c r="C52" s="4" t="n">
+        <v>31681844</v>
+      </c>
+      <c r="D52" s="4" t="n">
         <v>14902586</v>
       </c>
-      <c r="D52" s="4" t="n">
-        <v>31681844</v>
-      </c>
       <c r="E52" s="4" t="n">
-        <v>31681844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1575,16 +1575,16 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>23714236170376</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>15832550399101</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>13098449902604</v>
+      </c>
+      <c r="E54" s="4" t="n">
         <v>10523796935046</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>13098449902604</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>15832550399101</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>23714236170376</v>
       </c>
     </row>
     <row r="55">
@@ -1594,16 +1594,16 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>18575165477143</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>13712736684773</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>11379279324447</v>
+      </c>
+      <c r="E55" s="4" t="n">
         <v>8474461394877</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>11379279324447</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>13712736684773</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>18575165477143</v>
       </c>
     </row>
     <row r="56">
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>18574474295299</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>13712183502929</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>11378723422861</v>
+      </c>
+      <c r="E56" s="4" t="n">
         <v>8474374694877</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>11378723422861</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>13712183502929</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>18574474295299</v>
       </c>
     </row>
     <row r="57">
@@ -1632,16 +1632,16 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>10051507915817</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>8800349446066</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>8108271528775</v>
+      </c>
+      <c r="E57" s="4" t="n">
         <v>5363331144812</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>8108271528775</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>8800349446066</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>10051507915817</v>
       </c>
     </row>
     <row r="58">
@@ -1651,16 +1651,16 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>5995965425047</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>3202439604461</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>2274331043145</v>
+      </c>
+      <c r="E58" s="4" t="n">
         <v>2307356375016</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>2274331043145</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>3202439604461</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>5995965425047</v>
       </c>
     </row>
     <row r="59">
@@ -1670,16 +1670,16 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>61615375012</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>37870117550</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>23463598041</v>
+      </c>
+      <c r="E59" s="4" t="n">
         <v>34974952041</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>23463598041</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>37870117550</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>61615375012</v>
       </c>
     </row>
     <row r="60">
@@ -1689,16 +1689,16 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>244716064984</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>124543935725</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>39713137523</v>
+      </c>
+      <c r="E60" s="4" t="n">
         <v>3120462679</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>39713137523</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>124543935725</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>244716064984</v>
       </c>
     </row>
     <row r="61">
@@ -1708,16 +1708,16 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>1331638783393</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>1034444152158</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>669094486391</v>
+      </c>
+      <c r="E61" s="4" t="n">
         <v>535694930652</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>669094486391</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>1034444152158</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>1331638783393</v>
       </c>
     </row>
     <row r="62">
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>281753290017</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>194907134412</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>125947493296</v>
+      </c>
+      <c r="E62" s="4" t="n">
         <v>103346666037</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>125947493296</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>194907134412</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>281753290017</v>
       </c>
     </row>
     <row r="63">
@@ -1784,16 +1784,16 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>94765132430</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>89015814529</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>113315953611</v>
+      </c>
+      <c r="E65" s="4" t="n">
         <v>112206340770</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>113315953611</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>89015814529</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>94765132430</v>
       </c>
     </row>
     <row r="66">
@@ -1803,16 +1803,16 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
-        <v>0</v>
+        <v>5828163047</v>
       </c>
       <c r="C66" s="4" t="n">
+        <v>2956037244</v>
+      </c>
+      <c r="D66" s="4" t="n">
         <v>303659660</v>
       </c>
-      <c r="D66" s="4" t="n">
-        <v>2956037244</v>
-      </c>
       <c r="E66" s="4" t="n">
-        <v>5828163047</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1822,16 +1822,16 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>8178120854</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>5733824194</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>10677497597</v>
+      </c>
+      <c r="E67" s="4" t="n">
         <v>14021497597</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>10677497597</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>5733824194</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>8178120854</v>
       </c>
     </row>
     <row r="68">
@@ -1841,16 +1841,16 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
+        <v>691181844</v>
+      </c>
+      <c r="C68" s="4" t="n">
+        <v>553181844</v>
+      </c>
+      <c r="D68" s="4" t="n">
+        <v>555901586</v>
+      </c>
+      <c r="E68" s="4" t="n">
         <v>86700000</v>
-      </c>
-      <c r="C68" s="4" t="n">
-        <v>555901586</v>
-      </c>
-      <c r="D68" s="4" t="n">
-        <v>553181844</v>
-      </c>
-      <c r="E68" s="4" t="n">
-        <v>691181844</v>
       </c>
     </row>
     <row r="69">
@@ -1898,16 +1898,16 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
+        <v>659500000</v>
+      </c>
+      <c r="C71" s="4" t="n">
+        <v>521500000</v>
+      </c>
+      <c r="D71" s="4" t="n">
+        <v>540999000</v>
+      </c>
+      <c r="E71" s="4" t="n">
         <v>86700000</v>
-      </c>
-      <c r="C71" s="4" t="n">
-        <v>540999000</v>
-      </c>
-      <c r="D71" s="4" t="n">
-        <v>521500000</v>
-      </c>
-      <c r="E71" s="4" t="n">
-        <v>659500000</v>
       </c>
     </row>
     <row r="72">
@@ -1936,16 +1936,16 @@
         </is>
       </c>
       <c r="B73" s="4" t="n">
-        <v>0</v>
+        <v>31681844</v>
       </c>
       <c r="C73" s="4" t="n">
+        <v>31681844</v>
+      </c>
+      <c r="D73" s="4" t="n">
         <v>14902586</v>
       </c>
-      <c r="D73" s="4" t="n">
-        <v>31681844</v>
-      </c>
       <c r="E73" s="4" t="n">
-        <v>31681844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2031,16 +2031,16 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>5139070693233</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>2119813714328</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>1719170578157</v>
+      </c>
+      <c r="E78" s="4" t="n">
         <v>2049335540169</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>1719170578157</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>2119813714328</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>5139070693233</v>
       </c>
     </row>
     <row r="79">
@@ -2050,16 +2050,16 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>5139070693233</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>2119813714328</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>1719170578157</v>
+      </c>
+      <c r="E79" s="4" t="n">
         <v>2049335540169</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>1719170578157</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>2119813714328</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>5139070693233</v>
       </c>
     </row>
     <row r="80">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
-        <v>1184725350000</v>
+        <v>1703017850000</v>
       </c>
       <c r="C80" s="4" t="n">
         <v>1362423890000</v>
@@ -2078,7 +2078,7 @@
         <v>1362423890000</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1703017850000</v>
+        <v>1184725350000</v>
       </c>
     </row>
     <row r="81">
@@ -2240,16 +2240,16 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>2468442850502</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>549386390157</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>236832252322</v>
+      </c>
+      <c r="E89" s="4" t="n">
         <v>823505616594</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>236832252322</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>549386390157</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>2468442850502</v>
       </c>
     </row>
     <row r="90">
@@ -2354,16 +2354,16 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
+        <v>23714236170376</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>15832550399101</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>13098449902604</v>
+      </c>
+      <c r="E95" s="4" t="n">
         <v>10523796935046</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>13098449902604</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>15832550399101</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>23714236170376</v>
       </c>
     </row>
     <row r="96">
@@ -2449,16 +2449,16 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="4" t="n">
         <v>40000000000</v>
-      </c>
-      <c r="C100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2525,16 +2525,16 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
+        <v>1411954000</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>8230000000</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>770956800</v>
+      </c>
+      <c r="E104" s="4" t="n">
         <v>1795608000</v>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>770956800</v>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>8230000000</v>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>1411954000</v>
       </c>
     </row>
     <row r="105">
@@ -2601,16 +2601,16 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
+        <v>498506024698</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>219923436590</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>13605024822</v>
+      </c>
+      <c r="E108" s="4" t="n">
         <v>322325273</v>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>13605024822</v>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>219923436590</v>
-      </c>
-      <c r="E108" s="4" t="n">
-        <v>498506024698</v>
       </c>
     </row>
     <row r="109">
@@ -2753,7 +2753,7 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
-        <v>1184725350000</v>
+        <v>1703017850000</v>
       </c>
       <c r="C116" s="4" t="n">
         <v>1362423890000</v>
@@ -2762,7 +2762,7 @@
         <v>1362423890000</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>1703017850000</v>
+        <v>1184725350000</v>
       </c>
     </row>
     <row r="117">
@@ -2791,16 +2791,16 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
+        <v>197121393961</v>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>236975520956</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>586570809094</v>
+      </c>
+      <c r="E118" s="4" t="n">
         <v>437992070152</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>586570809094</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>236975520956</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>197121393961</v>
       </c>
     </row>
     <row r="119">
@@ -2810,16 +2810,16 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>2271321456541</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>312410869201</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>-349738556772</v>
+      </c>
+      <c r="E119" s="4" t="n">
         <v>385513546442</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>-349738556772</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>312410869201</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>2271321456541</v>
       </c>
     </row>
     <row r="120">
@@ -2829,16 +2829,16 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
+        <v>1411954000</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>8230000000</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>770956800</v>
+      </c>
+      <c r="E120" s="4" t="n">
         <v>1795608000</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>770956800</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>8230000000</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>1411954000</v>
       </c>
     </row>
     <row r="121">
@@ -2867,16 +2867,16 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
+        <v>967609992731</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>208003434171</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>119914435835</v>
+      </c>
+      <c r="E122" s="4" t="n">
         <v>41104573575</v>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>119914435835</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>208003434171</v>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>967609992731</v>
       </c>
     </row>
     <row r="123">
@@ -2912,11 +2912,11 @@
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2927,22 +2927,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>51232049640567</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>40241629282059</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>31975613596365</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>30276710796279</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>31975613596365</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>40241629282059</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>51232049640567</v>
       </c>
     </row>
     <row r="3">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-149181195799</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-137136750875</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-125963979645</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>-110910039609</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-125963979645</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-137136750875</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-149181195799</v>
       </c>
     </row>
     <row r="4">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>51082868444768</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>40104492531184</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>31849649616720</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>30165800756670</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>31849649616720</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>40104492531184</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>51082868444768</v>
       </c>
     </row>
     <row r="5">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-41073163986683</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-32521431587237</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-26688006159054</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-25462623377413</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-26688006159054</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-32521431587237</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-41073163986683</v>
       </c>
     </row>
     <row r="6">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>10009704458085</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>7583060943947</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>5161643457666</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>4703177379257</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>5161643457666</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>7583060943947</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>10009704458085</v>
       </c>
     </row>
     <row r="7">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>287764741779</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>106913298138</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>80257624527</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>173746497842</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>80257624527</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>106913298138</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>287764741779</v>
       </c>
     </row>
     <row r="8">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-388683187751</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-253792623553</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-292262559450</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>-256319530992</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-292262559450</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-253792623553</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-388683187751</v>
       </c>
     </row>
     <row r="9">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>-388595922369</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-253428831252</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-284917373606</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>-231527904809</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-284917373606</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-253428831252</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-388595922369</v>
       </c>
     </row>
     <row r="10">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-7018206246026</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-5527210989725</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-4169668799072</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>-3259297597681</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-4169668799072</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-5527210989725</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-7018206246026</v>
       </c>
     </row>
     <row r="11">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-1677744619772</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-1365833850070</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-1076478805719</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-887338884656</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-1076478805719</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-1365833850070</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-1677744619772</v>
       </c>
     </row>
     <row r="12">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>1212835146315</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>543136778737</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-296509082048</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>473967863770</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-296509082048</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>543136778737</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>1212835146315</v>
       </c>
     </row>
     <row r="13">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>29912692698</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>24090237620</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>22062244997</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>16254109001</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>22062244997</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>24090237620</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>29912692698</v>
       </c>
     </row>
     <row r="14">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-23630336340</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-40269928171</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-19734846239</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-4598558802</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-19734846239</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-40269928171</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-23630336340</v>
       </c>
     </row>
     <row r="15">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>6282356358</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-16179690551</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>2327398758</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>11655550199</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>2327398758</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-16179690551</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>6282356358</v>
       </c>
     </row>
     <row r="16">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>1219117502673</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>526957088186</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>-294181683290</v>
+      </c>
+      <c r="E17" s="4" t="n">
         <v>485623413969</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>-294181683290</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>526957088186</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>1219117502673</v>
       </c>
     </row>
     <row r="18">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-234877775599</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-118526676650</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-34994338768</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-86686691655</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-34994338768</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-118526676650</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-234877775599</v>
       </c>
     </row>
     <row r="19">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-16779258</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-20502454</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>-862524906</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-20502454</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-16779258</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-234877775599</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-118543455908</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-35014841222</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-87549216561</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-35014841222</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-118543455908</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-234877775599</v>
       </c>
     </row>
     <row r="21">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>984239727074</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>408413632278</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-329196524512</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>398074197408</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>-329196524512</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>408413632278</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>984239727074</v>
       </c>
     </row>
     <row r="22">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>189374783523</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>90897366661</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>16446964816</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>7713342831</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>16446964816</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>90897366661</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>189374783523</v>
       </c>
     </row>
     <row r="23">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>794864943551</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>317516265617</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>-345643489328</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>390360854577</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>-345643489328</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>317516265617</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>794864943551</v>
       </c>
     </row>
     <row r="24">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>4653</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>2293</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>2865</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>-2537</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>2293</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>4653</v>
       </c>
     </row>
     <row r="25">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>4653</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>2293</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="E25" s="4" t="n">
         <v>2865</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>-2537</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>2293</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>4653</v>
       </c>
     </row>
     <row r="26">
@@ -3435,11 +3435,11 @@
   <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="89" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3450,22 +3450,22 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>2022</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2025</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>1219117502673</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>526957088186</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>-294181683290</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>485623413969</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>-294181683290</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>526957088186</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>1219117502673</v>
       </c>
     </row>
     <row r="3">
@@ -3495,16 +3495,16 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>402557018224</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>318442950010</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>233071988505</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>115286135177</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>233071988505</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>318442950010</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>402557018224</v>
       </c>
     </row>
     <row r="4">
@@ -3514,16 +3514,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>32010999772</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>17863960788</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>2521192297</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>-4485565669</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2521192297</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>17863960788</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>32010999772</v>
       </c>
     </row>
     <row r="5">
@@ -3533,16 +3533,16 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-20360895</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-158409220</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-74512931</v>
+      </c>
+      <c r="E5" s="4" t="n">
         <v>-42532911</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-74512931</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-158409220</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-20360895</v>
       </c>
     </row>
     <row r="6">
@@ -3571,16 +3571,16 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-267669594473</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-70652632259</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-50019830875</v>
+      </c>
+      <c r="E7" s="4" t="n">
         <v>-147853905457</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-50019830875</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-70652632259</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-267669594473</v>
       </c>
     </row>
     <row r="8">
@@ -3590,16 +3590,16 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>388595922369</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>253428831252</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>284917373606</v>
+      </c>
+      <c r="E8" s="4" t="n">
         <v>231527904809</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>284917373606</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>253428831252</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>388595922369</v>
       </c>
     </row>
     <row r="9">
@@ -3628,16 +3628,16 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>1774591487670</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>1045881788757</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>176234527312</v>
+      </c>
+      <c r="E10" s="4" t="n">
         <v>680055449918</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>176234527312</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>1045881788757</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1774591487670</v>
       </c>
     </row>
     <row r="11">
@@ -3647,16 +3647,16 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-289450397420</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>136390770666</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>27356978357</v>
+      </c>
+      <c r="E11" s="4" t="n">
         <v>-93023120614</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>27356978357</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>136390770666</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-289450397420</v>
       </c>
     </row>
     <row r="12">
@@ -3666,16 +3666,16 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-1721131354627</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-1821393826979</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-1944517235201</v>
+      </c>
+      <c r="E12" s="4" t="n">
         <v>-1549588422248</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-1944517235201</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-1821393826979</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-1721131354627</v>
       </c>
     </row>
     <row r="13">
@@ -3685,16 +3685,16 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>3488987404115</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>1535573066662</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>175960973788</v>
+      </c>
+      <c r="E13" s="4" t="n">
         <v>36245882912</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>175960973788</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>1535573066662</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>3488987404115</v>
       </c>
     </row>
     <row r="14">
@@ -3704,16 +3704,16 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>1680342037</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>4499571232</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>12732185744</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>-226194254906</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>12732185744</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>4499571232</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>1680342037</v>
       </c>
     </row>
     <row r="15">
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-393209707585</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-224960303416</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-301416254867</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>-218989646740</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-301416254867</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-224960303416</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-393209707585</v>
       </c>
     </row>
     <row r="16">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>-114141221156</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-38914311552</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-111047856</v>
+      </c>
+      <c r="E16" s="4" t="n">
         <v>-135411036538</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>-111047856</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-38914311552</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-114141221156</v>
       </c>
     </row>
     <row r="17">
@@ -3780,16 +3780,16 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-10000000000</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-3344000000</v>
+      </c>
+      <c r="E18" s="4" t="n">
         <v>-787133000</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-3344000000</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-10000000000</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3799,16 +3799,16 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>2747326553034</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>627076755370</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>-1857103872723</v>
+      </c>
+      <c r="E19" s="4" t="n">
         <v>-1507692281216</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>-1857103872723</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>627076755370</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>2747326553034</v>
       </c>
     </row>
     <row r="20">
@@ -3818,16 +3818,16 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-534361131923</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-489745872056</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-705276095241</v>
+      </c>
+      <c r="E20" s="4" t="n">
         <v>-518166901951</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-705276095241</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-489745872056</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-534361131923</v>
       </c>
     </row>
     <row r="21">
@@ -3837,16 +3837,16 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>10150000</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>22192000</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>38832000</v>
+      </c>
+      <c r="E21" s="4" t="n">
         <v>239047620</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>38832000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>22192000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>10150000</v>
       </c>
     </row>
     <row r="22">
@@ -3856,16 +3856,16 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-9601000000000</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-2206000000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-2551000000000</v>
+      </c>
+      <c r="E22" s="4" t="n">
         <v>-6940000000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-2551000000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-2206000000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-9601000000000</v>
       </c>
     </row>
     <row r="23">
@@ -3875,16 +3875,16 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>4658000000000</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>2414000000000</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>2516000000000</v>
+      </c>
+      <c r="E23" s="4" t="n">
         <v>9161500000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>2516000000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>2414000000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>4658000000000</v>
       </c>
     </row>
     <row r="24">
@@ -3894,16 +3894,16 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="4" t="n">
         <v>-2461794466</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3932,16 +3932,16 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>213448572393</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>102089454700</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>68561151538</v>
+      </c>
+      <c r="E26" s="4" t="n">
         <v>158973736193</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>68561151538</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>102089454700</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>213448572393</v>
       </c>
     </row>
     <row r="27">
@@ -3951,16 +3951,16 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-5263902409530</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-179634225356</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-671676111703</v>
+      </c>
+      <c r="E27" s="4" t="n">
         <v>1860084087396</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-671676111703</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-179634225356</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>-5263902409530</v>
       </c>
     </row>
     <row r="28">
@@ -3970,16 +3970,16 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>2037461548491</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>51569080000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>58267830000</v>
+      </c>
+      <c r="E28" s="4" t="n">
         <v>11478000000</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>58267830000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>51569080000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>2037461548491</v>
       </c>
     </row>
     <row r="29">
@@ -4008,16 +4008,16 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>24716406311275</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>18698414695683</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>16941931226074</v>
+      </c>
+      <c r="E30" s="4" t="n">
         <v>13421852950456</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>16941931226074</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>18698414695683</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>24716406311275</v>
       </c>
     </row>
     <row r="31">
@@ -4027,16 +4027,16 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>-23465247841524</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-18006336778392</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-14196990842111</v>
+      </c>
+      <c r="E31" s="4" t="n">
         <v>-14105927868424</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-14196990842111</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-18006336778392</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-23465247841524</v>
       </c>
     </row>
     <row r="32">
@@ -4065,16 +4065,16 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-54283249510</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-59236267500</v>
+      </c>
+      <c r="E33" s="4" t="n">
         <v>-39490896000</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-59236267500</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-54283249510</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4103,16 +4103,16 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>3288620018242</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>689363747781</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>2743971946463</v>
+      </c>
+      <c r="E35" s="4" t="n">
         <v>-712087813968</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>2743971946463</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>689363747781</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>3288620018242</v>
       </c>
     </row>
     <row r="36">
@@ -4122,16 +4122,16 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>772044161746</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>1136806277795</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>215191962037</v>
+      </c>
+      <c r="E36" s="4" t="n">
         <v>-359696007788</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>215191962037</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>1136806277795</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>772044161746</v>
       </c>
     </row>
     <row r="37">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>2097787236988</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>745556075005</v>
+      </c>
+      <c r="E37" s="4" t="n">
         <v>1105209549882</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>745556075005</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>2097787236988</v>
       </c>
     </row>
     <row r="38">
@@ -4160,16 +4160,16 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>20360895</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>158409220</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>74512931</v>
+      </c>
+      <c r="E38" s="4" t="n">
         <v>42532911</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>74512931</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>158409220</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>20360895</v>
       </c>
     </row>
     <row r="39">
@@ -4179,16 +4179,16 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>2869851759629</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>2097787236988</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="E39" s="4" t="n">
         <v>745556075005</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>2097787236988</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>2869851759629</v>
       </c>
     </row>
     <row r="40">
@@ -4262,11 +4262,11 @@
   <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="56" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -4277,8 +4277,12 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="6" t="n"/>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
+        </is>
+      </c>
     </row>
     <row r="3"/>
     <row r="4">
@@ -4299,19 +4303,19 @@
         </is>
       </c>
       <c r="B5" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C5" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D5" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E5" s="10">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>
@@ -4825,19 +4829,19 @@
         </is>
       </c>
       <c r="B38" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="C38" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="D38" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="E38" s="10">
         <f>'balance_sheet'!B1</f>
-        <v/>
-      </c>
-      <c r="C38" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="D38" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>'balance_sheet'!E1</f>
         <v/>
       </c>
     </row>

--- a/financials/FRT/FRT_financials.xlsx
+++ b/financials/FRT/FRT_financials.xlsx
@@ -543,14 +543,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:I123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -561,22 +565,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -587,16 +611,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>4815269284036</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>6173238780511</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>4959999144880</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>10185041534436</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>9326797408285</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>11415308018413</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>14026158730456</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>21787052185671</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>14026158730456</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>11415308018413</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>9326797408285</v>
       </c>
     </row>
     <row r="3">
@@ -606,16 +642,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>948378394826</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>869649553585</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>701504239398</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>1105209549882</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>745556075005</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>2097787236988</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>2869851759629</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>2097787236988</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>745556075005</v>
       </c>
     </row>
     <row r="4">
@@ -625,16 +673,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>855378394826</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>415978667247</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>551504239398</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>679938797236</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>450488205110</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>514817562060</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>475787236988</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>385251759629</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>475787236988</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>514817562060</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>450488205110</v>
       </c>
     </row>
     <row r="5">
@@ -644,16 +704,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>93000000000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>453670886338</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>150000000000</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>425270752646</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>295067869895</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>446004987913</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1622000000000</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>2484600000000</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>1622000000000</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>446004987913</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>295067869895</v>
       </c>
     </row>
     <row r="6">
@@ -674,6 +746,18 @@
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -681,16 +765,20 @@
           <t>Đầu tư ngắn hạn</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="B7" s="4" t="inlineStr"/>
+      <c r="C7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -712,6 +800,18 @@
       <c r="E8" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -720,16 +820,28 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>1206756927412</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1178069210426</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>1498241305903</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1948474611240</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>538346191905</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>394464296948</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>417127103606</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>728878339921</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>417127103606</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>394464296948</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>538346191905</v>
       </c>
     </row>
     <row r="10">
@@ -739,16 +851,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>237824070242</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>294574594760</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>172584643781</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>80725494654</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>89622537320</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>126026140388</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>176150692098</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>233091257926</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>176150692098</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>126026140388</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>89622537320</v>
       </c>
     </row>
     <row r="11">
@@ -758,16 +882,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>144013265281</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>96527158702</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>93596830533</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>128696749438</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>73767134666</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>48902780339</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>43997579646</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>94792455388</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>43997579646</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>48902780339</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>73767134666</v>
       </c>
     </row>
     <row r="12">
@@ -788,6 +924,18 @@
       <c r="E12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -807,6 +955,18 @@
       <c r="E13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -815,16 +975,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>722345486208</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>499067505423</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>405045636978</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>186801082361</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>342099580137</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>227411821380</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>206546170984</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>410499058289</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>206546170984</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>227411821380</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>342099580137</v>
       </c>
     </row>
     <row r="15">
@@ -834,16 +1006,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-17784960512</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-34459114652</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-57985805389</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-7748715213</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-7143060218</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-7876445159</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-9567339122</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>-9504431682</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-9567339122</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-7876445159</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-7143060218</v>
       </c>
     </row>
     <row r="16">
@@ -853,16 +1037,28 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>2506218917201</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3383542174980</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>1826717690762</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>4930359332607</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>6483827665529</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>8426860753034</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>10234733890772</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>11926663463990</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>10234733890772</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>8426860753034</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>6483827665529</v>
       </c>
     </row>
     <row r="17">
@@ -872,16 +1068,28 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>2519583804091</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>3399092416117</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>1853134198142</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>4975973822810</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>6525562245058</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>8470079480259</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>10291473307238</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>12012604661865</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>10291473307238</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>8470079480259</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>6525562245058</v>
       </c>
     </row>
     <row r="18">
@@ -891,16 +1099,28 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-13364886890</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-15550241137</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-26416507380</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-45614490203</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-41734579529</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-43218727225</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>-56739416466</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>-85941197875</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-56739416466</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-43218727225</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-41734579529</v>
       </c>
     </row>
     <row r="19">
@@ -921,6 +1141,18 @@
       <c r="E19" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -929,16 +1161,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>94320134590</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>118431159332</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>119330193082</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>163029953119</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>260931923787</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>230547735063</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>252093295842</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>262782269911</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>252093295842</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>230547735063</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>260931923787</v>
       </c>
     </row>
     <row r="21">
@@ -948,16 +1192,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>55454839536</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>128901646703</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>26045172004</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>217235680315</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>157021246028</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>186402495200</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>16870747637</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>47661947145</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>16870747637</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>186402495200</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>157021246028</v>
       </c>
     </row>
     <row r="22">
@@ -967,16 +1223,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>27500</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1858819</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>1858819</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>232407273</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>22114306031</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>22210188195</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>21546455611</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>22214405075</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>21546455611</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>22210188195</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>22114306031</v>
       </c>
     </row>
     <row r="23">
@@ -985,16 +1253,20 @@
           <t>Tài sản lưu động khác</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" s="4" t="n">
+      <c r="B23" s="4" t="inlineStr"/>
+      <c r="C23" s="4" t="inlineStr"/>
+      <c r="D23" s="4" t="inlineStr"/>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,16 +1277,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>352400130929</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>420534253911</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>427578741148</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>635298266482</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1196999526761</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>1683141884191</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>1806391668645</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>1927183984705</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>1806391668645</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>1683141884191</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>1196999526761</v>
       </c>
     </row>
     <row r="25">
@@ -1024,16 +1308,28 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>84027534483</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>105270293641</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>116400384163</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>136776859874</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>170162186921</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>179315098485</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>182805424079</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>194450060810</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>182805424079</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>179315098485</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>170162186921</v>
       </c>
     </row>
     <row r="26">
@@ -1054,6 +1350,18 @@
       <c r="E26" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -1073,6 +1381,18 @@
       <c r="E27" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
@@ -1081,16 +1401,28 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>84027534483</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>105270293641</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>116400384163</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>136776859874</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>170162186921</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>179315098485</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>182805424079</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>194450060810</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>182805424079</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>179315098485</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>170162186921</v>
       </c>
     </row>
     <row r="29">
@@ -1111,6 +1443,18 @@
       <c r="E29" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
@@ -1119,16 +1463,28 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>45591818347</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>48570958580</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>50627870323</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>448088085056</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>847269560047</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>1307637254001</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>1445982801672</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>1574317843107</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1445982801672</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>1307637254001</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>847269560047</v>
       </c>
     </row>
     <row r="31">
@@ -1138,16 +1494,28 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>5154076518</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>6614568303</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>8708246794</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>292481788227</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>675128050014</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>1079496087742</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>1156676461871</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>1196539820561</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>1156676461871</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>1079496087742</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>675128050014</v>
       </c>
     </row>
     <row r="32">
@@ -1157,16 +1525,28 @@
         </is>
       </c>
       <c r="B32" s="4" t="n">
+        <v>9344459141</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>11190777144</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>14159992286</v>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>489527414193</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>979182072742</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>1608729339222</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>1915183739839</v>
+      </c>
+      <c r="I32" s="4" t="n">
         <v>2285328752900</v>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>1915183739839</v>
-      </c>
-      <c r="D32" s="4" t="n">
-        <v>1608729339222</v>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>979182072742</v>
       </c>
     </row>
     <row r="33">
@@ -1176,16 +1556,28 @@
         </is>
       </c>
       <c r="B33" s="4" t="n">
+        <v>-4190382623</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>-4576208841</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-5451745492</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>-197045625966</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>-304054022728</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-529233251480</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>-758507277968</v>
+      </c>
+      <c r="I33" s="4" t="n">
         <v>-1088788932339</v>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>-758507277968</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>-529233251480</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-304054022728</v>
       </c>
     </row>
     <row r="34">
@@ -1206,6 +1598,18 @@
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -1225,6 +1629,18 @@
       <c r="E35" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
@@ -1244,6 +1660,18 @@
       <c r="E36" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -1252,16 +1680,28 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>40437741829</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>41956390277</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>41919623529</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>155606296829</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>172141510033</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>228141166259</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>289306339801</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>377778022546</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>289306339801</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>228141166259</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>172141510033</v>
       </c>
     </row>
     <row r="38">
@@ -1271,16 +1711,28 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>44481737990</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>46415767990</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>46875627990</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>162787719740</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>183893578870</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>255220010970</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>348666597970</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>495746297007</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>348666597970</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>255220010970</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>183893578870</v>
       </c>
     </row>
     <row r="39">
@@ -1290,16 +1742,28 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>-4043996161</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>-4459377713</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-4956004461</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>-7181422911</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>-11752068837</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>-27078844711</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>-59360258169</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>-117968274461</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>-59360258169</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>-27078844711</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>-11752068837</v>
       </c>
     </row>
     <row r="40">
@@ -1320,6 +1784,18 @@
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -1339,6 +1815,18 @@
       <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -1358,6 +1846,18 @@
       <c r="E42" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
@@ -1377,6 +1877,18 @@
       <c r="E43" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
@@ -1396,6 +1908,18 @@
       <c r="E44" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
@@ -1415,6 +1939,18 @@
       <c r="E45" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
@@ -1434,6 +1970,18 @@
       <c r="E46" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
@@ -1453,6 +2001,18 @@
       <c r="E47" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -1472,6 +2032,18 @@
       <c r="E48" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
@@ -1491,6 +2063,18 @@
       <c r="E49" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
@@ -1499,16 +2083,28 @@
         </is>
       </c>
       <c r="B50" s="4" t="n">
+        <v>222780778099</v>
+      </c>
+      <c r="C50" s="4" t="n">
+        <v>266693001690</v>
+      </c>
+      <c r="D50" s="4" t="n">
+        <v>260550486662</v>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>50342412461</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>177772171793</v>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>195418574905</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>169373442894</v>
+      </c>
+      <c r="I50" s="4" t="n">
         <v>157004126788</v>
-      </c>
-      <c r="C50" s="4" t="n">
-        <v>169373442894</v>
-      </c>
-      <c r="D50" s="4" t="n">
-        <v>195418574905</v>
-      </c>
-      <c r="E50" s="4" t="n">
-        <v>177772171793</v>
       </c>
     </row>
     <row r="51">
@@ -1518,16 +2114,28 @@
         </is>
       </c>
       <c r="B51" s="4" t="n">
+        <v>222780778099</v>
+      </c>
+      <c r="C51" s="4" t="n">
+        <v>266693001690</v>
+      </c>
+      <c r="D51" s="4" t="n">
+        <v>257565908116</v>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>49474287687</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>177766571925</v>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>195418574905</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>169373442894</v>
+      </c>
+      <c r="I51" s="4" t="n">
         <v>157004126788</v>
-      </c>
-      <c r="C51" s="4" t="n">
-        <v>169373442894</v>
-      </c>
-      <c r="D51" s="4" t="n">
-        <v>195418574905</v>
-      </c>
-      <c r="E51" s="4" t="n">
-        <v>177766571925</v>
       </c>
     </row>
     <row r="52">
@@ -1537,16 +2145,28 @@
         </is>
       </c>
       <c r="B52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="4" t="n">
+        <v>6279401759</v>
+      </c>
+      <c r="D52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>14902586</v>
+      </c>
+      <c r="H52" s="4" t="n">
         <v>31681844</v>
       </c>
-      <c r="C52" s="4" t="n">
+      <c r="I52" s="4" t="n">
         <v>31681844</v>
-      </c>
-      <c r="D52" s="4" t="n">
-        <v>14902586</v>
-      </c>
-      <c r="E52" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1567,6 +2187,18 @@
       <c r="E53" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
@@ -1575,16 +2207,28 @@
         </is>
       </c>
       <c r="B54" s="4" t="n">
+        <v>5167669414965</v>
+      </c>
+      <c r="C54" s="4" t="n">
+        <v>6593773034422</v>
+      </c>
+      <c r="D54" s="4" t="n">
+        <v>5387577886028</v>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>10820339800918</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>10523796935046</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>13098449902604</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>15832550399101</v>
+      </c>
+      <c r="I54" s="4" t="n">
         <v>23714236170376</v>
-      </c>
-      <c r="C54" s="4" t="n">
-        <v>15832550399101</v>
-      </c>
-      <c r="D54" s="4" t="n">
-        <v>13098449902604</v>
-      </c>
-      <c r="E54" s="4" t="n">
-        <v>10523796935046</v>
       </c>
     </row>
     <row r="55">
@@ -1594,16 +2238,28 @@
         </is>
       </c>
       <c r="B55" s="4" t="n">
+        <v>4008902282342</v>
+      </c>
+      <c r="C55" s="4" t="n">
+        <v>5314409715145</v>
+      </c>
+      <c r="D55" s="4" t="n">
+        <v>4162447981264</v>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>9141065562157</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>8474461394877</v>
+      </c>
+      <c r="G55" s="4" t="n">
+        <v>11379279324447</v>
+      </c>
+      <c r="H55" s="4" t="n">
+        <v>13712736684773</v>
+      </c>
+      <c r="I55" s="4" t="n">
         <v>18575165477143</v>
-      </c>
-      <c r="C55" s="4" t="n">
-        <v>13712736684773</v>
-      </c>
-      <c r="D55" s="4" t="n">
-        <v>11379279324447</v>
-      </c>
-      <c r="E55" s="4" t="n">
-        <v>8474461394877</v>
       </c>
     </row>
     <row r="56">
@@ -1613,16 +2269,28 @@
         </is>
       </c>
       <c r="B56" s="4" t="n">
+        <v>4008902282342</v>
+      </c>
+      <c r="C56" s="4" t="n">
+        <v>5308130313386</v>
+      </c>
+      <c r="D56" s="4" t="n">
+        <v>4162447981264</v>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>9140978862157</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>8474374694877</v>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>11378723422861</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>13712183502929</v>
+      </c>
+      <c r="I56" s="4" t="n">
         <v>18574474295299</v>
-      </c>
-      <c r="C56" s="4" t="n">
-        <v>13712183502929</v>
-      </c>
-      <c r="D56" s="4" t="n">
-        <v>11378723422861</v>
-      </c>
-      <c r="E56" s="4" t="n">
-        <v>8474374694877</v>
       </c>
     </row>
     <row r="57">
@@ -1632,16 +2300,28 @@
         </is>
       </c>
       <c r="B57" s="4" t="n">
+        <v>2947271984607</v>
+      </c>
+      <c r="C57" s="4" t="n">
+        <v>3698035574035</v>
+      </c>
+      <c r="D57" s="4" t="n">
+        <v>2485948231980</v>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>6047406062780</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>5363331144812</v>
+      </c>
+      <c r="G57" s="4" t="n">
+        <v>8108271528775</v>
+      </c>
+      <c r="H57" s="4" t="n">
+        <v>8800349446066</v>
+      </c>
+      <c r="I57" s="4" t="n">
         <v>10051507915817</v>
-      </c>
-      <c r="C57" s="4" t="n">
-        <v>8800349446066</v>
-      </c>
-      <c r="D57" s="4" t="n">
-        <v>8108271528775</v>
-      </c>
-      <c r="E57" s="4" t="n">
-        <v>5363331144812</v>
       </c>
     </row>
     <row r="58">
@@ -1651,16 +2331,28 @@
         </is>
       </c>
       <c r="B58" s="4" t="n">
+        <v>705892254385</v>
+      </c>
+      <c r="C58" s="4" t="n">
+        <v>1287522072458</v>
+      </c>
+      <c r="D58" s="4" t="n">
+        <v>1214790045465</v>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>2372633079056</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>2307356375016</v>
+      </c>
+      <c r="G58" s="4" t="n">
+        <v>2274331043145</v>
+      </c>
+      <c r="H58" s="4" t="n">
+        <v>3202439604461</v>
+      </c>
+      <c r="I58" s="4" t="n">
         <v>5995965425047</v>
-      </c>
-      <c r="C58" s="4" t="n">
-        <v>3202439604461</v>
-      </c>
-      <c r="D58" s="4" t="n">
-        <v>2274331043145</v>
-      </c>
-      <c r="E58" s="4" t="n">
-        <v>2307356375016</v>
       </c>
     </row>
     <row r="59">
@@ -1670,16 +2362,28 @@
         </is>
       </c>
       <c r="B59" s="4" t="n">
+        <v>13917697969</v>
+      </c>
+      <c r="C59" s="4" t="n">
+        <v>19464369762</v>
+      </c>
+      <c r="D59" s="4" t="n">
+        <v>28401024820</v>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>54005913363</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>34974952041</v>
+      </c>
+      <c r="G59" s="4" t="n">
+        <v>23463598041</v>
+      </c>
+      <c r="H59" s="4" t="n">
+        <v>37870117550</v>
+      </c>
+      <c r="I59" s="4" t="n">
         <v>61615375012</v>
-      </c>
-      <c r="C59" s="4" t="n">
-        <v>37870117550</v>
-      </c>
-      <c r="D59" s="4" t="n">
-        <v>23463598041</v>
-      </c>
-      <c r="E59" s="4" t="n">
-        <v>34974952041</v>
       </c>
     </row>
     <row r="60">
@@ -1689,16 +2393,28 @@
         </is>
       </c>
       <c r="B60" s="4" t="n">
+        <v>24449995872</v>
+      </c>
+      <c r="C60" s="4" t="n">
+        <v>9107550641</v>
+      </c>
+      <c r="D60" s="4" t="n">
+        <v>31619901384</v>
+      </c>
+      <c r="E60" s="4" t="n">
+        <v>71323601688</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>3120462679</v>
+      </c>
+      <c r="G60" s="4" t="n">
+        <v>39713137523</v>
+      </c>
+      <c r="H60" s="4" t="n">
+        <v>124543935725</v>
+      </c>
+      <c r="I60" s="4" t="n">
         <v>244716064984</v>
-      </c>
-      <c r="C60" s="4" t="n">
-        <v>124543935725</v>
-      </c>
-      <c r="D60" s="4" t="n">
-        <v>39713137523</v>
-      </c>
-      <c r="E60" s="4" t="n">
-        <v>3120462679</v>
       </c>
     </row>
     <row r="61">
@@ -1708,16 +2424,28 @@
         </is>
       </c>
       <c r="B61" s="4" t="n">
+        <v>1115924887</v>
+      </c>
+      <c r="C61" s="4" t="n">
+        <v>1512347136</v>
+      </c>
+      <c r="D61" s="4" t="n">
+        <v>1577532062</v>
+      </c>
+      <c r="E61" s="4" t="n">
+        <v>408611138142</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>535694930652</v>
+      </c>
+      <c r="G61" s="4" t="n">
+        <v>669094486391</v>
+      </c>
+      <c r="H61" s="4" t="n">
+        <v>1034444152158</v>
+      </c>
+      <c r="I61" s="4" t="n">
         <v>1331638783393</v>
-      </c>
-      <c r="C61" s="4" t="n">
-        <v>1034444152158</v>
-      </c>
-      <c r="D61" s="4" t="n">
-        <v>669094486391</v>
-      </c>
-      <c r="E61" s="4" t="n">
-        <v>535694930652</v>
       </c>
     </row>
     <row r="62">
@@ -1727,16 +2455,28 @@
         </is>
       </c>
       <c r="B62" s="4" t="n">
+        <v>157056851165</v>
+      </c>
+      <c r="C62" s="4" t="n">
+        <v>162531437632</v>
+      </c>
+      <c r="D62" s="4" t="n">
+        <v>219972444070</v>
+      </c>
+      <c r="E62" s="4" t="n">
+        <v>86457469555</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>103346666037</v>
+      </c>
+      <c r="G62" s="4" t="n">
+        <v>125947493296</v>
+      </c>
+      <c r="H62" s="4" t="n">
+        <v>194907134412</v>
+      </c>
+      <c r="I62" s="4" t="n">
         <v>281753290017</v>
-      </c>
-      <c r="C62" s="4" t="n">
-        <v>194907134412</v>
-      </c>
-      <c r="D62" s="4" t="n">
-        <v>125947493296</v>
-      </c>
-      <c r="E62" s="4" t="n">
-        <v>103346666037</v>
       </c>
     </row>
     <row r="63">
@@ -1757,6 +2497,18 @@
       <c r="E63" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
@@ -1776,6 +2528,18 @@
       <c r="E64" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
@@ -1784,16 +2548,28 @@
         </is>
       </c>
       <c r="B65" s="4" t="n">
+        <v>146801625616</v>
+      </c>
+      <c r="C65" s="4" t="n">
+        <v>110701883788</v>
+      </c>
+      <c r="D65" s="4" t="n">
+        <v>162944770886</v>
+      </c>
+      <c r="E65" s="4" t="n">
+        <v>85527316976</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>112206340770</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>113315953611</v>
+      </c>
+      <c r="H65" s="4" t="n">
+        <v>89015814529</v>
+      </c>
+      <c r="I65" s="4" t="n">
         <v>94765132430</v>
-      </c>
-      <c r="C65" s="4" t="n">
-        <v>89015814529</v>
-      </c>
-      <c r="D65" s="4" t="n">
-        <v>113315953611</v>
-      </c>
-      <c r="E65" s="4" t="n">
-        <v>112206340770</v>
       </c>
     </row>
     <row r="66">
@@ -1803,16 +2579,28 @@
         </is>
       </c>
       <c r="B66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="4" t="n">
+        <v>303659660</v>
+      </c>
+      <c r="H66" s="4" t="n">
+        <v>2956037244</v>
+      </c>
+      <c r="I66" s="4" t="n">
         <v>5828163047</v>
-      </c>
-      <c r="C66" s="4" t="n">
-        <v>2956037244</v>
-      </c>
-      <c r="D66" s="4" t="n">
-        <v>303659660</v>
-      </c>
-      <c r="E66" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1822,16 +2610,28 @@
         </is>
       </c>
       <c r="B67" s="4" t="n">
+        <v>12395947841</v>
+      </c>
+      <c r="C67" s="4" t="n">
+        <v>19255077934</v>
+      </c>
+      <c r="D67" s="4" t="n">
+        <v>17194030597</v>
+      </c>
+      <c r="E67" s="4" t="n">
+        <v>14808630597</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>14021497597</v>
+      </c>
+      <c r="G67" s="4" t="n">
+        <v>10677497597</v>
+      </c>
+      <c r="H67" s="4" t="n">
+        <v>5733824194</v>
+      </c>
+      <c r="I67" s="4" t="n">
         <v>8178120854</v>
-      </c>
-      <c r="C67" s="4" t="n">
-        <v>5733824194</v>
-      </c>
-      <c r="D67" s="4" t="n">
-        <v>10677497597</v>
-      </c>
-      <c r="E67" s="4" t="n">
-        <v>14021497597</v>
       </c>
     </row>
     <row r="68">
@@ -1841,17 +2641,29 @@
         </is>
       </c>
       <c r="B68" s="4" t="n">
-        <v>691181844</v>
+        <v>0</v>
       </c>
       <c r="C68" s="4" t="n">
-        <v>553181844</v>
+        <v>6279401759</v>
       </c>
       <c r="D68" s="4" t="n">
-        <v>555901586</v>
+        <v>0</v>
       </c>
       <c r="E68" s="4" t="n">
         <v>86700000</v>
       </c>
+      <c r="F68" s="4" t="n">
+        <v>86700000</v>
+      </c>
+      <c r="G68" s="4" t="n">
+        <v>555901586</v>
+      </c>
+      <c r="H68" s="4" t="n">
+        <v>553181844</v>
+      </c>
+      <c r="I68" s="4" t="n">
+        <v>691181844</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
@@ -1871,6 +2683,18 @@
       <c r="E69" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="inlineStr">
@@ -1890,6 +2714,18 @@
       <c r="E70" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
@@ -1898,17 +2734,29 @@
         </is>
       </c>
       <c r="B71" s="4" t="n">
-        <v>659500000</v>
+        <v>0</v>
       </c>
       <c r="C71" s="4" t="n">
-        <v>521500000</v>
+        <v>0</v>
       </c>
       <c r="D71" s="4" t="n">
-        <v>540999000</v>
+        <v>0</v>
       </c>
       <c r="E71" s="4" t="n">
         <v>86700000</v>
       </c>
+      <c r="F71" s="4" t="n">
+        <v>86700000</v>
+      </c>
+      <c r="G71" s="4" t="n">
+        <v>540999000</v>
+      </c>
+      <c r="H71" s="4" t="n">
+        <v>521500000</v>
+      </c>
+      <c r="I71" s="4" t="n">
+        <v>659500000</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
@@ -1928,6 +2776,18 @@
       <c r="E72" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
@@ -1935,17 +2795,21 @@
           <t>Thuế thu nhập hoãn lại</t>
         </is>
       </c>
-      <c r="B73" s="4" t="n">
+      <c r="B73" s="4" t="inlineStr"/>
+      <c r="C73" s="4" t="inlineStr"/>
+      <c r="D73" s="4" t="inlineStr"/>
+      <c r="E73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="4" t="n">
+        <v>14902586</v>
+      </c>
+      <c r="H73" s="4" t="n">
         <v>31681844</v>
       </c>
-      <c r="C73" s="4" t="n">
+      <c r="I73" s="4" t="n">
         <v>31681844</v>
-      </c>
-      <c r="D73" s="4" t="n">
-        <v>14902586</v>
-      </c>
-      <c r="E73" s="4" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1966,6 +2830,18 @@
       <c r="E74" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
@@ -1985,6 +2861,18 @@
       <c r="E75" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="inlineStr">
@@ -2004,6 +2892,18 @@
       <c r="E76" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
@@ -2023,6 +2923,18 @@
       <c r="E77" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -2031,16 +2943,28 @@
         </is>
       </c>
       <c r="B78" s="4" t="n">
+        <v>1158767132623</v>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>1279363319277</v>
+      </c>
+      <c r="D78" s="4" t="n">
+        <v>1225129904764</v>
+      </c>
+      <c r="E78" s="4" t="n">
+        <v>1679274238761</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>2049335540169</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>1719170578157</v>
+      </c>
+      <c r="H78" s="4" t="n">
+        <v>2119813714328</v>
+      </c>
+      <c r="I78" s="4" t="n">
         <v>5139070693233</v>
-      </c>
-      <c r="C78" s="4" t="n">
-        <v>2119813714328</v>
-      </c>
-      <c r="D78" s="4" t="n">
-        <v>1719170578157</v>
-      </c>
-      <c r="E78" s="4" t="n">
-        <v>2049335540169</v>
       </c>
     </row>
     <row r="79">
@@ -2050,16 +2974,28 @@
         </is>
       </c>
       <c r="B79" s="4" t="n">
+        <v>1158767132623</v>
+      </c>
+      <c r="C79" s="4" t="n">
+        <v>1279363319277</v>
+      </c>
+      <c r="D79" s="4" t="n">
+        <v>1225129904764</v>
+      </c>
+      <c r="E79" s="4" t="n">
+        <v>1679274238761</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>2049335540169</v>
+      </c>
+      <c r="G79" s="4" t="n">
+        <v>1719170578157</v>
+      </c>
+      <c r="H79" s="4" t="n">
+        <v>2119813714328</v>
+      </c>
+      <c r="I79" s="4" t="n">
         <v>5139070693233</v>
-      </c>
-      <c r="C79" s="4" t="n">
-        <v>2119813714328</v>
-      </c>
-      <c r="D79" s="4" t="n">
-        <v>1719170578157</v>
-      </c>
-      <c r="E79" s="4" t="n">
-        <v>2049335540169</v>
       </c>
     </row>
     <row r="80">
@@ -2069,16 +3005,28 @@
         </is>
       </c>
       <c r="B80" s="4" t="n">
+        <v>680000000000</v>
+      </c>
+      <c r="C80" s="4" t="n">
+        <v>789817920000</v>
+      </c>
+      <c r="D80" s="4" t="n">
+        <v>789817920000</v>
+      </c>
+      <c r="E80" s="4" t="n">
+        <v>789817920000</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>1184725350000</v>
+      </c>
+      <c r="G80" s="4" t="n">
+        <v>1362423890000</v>
+      </c>
+      <c r="H80" s="4" t="n">
+        <v>1362423890000</v>
+      </c>
+      <c r="I80" s="4" t="n">
         <v>1703017850000</v>
-      </c>
-      <c r="C80" s="4" t="n">
-        <v>1362423890000</v>
-      </c>
-      <c r="D80" s="4" t="n">
-        <v>1362423890000</v>
-      </c>
-      <c r="E80" s="4" t="n">
-        <v>1184725350000</v>
       </c>
     </row>
     <row r="81">
@@ -2099,6 +3047,18 @@
       <c r="E81" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="inlineStr">
@@ -2118,6 +3078,18 @@
       <c r="E82" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="inlineStr">
@@ -2137,6 +3109,18 @@
       <c r="E83" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="inlineStr">
@@ -2156,6 +3140,18 @@
       <c r="E84" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="inlineStr">
@@ -2175,6 +3171,18 @@
       <c r="E85" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
@@ -2194,6 +3202,18 @@
       <c r="E86" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="inlineStr">
@@ -2213,6 +3233,18 @@
       <c r="E87" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="inlineStr">
@@ -2232,6 +3264,18 @@
       <c r="E88" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
@@ -2240,16 +3284,28 @@
         </is>
       </c>
       <c r="B89" s="4" t="n">
+        <v>453783369453</v>
+      </c>
+      <c r="C89" s="4" t="n">
+        <v>483908235123</v>
+      </c>
+      <c r="D89" s="4" t="n">
+        <v>423908570033</v>
+      </c>
+      <c r="E89" s="4" t="n">
+        <v>872390396152</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>823505616594</v>
+      </c>
+      <c r="G89" s="4" t="n">
+        <v>236832252322</v>
+      </c>
+      <c r="H89" s="4" t="n">
+        <v>549386390157</v>
+      </c>
+      <c r="I89" s="4" t="n">
         <v>2468442850502</v>
-      </c>
-      <c r="C89" s="4" t="n">
-        <v>549386390157</v>
-      </c>
-      <c r="D89" s="4" t="n">
-        <v>236832252322</v>
-      </c>
-      <c r="E89" s="4" t="n">
-        <v>823505616594</v>
       </c>
     </row>
     <row r="90">
@@ -2270,6 +3326,18 @@
       <c r="E90" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
@@ -2289,6 +3357,18 @@
       <c r="E91" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
@@ -2308,6 +3388,18 @@
       <c r="E92" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="inlineStr">
@@ -2327,6 +3419,18 @@
       <c r="E93" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
@@ -2346,6 +3450,18 @@
       <c r="E94" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
@@ -2354,16 +3470,28 @@
         </is>
       </c>
       <c r="B95" s="4" t="n">
+        <v>5167669414965</v>
+      </c>
+      <c r="C95" s="4" t="n">
+        <v>6593773034422</v>
+      </c>
+      <c r="D95" s="4" t="n">
+        <v>5387577886028</v>
+      </c>
+      <c r="E95" s="4" t="n">
+        <v>10820339800918</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>10523796935046</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>13098449902604</v>
+      </c>
+      <c r="H95" s="4" t="n">
+        <v>15832550399101</v>
+      </c>
+      <c r="I95" s="4" t="n">
         <v>23714236170376</v>
-      </c>
-      <c r="C95" s="4" t="n">
-        <v>15832550399101</v>
-      </c>
-      <c r="D95" s="4" t="n">
-        <v>13098449902604</v>
-      </c>
-      <c r="E95" s="4" t="n">
-        <v>10523796935046</v>
       </c>
     </row>
     <row r="96">
@@ -2384,6 +3512,18 @@
       <c r="E96" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="inlineStr">
@@ -2403,6 +3543,18 @@
       <c r="E97" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="inlineStr">
@@ -2422,6 +3574,18 @@
       <c r="E98" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
@@ -2441,6 +3605,18 @@
       <c r="E99" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="inlineStr">
@@ -2449,16 +3625,28 @@
         </is>
       </c>
       <c r="B100" s="4" t="n">
-        <v>0</v>
+        <v>120359066193</v>
       </c>
       <c r="C100" s="4" t="n">
-        <v>0</v>
+        <v>322359066193</v>
       </c>
       <c r="D100" s="4" t="n">
-        <v>0</v>
+        <v>885000000000</v>
       </c>
       <c r="E100" s="4" t="n">
+        <v>1560000000000</v>
+      </c>
+      <c r="F100" s="4" t="n">
         <v>40000000000</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2479,6 +3667,18 @@
       <c r="E101" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="inlineStr">
@@ -2498,6 +3698,18 @@
       <c r="E102" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
@@ -2517,6 +3729,18 @@
       <c r="E103" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -2525,16 +3749,28 @@
         </is>
       </c>
       <c r="B104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="4" t="n">
+        <v>90909091</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>1795608000</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>770956800</v>
+      </c>
+      <c r="H104" s="4" t="n">
+        <v>8230000000</v>
+      </c>
+      <c r="I104" s="4" t="n">
         <v>1411954000</v>
-      </c>
-      <c r="C104" s="4" t="n">
-        <v>8230000000</v>
-      </c>
-      <c r="D104" s="4" t="n">
-        <v>770956800</v>
-      </c>
-      <c r="E104" s="4" t="n">
-        <v>1795608000</v>
       </c>
     </row>
     <row r="105">
@@ -2555,6 +3791,18 @@
       <c r="E105" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="inlineStr">
@@ -2562,16 +3810,20 @@
           <t>Đầu tư nắm giữ đến ngày đáo hạn</t>
         </is>
       </c>
-      <c r="B106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="4" t="n">
+      <c r="B106" s="4" t="inlineStr"/>
+      <c r="C106" s="4" t="inlineStr"/>
+      <c r="D106" s="4" t="inlineStr"/>
+      <c r="E106" s="4" t="inlineStr"/>
+      <c r="F106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2593,6 +3845,18 @@
       <c r="E107" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
@@ -2601,16 +3865,28 @@
         </is>
       </c>
       <c r="B108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="4" t="n">
+        <v>205650000</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>322325273</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>13605024822</v>
+      </c>
+      <c r="H108" s="4" t="n">
+        <v>219923436590</v>
+      </c>
+      <c r="I108" s="4" t="n">
         <v>498506024698</v>
-      </c>
-      <c r="C108" s="4" t="n">
-        <v>219923436590</v>
-      </c>
-      <c r="D108" s="4" t="n">
-        <v>13605024822</v>
-      </c>
-      <c r="E108" s="4" t="n">
-        <v>322325273</v>
       </c>
     </row>
     <row r="109">
@@ -2631,6 +3907,18 @@
       <c r="E109" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="inlineStr">
@@ -2650,6 +3938,18 @@
       <c r="E110" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="inlineStr">
@@ -2669,6 +3969,18 @@
       <c r="E111" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="inlineStr">
@@ -2688,6 +4000,18 @@
       <c r="E112" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
@@ -2707,6 +4031,18 @@
       <c r="E113" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
@@ -2726,6 +4062,18 @@
       <c r="E114" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
@@ -2733,16 +4081,20 @@
           <t>Cổ phiếu ưu đãi</t>
         </is>
       </c>
-      <c r="B115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="4" t="n">
+      <c r="B115" s="4" t="inlineStr"/>
+      <c r="C115" s="4" t="inlineStr"/>
+      <c r="D115" s="4" t="inlineStr"/>
+      <c r="E115" s="4" t="inlineStr"/>
+      <c r="F115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2753,16 +4105,28 @@
         </is>
       </c>
       <c r="B116" s="4" t="n">
+        <v>680000000000</v>
+      </c>
+      <c r="C116" s="4" t="n">
+        <v>789817920000</v>
+      </c>
+      <c r="D116" s="4" t="n">
+        <v>789817920000</v>
+      </c>
+      <c r="E116" s="4" t="n">
+        <v>789817920000</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>1184725350000</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>1362423890000</v>
+      </c>
+      <c r="H116" s="4" t="n">
+        <v>1362423890000</v>
+      </c>
+      <c r="I116" s="4" t="n">
         <v>1703017850000</v>
-      </c>
-      <c r="C116" s="4" t="n">
-        <v>1362423890000</v>
-      </c>
-      <c r="D116" s="4" t="n">
-        <v>1362423890000</v>
-      </c>
-      <c r="E116" s="4" t="n">
-        <v>1184725350000</v>
       </c>
     </row>
     <row r="117">
@@ -2783,6 +4147,18 @@
       <c r="E117" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -2791,16 +4167,28 @@
         </is>
       </c>
       <c r="B118" s="4" t="n">
+        <v>116454372696</v>
+      </c>
+      <c r="C118" s="4" t="n">
+        <v>282085449452</v>
+      </c>
+      <c r="D118" s="4" t="n">
+        <v>404926443124</v>
+      </c>
+      <c r="E118" s="4" t="n">
+        <v>423908570033</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>437992070152</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>586570809094</v>
+      </c>
+      <c r="H118" s="4" t="n">
+        <v>236975520956</v>
+      </c>
+      <c r="I118" s="4" t="n">
         <v>197121393961</v>
-      </c>
-      <c r="C118" s="4" t="n">
-        <v>236975520956</v>
-      </c>
-      <c r="D118" s="4" t="n">
-        <v>586570809094</v>
-      </c>
-      <c r="E118" s="4" t="n">
-        <v>437992070152</v>
       </c>
     </row>
     <row r="119">
@@ -2810,16 +4198,28 @@
         </is>
       </c>
       <c r="B119" s="4" t="n">
+        <v>337328996757</v>
+      </c>
+      <c r="C119" s="4" t="n">
+        <v>201822785671</v>
+      </c>
+      <c r="D119" s="4" t="n">
+        <v>18982126909</v>
+      </c>
+      <c r="E119" s="4" t="n">
+        <v>448481826119</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>385513546442</v>
+      </c>
+      <c r="G119" s="4" t="n">
+        <v>-349738556772</v>
+      </c>
+      <c r="H119" s="4" t="n">
+        <v>312410869201</v>
+      </c>
+      <c r="I119" s="4" t="n">
         <v>2271321456541</v>
-      </c>
-      <c r="C119" s="4" t="n">
-        <v>312410869201</v>
-      </c>
-      <c r="D119" s="4" t="n">
-        <v>-349738556772</v>
-      </c>
-      <c r="E119" s="4" t="n">
-        <v>385513546442</v>
       </c>
     </row>
     <row r="120">
@@ -2829,16 +4229,28 @@
         </is>
       </c>
       <c r="B120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="4" t="n">
+        <v>90909091</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>1795608000</v>
+      </c>
+      <c r="G120" s="4" t="n">
+        <v>770956800</v>
+      </c>
+      <c r="H120" s="4" t="n">
+        <v>8230000000</v>
+      </c>
+      <c r="I120" s="4" t="n">
         <v>1411954000</v>
-      </c>
-      <c r="C120" s="4" t="n">
-        <v>8230000000</v>
-      </c>
-      <c r="D120" s="4" t="n">
-        <v>770956800</v>
-      </c>
-      <c r="E120" s="4" t="n">
-        <v>1795608000</v>
       </c>
     </row>
     <row r="121">
@@ -2859,6 +4271,18 @@
       <c r="E121" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
@@ -2867,16 +4291,28 @@
         </is>
       </c>
       <c r="B122" s="4" t="n">
+        <v>24983763170</v>
+      </c>
+      <c r="C122" s="4" t="n">
+        <v>5637164154</v>
+      </c>
+      <c r="D122" s="4" t="n">
+        <v>11403414731</v>
+      </c>
+      <c r="E122" s="4" t="n">
+        <v>17065922609</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>41104573575</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>119914435835</v>
+      </c>
+      <c r="H122" s="4" t="n">
+        <v>208003434171</v>
+      </c>
+      <c r="I122" s="4" t="n">
         <v>967609992731</v>
-      </c>
-      <c r="C122" s="4" t="n">
-        <v>208003434171</v>
-      </c>
-      <c r="D122" s="4" t="n">
-        <v>119914435835</v>
-      </c>
-      <c r="E122" s="4" t="n">
-        <v>41104573575</v>
       </c>
     </row>
     <row r="123">
@@ -2895,6 +4331,18 @@
         <v>0</v>
       </c>
       <c r="E123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2909,14 +4357,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2927,22 +4379,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -2953,16 +4425,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>15889645872798</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>16988956546078</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>14799952534765</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>22619505421050</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>30276710796279</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>31975613596365</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>40241629282059</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>51232049640567</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>40241629282059</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>31975613596365</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>30276710796279</v>
       </c>
     </row>
     <row r="3">
@@ -2972,16 +4456,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>-591311306900</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>-354996798915</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-138535502543</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>-124544012968</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>-110910039609</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-125963979645</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>-137136750875</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>-149181195799</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>-137136750875</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>-125963979645</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>-110910039609</v>
       </c>
     </row>
     <row r="4">
@@ -2991,16 +4487,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>15298334565898</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>16633959747163</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>14661417032222</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>22494961408082</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>30165800756670</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>31849649616720</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>40104492531184</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>51082868444768</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>40104492531184</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>31849649616720</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>30165800756670</v>
       </c>
     </row>
     <row r="5">
@@ -3010,16 +4518,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-13254725142547</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-14522902581026</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-12620414733505</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>-19343448146483</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-25462623377413</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-26688006159054</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>-32521431587237</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>-41073163986683</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-32521431587237</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-26688006159054</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-25462623377413</v>
       </c>
     </row>
     <row r="6">
@@ -3029,16 +4549,28 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
+        <v>2043609423351</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>2111057166137</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>2041002298717</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>3151513261599</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>4703177379257</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>5161643457666</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>7583060943947</v>
+      </c>
+      <c r="I6" s="4" t="n">
         <v>10009704458085</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>7583060943947</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>5161643457666</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>4703177379257</v>
       </c>
     </row>
     <row r="7">
@@ -3048,16 +4580,28 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>42866217249</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>78050133404</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>70749420260</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>197580982169</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>173746497842</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>80257624527</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>106913298138</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>287764741779</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>106913298138</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>80257624527</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>173746497842</v>
       </c>
     </row>
     <row r="8">
@@ -3067,16 +4611,28 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>-100572817952</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>-147964791194</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-133811898461</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-146245489692</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>-256319530992</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>-292262559450</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>-253792623553</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>-388683187751</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>-253792623553</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>-292262559450</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>-256319530992</v>
       </c>
     </row>
     <row r="9">
@@ -3086,16 +4642,28 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
+        <v>-95670507863</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-135183263352</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>-113682404790</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>-132229176761</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>-231527904809</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>-284917373606</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>-253428831252</v>
+      </c>
+      <c r="I9" s="4" t="n">
         <v>-388595922369</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>-253428831252</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>-284917373606</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>-231527904809</v>
       </c>
     </row>
     <row r="10">
@@ -3105,16 +4673,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>-1296274813568</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-1419309973054</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-1565736555190</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>-2071124789339</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>-3259297597681</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>-4169668799072</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>-5527210989725</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>-7018206246026</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>-5527210989725</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>-4169668799072</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>-3259297597681</v>
       </c>
     </row>
     <row r="11">
@@ -3124,16 +4704,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-286839549948</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-349010009416</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-397884049877</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>-585528444388</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-887338884656</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>-1076478805719</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>-1365833850070</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>-1677744619772</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>-1365833850070</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>-1076478805719</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-887338884656</v>
       </c>
     </row>
     <row r="12">
@@ -3143,16 +4735,28 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>402788459132</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>272822525877</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>14319215449</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>546195520349</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>473967863770</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-296509082048</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>543136778737</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>1212835146315</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>543136778737</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-296509082048</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>473967863770</v>
       </c>
     </row>
     <row r="13">
@@ -3162,16 +4766,28 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>34150544259</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>5334005795</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>14991747878</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>9425637534</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>16254109001</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>22062244997</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>24090237620</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>29912692698</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>24090237620</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>22062244997</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>16254109001</v>
       </c>
     </row>
     <row r="14">
@@ -3181,16 +4797,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-2163805024</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-153872420</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-883584837</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-1480892306</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-4598558802</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>-19734846239</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>-40269928171</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>-23630336340</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>-40269928171</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>-19734846239</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-4598558802</v>
       </c>
     </row>
     <row r="15">
@@ -3200,16 +4828,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>31986739235</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>5180133375</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>14108163041</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>7944745228</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>11655550199</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>2327398758</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-16179690551</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>6282356358</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-16179690551</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>2327398758</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>11655550199</v>
       </c>
     </row>
     <row r="16">
@@ -3230,6 +4870,18 @@
       <c r="E16" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3238,16 +4890,28 @@
         </is>
       </c>
       <c r="B17" s="4" t="n">
+        <v>434775198367</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>278002659252</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>28427378490</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>554140265577</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>485623413969</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-294181683290</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>526957088186</v>
+      </c>
+      <c r="I17" s="4" t="n">
         <v>1219117502673</v>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>526957088186</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>-294181683290</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>485623413969</v>
       </c>
     </row>
     <row r="18">
@@ -3257,16 +4921,28 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
+        <v>-87028076358</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-67875765738</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-27474628269</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-108125465377</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-86686691655</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-34994338768</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>-118526676650</v>
+      </c>
+      <c r="I18" s="4" t="n">
         <v>-234877775599</v>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>-118526676650</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>-34994338768</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-86686691655</v>
       </c>
     </row>
     <row r="19">
@@ -3279,13 +4955,25 @@
         <v>0</v>
       </c>
       <c r="C19" s="4" t="n">
+        <v>-6279401759</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>9263980305</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-2116453772</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>-862524906</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-20502454</v>
+      </c>
+      <c r="H19" s="4" t="n">
         <v>-16779258</v>
       </c>
-      <c r="D19" s="4" t="n">
-        <v>-20502454</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-862524906</v>
+      <c r="I19" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -3295,16 +4983,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-87028076358</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-74155167497</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-18210647964</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-110241919149</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-87549216561</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-35014841222</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-118543455908</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>-234877775599</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-118543455908</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-35014841222</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-87549216561</v>
       </c>
     </row>
     <row r="21">
@@ -3314,16 +5014,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>347747122009</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>203847491755</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>10216730526</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>443898346428</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>398074197408</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>-329196524512</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>408413632278</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>984239727074</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>408413632278</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>-329196524512</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>398074197408</v>
       </c>
     </row>
     <row r="22">
@@ -3333,16 +5045,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-16236829</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-9167987408</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-14501865720</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>166178809</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>7713342831</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>16446964816</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>90897366661</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>189374783523</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>90897366661</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>16446964816</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>7713342831</v>
       </c>
     </row>
     <row r="23">
@@ -3352,16 +5076,28 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>347763358838</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>213015479163</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>24718596246</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>443732167619</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>390360854577</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>-345643489328</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>317516265617</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>794864943551</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>317516265617</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>-345643489328</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>390360854577</v>
       </c>
     </row>
     <row r="24">
@@ -3371,16 +5107,28 @@
         </is>
       </c>
       <c r="B24" s="4" t="n">
+        <v>4961</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>2612</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>266</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>3745</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>2865</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>2293</v>
+      </c>
+      <c r="I24" s="4" t="n">
         <v>4653</v>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>2293</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>-2537</v>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>2865</v>
       </c>
     </row>
     <row r="25">
@@ -3390,16 +5138,28 @@
         </is>
       </c>
       <c r="B25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>3745</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>2865</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>-2537</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>2293</v>
+      </c>
+      <c r="I25" s="4" t="n">
         <v>4653</v>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>2293</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>-2537</v>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>2865</v>
       </c>
     </row>
     <row r="26">
@@ -3418,6 +5178,18 @@
         <v>0</v>
       </c>
       <c r="E26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3432,14 +5204,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3450,22 +5226,42 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
           <t>2025</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>2022</t>
         </is>
       </c>
     </row>
@@ -3476,16 +5272,28 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
+        <v>434775198367</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>278002659252</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>28427378490</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>554140265577</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>485623413969</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>-294181683290</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>526957088186</v>
+      </c>
+      <c r="I2" s="4" t="n">
         <v>1219117502673</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>526957088186</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>-294181683290</v>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>485623413969</v>
       </c>
     </row>
     <row r="3">
@@ -3495,16 +5303,28 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>781002276</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>836635952</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>1372163399</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>71537572161</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>115286135177</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>233071988505</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>318442950010</v>
+      </c>
+      <c r="I3" s="4" t="n">
         <v>402557018224</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>318442950010</v>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>233071988505</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>115286135177</v>
       </c>
     </row>
     <row r="4">
@@ -3514,16 +5334,28 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>14477629465</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>18859508387</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>34392956980</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>-31039107353</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>-4485565669</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>2521192297</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>17863960788</v>
+      </c>
+      <c r="I4" s="4" t="n">
         <v>32010999772</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>17863960788</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>2521192297</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>-4485565669</v>
       </c>
     </row>
     <row r="5">
@@ -3533,16 +5365,28 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
+        <v>-2380950000</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-1573500000</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-75365966</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>7513094690</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>-42532911</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>-74512931</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>-158409220</v>
+      </c>
+      <c r="I5" s="4" t="n">
         <v>-20360895</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-158409220</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>-74512931</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>-42532911</v>
       </c>
     </row>
     <row r="6">
@@ -3563,6 +5407,18 @@
       <c r="E6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -3571,16 +5427,28 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
+        <v>-20946487598</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>-61193294228</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-55870719645</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>-169344292160</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>-147853905457</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>-50019830875</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>-70652632259</v>
+      </c>
+      <c r="I7" s="4" t="n">
         <v>-267669594473</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>-70652632259</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>-50019830875</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>-147853905457</v>
       </c>
     </row>
     <row r="8">
@@ -3590,16 +5458,28 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
+        <v>95670507863</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>135183263352</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>113682404790</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>132229176761</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>231527904809</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>284917373606</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>253428831252</v>
+      </c>
+      <c r="I8" s="4" t="n">
         <v>388595922369</v>
-      </c>
-      <c r="C8" s="4" t="n">
-        <v>253428831252</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>284917373606</v>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>231527904809</v>
       </c>
     </row>
     <row r="9">
@@ -3620,6 +5500,18 @@
       <c r="E9" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -3628,16 +5520,28 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
+        <v>522376900373</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>370115272715</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>121928818048</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>565036709676</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>680055449918</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>176234527312</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>1045881788757</v>
+      </c>
+      <c r="I10" s="4" t="n">
         <v>1774591487670</v>
-      </c>
-      <c r="C10" s="4" t="n">
-        <v>1045881788757</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>176234527312</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>680055449918</v>
       </c>
     </row>
     <row r="11">
@@ -3647,16 +5551,28 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
+        <v>-60063346100</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>131185574067</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-79329822257</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>88624032848</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>-93023120614</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>27356978357</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>136390770666</v>
+      </c>
+      <c r="I11" s="4" t="n">
         <v>-289450397420</v>
-      </c>
-      <c r="C11" s="4" t="n">
-        <v>136390770666</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>27356978357</v>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>-93023120614</v>
       </c>
     </row>
     <row r="12">
@@ -3666,16 +5582,28 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
+        <v>-790234430865</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-879508612026</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>1545958217975</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>-3122839624668</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>-1549588422248</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>-1944517235201</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>-1821393826979</v>
+      </c>
+      <c r="I12" s="4" t="n">
         <v>-1721131354627</v>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>-1821393826979</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>-1944517235201</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>-1549588422248</v>
       </c>
     </row>
     <row r="13">
@@ -3685,16 +5613,28 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
+        <v>-849889822830</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>554572458872</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>65446926710</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>1387811818622</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>36245882912</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>175960973788</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1535573066662</v>
+      </c>
+      <c r="I13" s="4" t="n">
         <v>3488987404115</v>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>1535573066662</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>175960973788</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>36245882912</v>
       </c>
     </row>
     <row r="14">
@@ -3704,16 +5644,28 @@
         </is>
       </c>
       <c r="B14" s="4" t="n">
+        <v>-17223193362</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-68023248333</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>8228059824</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-9225639566</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>-226194254906</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>12732185744</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>4499571232</v>
+      </c>
+      <c r="I14" s="4" t="n">
         <v>1680342037</v>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>4499571232</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>12732185744</v>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>-226194254906</v>
       </c>
     </row>
     <row r="15">
@@ -3723,16 +5675,28 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
+        <v>-90618315335</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-133877354423</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-114531622270</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>-120489823926</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>-218989646740</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>-301416254867</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>-224960303416</v>
+      </c>
+      <c r="I15" s="4" t="n">
         <v>-393209707585</v>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>-224960303416</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>-301416254867</v>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>-218989646740</v>
       </c>
     </row>
     <row r="16">
@@ -3742,16 +5706,28 @@
         </is>
       </c>
       <c r="B16" s="4" t="n">
+        <v>-92733427092</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-82148822013</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-23606280229</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-90641021151</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>-135411036538</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>-111047856</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>-38914311552</v>
+      </c>
+      <c r="I16" s="4" t="n">
         <v>-114141221156</v>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>-38914311552</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>-111047856</v>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>-135411036538</v>
       </c>
     </row>
     <row r="17">
@@ -3772,6 +5748,18 @@
       <c r="E17" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -3780,16 +5768,28 @@
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>0</v>
+        <v>-8350581050</v>
       </c>
       <c r="C18" s="4" t="n">
+        <v>-512175011</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-5761400376</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-2385400000</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>-787133000</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>-3344000000</v>
+      </c>
+      <c r="H18" s="4" t="n">
         <v>-10000000000</v>
       </c>
-      <c r="D18" s="4" t="n">
-        <v>-3344000000</v>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>-787133000</v>
+      <c r="I18" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3799,16 +5799,28 @@
         </is>
       </c>
       <c r="B19" s="4" t="n">
+        <v>-1386736216261</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-108196906152</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>1518332897425</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>-1304108948165</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>-1507692281216</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>-1857103872723</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>627076755370</v>
+      </c>
+      <c r="I19" s="4" t="n">
         <v>2747326553034</v>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>627076755370</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>-1857103872723</v>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>-1507692281216</v>
       </c>
     </row>
     <row r="20">
@@ -3818,16 +5830,28 @@
         </is>
       </c>
       <c r="B20" s="4" t="n">
+        <v>-74372727</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-3815776185</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>-3429075142</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-172331745214</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-518166901951</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>-705276095241</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>-489745872056</v>
+      </c>
+      <c r="I20" s="4" t="n">
         <v>-534361131923</v>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>-489745872056</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>-705276095241</v>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>-518166901951</v>
       </c>
     </row>
     <row r="21">
@@ -3837,16 +5861,28 @@
         </is>
       </c>
       <c r="B21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>239047620</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>38832000</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>22192000</v>
+      </c>
+      <c r="I21" s="4" t="n">
         <v>10150000</v>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>22192000</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>38832000</v>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>239047620</v>
       </c>
     </row>
     <row r="22">
@@ -3856,16 +5892,28 @@
         </is>
       </c>
       <c r="B22" s="4" t="n">
+        <v>-124499109164</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-1321150000000</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>-1549982232750</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>-12892435886578</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>-6940000000000</v>
+      </c>
+      <c r="G22" s="4" t="n">
+        <v>-2551000000000</v>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>-2206000000000</v>
+      </c>
+      <c r="I22" s="4" t="n">
         <v>-9601000000000</v>
-      </c>
-      <c r="C22" s="4" t="n">
-        <v>-2206000000000</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>-2551000000000</v>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>-6940000000000</v>
       </c>
     </row>
     <row r="23">
@@ -3875,16 +5923,28 @@
         </is>
       </c>
       <c r="B23" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>628646866305</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>1098825790697</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>11185094571490</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>9161500000000</v>
+      </c>
+      <c r="G23" s="4" t="n">
+        <v>2516000000000</v>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>2414000000000</v>
+      </c>
+      <c r="I23" s="4" t="n">
         <v>4658000000000</v>
-      </c>
-      <c r="C23" s="4" t="n">
-        <v>2414000000000</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>2516000000000</v>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>9161500000000</v>
       </c>
     </row>
     <row r="24">
@@ -3903,7 +5963,19 @@
         <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
+        <v>-120627928834</v>
+      </c>
+      <c r="F24" s="4" t="n">
         <v>-2461794466</v>
+      </c>
+      <c r="G24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -3924,6 +5996,18 @@
       <c r="E25" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -3932,16 +6016,28 @@
         </is>
       </c>
       <c r="B26" s="4" t="n">
+        <v>19961655437</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>49329885363</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>58323657870</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>143926511675</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>158973736193</v>
+      </c>
+      <c r="G26" s="4" t="n">
+        <v>68561151538</v>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>102089454700</v>
+      </c>
+      <c r="I26" s="4" t="n">
         <v>213448572393</v>
-      </c>
-      <c r="C26" s="4" t="n">
-        <v>102089454700</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>68561151538</v>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>158973736193</v>
       </c>
     </row>
     <row r="27">
@@ -3951,16 +6047,28 @@
         </is>
       </c>
       <c r="B27" s="4" t="n">
+        <v>-104611826454</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>-646989024517</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-396261859325</v>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>-1856374477461</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1860084087396</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>-671676111703</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>-179634225356</v>
+      </c>
+      <c r="I27" s="4" t="n">
         <v>-5263902409530</v>
-      </c>
-      <c r="C27" s="4" t="n">
-        <v>-179634225356</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>-671676111703</v>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>1860084087396</v>
       </c>
     </row>
     <row r="28">
@@ -3970,16 +6078,28 @@
         </is>
       </c>
       <c r="B28" s="4" t="n">
+        <v>25000000000</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>6800000000</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>18232000000</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>10244000000</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>11478000000</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>58267830000</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>51569080000</v>
+      </c>
+      <c r="I28" s="4" t="n">
         <v>2037461548491</v>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>51569080000</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>58267830000</v>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>11478000000</v>
       </c>
     </row>
     <row r="29">
@@ -3992,12 +6112,24 @@
         <v>0</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0</v>
+        <v>-14000000000</v>
       </c>
       <c r="D29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4008,16 +6140,28 @@
         </is>
       </c>
       <c r="B30" s="4" t="n">
+        <v>8665290182642</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>11735834006696</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>10586373171060</v>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>14976648751486</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>13421852950456</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>16941931226074</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>18698414695683</v>
+      </c>
+      <c r="I30" s="4" t="n">
         <v>24716406311275</v>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>18698414695683</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>16941931226074</v>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>13421852950456</v>
       </c>
     </row>
     <row r="31">
@@ -4027,16 +6171,28 @@
         </is>
       </c>
       <c r="B31" s="4" t="n">
+        <v>-6888639840795</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>-10983496917268</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>-11798460513115</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>-11422699256314</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>-14105927868424</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>-14196990842111</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>-18006336778392</v>
+      </c>
+      <c r="I31" s="4" t="n">
         <v>-23465247841524</v>
-      </c>
-      <c r="C31" s="4" t="n">
-        <v>-18006336778392</v>
-      </c>
-      <c r="D31" s="4" t="n">
-        <v>-14196990842111</v>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>-14105927868424</v>
       </c>
     </row>
     <row r="32">
@@ -4057,6 +6213,18 @@
       <c r="E32" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -4068,13 +6236,25 @@
         <v>0</v>
       </c>
       <c r="C33" s="4" t="n">
+        <v>-68680000000</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-78981792000</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>-39490896000</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>-59236267500</v>
+      </c>
+      <c r="H33" s="4" t="n">
         <v>-54283249510</v>
       </c>
-      <c r="D33" s="4" t="n">
-        <v>-59236267500</v>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>-39490896000</v>
+      <c r="I33" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4095,6 +6275,18 @@
       <c r="E34" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
@@ -4103,16 +6295,28 @@
         </is>
       </c>
       <c r="B35" s="4" t="n">
+        <v>1801650341847</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>676457089428</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-1272837134055</v>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>3564193495172</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>-712087813968</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>2743971946463</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>689363747781</v>
+      </c>
+      <c r="I35" s="4" t="n">
         <v>3288620018242</v>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>689363747781</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>2743971946463</v>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>-712087813968</v>
       </c>
     </row>
     <row r="36">
@@ -4122,16 +6326,28 @@
         </is>
       </c>
       <c r="B36" s="4" t="n">
+        <v>310302299132</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>-78728841241</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>-150766095955</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>403710069546</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>-359696007788</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>215191962037</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>1136806277795</v>
+      </c>
+      <c r="I36" s="4" t="n">
         <v>772044161746</v>
-      </c>
-      <c r="C36" s="4" t="n">
-        <v>1136806277795</v>
-      </c>
-      <c r="D36" s="4" t="n">
-        <v>215191962037</v>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>-359696007788</v>
       </c>
     </row>
     <row r="37">
@@ -4141,16 +6357,28 @@
         </is>
       </c>
       <c r="B37" s="4" t="n">
+        <v>638076095694</v>
+      </c>
+      <c r="C37" s="4" t="n">
+        <v>948378394826</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>852194969387</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>701504239398</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1105209549882</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>745556075005</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="I37" s="4" t="n">
         <v>2097787236988</v>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>745556075005</v>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>1105209549882</v>
       </c>
     </row>
     <row r="38">
@@ -4160,16 +6388,28 @@
         </is>
       </c>
       <c r="B38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>75365966</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>-4759062</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>42532911</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>74512931</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>158409220</v>
+      </c>
+      <c r="I38" s="4" t="n">
         <v>20360895</v>
-      </c>
-      <c r="C38" s="4" t="n">
-        <v>158409220</v>
-      </c>
-      <c r="D38" s="4" t="n">
-        <v>74512931</v>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>42532911</v>
       </c>
     </row>
     <row r="39">
@@ -4179,16 +6419,28 @@
         </is>
       </c>
       <c r="B39" s="4" t="n">
+        <v>948378394826</v>
+      </c>
+      <c r="C39" s="4" t="n">
+        <v>869649553585</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>701504239398</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>1105209549882</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>745556075005</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>960822549973</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>2097787236988</v>
+      </c>
+      <c r="I39" s="4" t="n">
         <v>2869851759629</v>
-      </c>
-      <c r="C39" s="4" t="n">
-        <v>2097787236988</v>
-      </c>
-      <c r="D39" s="4" t="n">
-        <v>960822549973</v>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>745556075005</v>
       </c>
     </row>
     <row r="40">
@@ -4209,6 +6461,18 @@
       <c r="E40" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
@@ -4228,6 +6492,18 @@
       <c r="E41" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="F41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
@@ -4245,6 +6521,18 @@
         <v>0</v>
       </c>
       <c r="E42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="4" t="n">
         <v>0</v>
       </c>
     </row>

--- a/financials/FRT/FRT_financials.xlsx
+++ b/financials/FRT/FRT_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -151,7 +151,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -178,10 +178,28 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6547,15 +6565,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="3" customWidth="1" min="6" max="6"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="3" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -6565,59 +6587,151 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="42" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Khối "CHỈ SỐ TÀI CHÍNH" tính bằng công thức từ khối "DỮ LIỆU TRÍCH XUẤT" bên dưới, không phải số nhập tay. Khối "DỮ LIỆU TRÍCH XUẤT" được dò tự động theo TÊN khoản mục (đúng theo tên gốc trong báo cáo) và theo NĂM từ 3 sheet balance_sheet / income_statement — không tham chiếu ô cố định. Có thể sửa nhãn khoản mục ở cột A khối này nếu công ty đổi tên dòng; công thức sẽ tự dò lại. Các năm được xếp tăng dần từ trái sang phải.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>I. CHỈ SỐ TÀI CHÍNH</t>
+        </is>
+      </c>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu</t>
+        </is>
+      </c>
+      <c r="B3" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C3" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D3" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E3" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F3" s="10">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G3" s="10">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H3" s="10">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I3" s="10">
+        <f>'balance_sheet'!I1</f>
+        <v/>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>I. CHỈ SỐ TÀI CHÍNH</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="n"/>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>1. Khả năng sinh lời</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Chỉ tiêu</t>
-        </is>
-      </c>
-      <c r="B5" s="10">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>'balance_sheet'!B1</f>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C5" s="14">
+        <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D5" s="14">
+        <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E5" s="14">
+        <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F5" s="14">
+        <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G5" s="14">
+        <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H5" s="14">
+        <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I5" s="14">
+        <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>1. Khả năng sinh lời</t>
-        </is>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>ROA (LNST / Tổng tài sản bình quân)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C6" s="14">
+        <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="D6" s="14">
+        <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="E6" s="14">
+        <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F6" s="14">
+        <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G6" s="14">
+        <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H6" s="14">
+        <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I6" s="14">
+        <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
+          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -6626,22 +6740,38 @@
         </is>
       </c>
       <c r="C7" s="14">
-        <f>IFERROR(C$54/((C$39+B$39)/2),"n/a")</f>
+        <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>IFERROR(D$54/((D$39+C$39)/2),"n/a")</f>
+        <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>IFERROR(E$54/((E$39+D$39)/2),"n/a")</f>
+        <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F7" s="14">
+        <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G7" s="14">
+        <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H7" s="14">
+        <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I7" s="14">
+        <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>ROA (LNST / Tổng tài sản bình quân)</t>
+          <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
@@ -6650,954 +6780,1568 @@
         </is>
       </c>
       <c r="C8" s="14">
-        <f>IFERROR(C$53/((C$40+B$40)/2),"n/a")</f>
+        <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>IFERROR(D$53/((D$40+C$40)/2),"n/a")</f>
+        <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>IFERROR(E$53/((E$40+D$40)/2),"n/a")</f>
+        <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="F8" s="14">
+        <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="G8" s="14">
+        <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="H8" s="14">
+        <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
+        <v/>
+      </c>
+      <c r="I8" s="14">
+        <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C9" s="14">
-        <f>IFERROR((C$54-B$54)/ABS(B$54),"n/a")</f>
-        <v/>
-      </c>
-      <c r="D9" s="14">
-        <f>IFERROR((D$54-C$54)/ABS(C$54),"n/a")</f>
-        <v/>
-      </c>
-      <c r="E9" s="14">
-        <f>IFERROR((E$54-D$54)/ABS(D$54),"n/a")</f>
-        <v/>
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2. Biên lợi nhuận</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Tăng trưởng Doanh thu thuần</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
+          <t>Biên lợi nhuận gộp</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>IFERROR(B$41/B$39,"n/a")</f>
+        <v/>
       </c>
       <c r="C10" s="14">
-        <f>IFERROR((C$46-B$46)/ABS(B$46),"n/a")</f>
+        <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>IFERROR((D$46-C$46)/ABS(C$46),"n/a")</f>
+        <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>IFERROR((E$46-D$46)/ABS(D$46),"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11"/>
+        <f>IFERROR(E$41/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F10" s="14">
+        <f>IFERROR(F$41/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G10" s="14">
+        <f>IFERROR(G$41/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H10" s="14">
+        <f>IFERROR(H$41/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I10" s="14">
+        <f>IFERROR(I$41/I$39,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng</t>
+        </is>
+      </c>
+      <c r="B11" s="14">
+        <f>IFERROR(B$46/B$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C11" s="14">
+        <f>IFERROR(C$46/C$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D11" s="14">
+        <f>IFERROR(D$46/D$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E11" s="14">
+        <f>IFERROR(E$46/E$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F11" s="14">
+        <f>IFERROR(F$46/F$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G11" s="14">
+        <f>IFERROR(G$46/G$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H11" s="14">
+        <f>IFERROR(H$46/H$39,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I11" s="14">
+        <f>IFERROR(I$46/I$39,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>2. Biên lợi nhuận</t>
+          <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Biên lợi nhuận gộp</t>
-        </is>
-      </c>
-      <c r="B13" s="14">
-        <f>IFERROR(B$48/B$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C13" s="14">
-        <f>IFERROR(C$48/C$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D13" s="14">
-        <f>IFERROR(D$48/D$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E13" s="14">
-        <f>IFERROR(E$48/E$46,"n/a")</f>
+          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+        </is>
+      </c>
+      <c r="B13" s="15">
+        <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C13" s="15">
+        <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D13" s="15">
+        <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E13" s="15">
+        <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G13" s="15">
+        <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H13" s="15">
+        <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I13" s="15">
+        <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng</t>
-        </is>
-      </c>
-      <c r="B14" s="14">
-        <f>IFERROR(B$53/B$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C14" s="14">
-        <f>IFERROR(C$53/C$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
-        <f>IFERROR(D$53/D$46,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E14" s="14">
-        <f>IFERROR(E$53/E$46,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15"/>
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B14" s="15">
+        <f>IFERROR(B$38/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C14" s="15">
+        <f>IFERROR(C$38/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D14" s="15">
+        <f>IFERROR(D$38/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E14" s="15">
+        <f>IFERROR(E$38/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>IFERROR(F$38/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G14" s="15">
+        <f>IFERROR(G$38/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H14" s="15">
+        <f>IFERROR(H$38/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I14" s="15">
+        <f>IFERROR(I$38/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B15" s="15">
+        <f>IFERROR(B$37/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C15" s="15">
+        <f>IFERROR(C$37/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D15" s="15">
+        <f>IFERROR(D$37/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E15" s="15">
+        <f>IFERROR(E$37/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>IFERROR(F$37/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G15" s="15">
+        <f>IFERROR(G$37/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H15" s="15">
+        <f>IFERROR(H$37/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I15" s="15">
+        <f>IFERROR(I$37/I$32,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>3. Đòn bẩy tài chính</t>
-        </is>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Nợ phải trả/Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B16" s="15">
+        <f>IFERROR(B$34/B$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C16" s="15">
+        <f>IFERROR(C$34/C$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D16" s="15">
+        <f>IFERROR(D$34/D$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E16" s="15">
+        <f>IFERROR(E$34/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
+        <f>IFERROR(F$34/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G16" s="15">
+        <f>IFERROR(G$34/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H16" s="15">
+        <f>IFERROR(H$34/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I16" s="15">
+        <f>IFERROR(I$34/I$32,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
       <c r="B17" s="15">
-        <f>IFERROR((B$44+B$45)/B$39,"n/a")</f>
+        <f>IFERROR(B$36/B$32,"n/a")</f>
         <v/>
       </c>
       <c r="C17" s="15">
-        <f>IFERROR((C$44+C$45)/C$39,"n/a")</f>
+        <f>IFERROR(C$36/C$32,"n/a")</f>
         <v/>
       </c>
       <c r="D17" s="15">
-        <f>IFERROR((D$44+D$45)/D$39,"n/a")</f>
+        <f>IFERROR(D$36/D$32,"n/a")</f>
         <v/>
       </c>
       <c r="E17" s="15">
-        <f>IFERROR((E$44+E$45)/E$39,"n/a")</f>
+        <f>IFERROR(E$36/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>IFERROR(F$36/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G17" s="15">
+        <f>IFERROR(G$36/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H17" s="15">
+        <f>IFERROR(H$36/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I17" s="15">
+        <f>IFERROR(I$36/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
+          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
       <c r="B18" s="15">
-        <f>IFERROR(B$45/B$39,"n/a")</f>
+        <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
       <c r="C18" s="15">
-        <f>IFERROR(C$45/C$39,"n/a")</f>
+        <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
       <c r="D18" s="15">
-        <f>IFERROR(D$45/D$39,"n/a")</f>
+        <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
       <c r="E18" s="15">
-        <f>IFERROR(E$45/E$39,"n/a")</f>
+        <f>IFERROR(E$35/E$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F18" s="15">
+        <f>IFERROR(F$35/F$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G18" s="15">
+        <f>IFERROR(G$35/G$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H18" s="15">
+        <f>IFERROR(H$35/H$32,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I18" s="15">
+        <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B19" s="15">
-        <f>IFERROR(B$44/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C19" s="15">
-        <f>IFERROR(C$44/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D19" s="15">
-        <f>IFERROR(D$44/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E19" s="15">
-        <f>IFERROR(E$44/E$39,"n/a")</f>
-        <v/>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>4. Chi phí &amp; khả năng trả lãi</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>Nợ phải trả/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B20" s="15">
-        <f>IFERROR(B$41/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C20" s="15">
-        <f>IFERROR(C$41/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D20" s="15">
-        <f>IFERROR(D$41/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E20" s="15">
-        <f>IFERROR(E$41/E$39,"n/a")</f>
+          <t>Chi phí bán hàng, quản lý/LN gộp</t>
+        </is>
+      </c>
+      <c r="B20" s="14">
+        <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C20" s="14">
+        <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D20" s="14">
+        <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E20" s="14">
+        <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F20" s="14">
+        <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G20" s="14">
+        <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H20" s="14">
+        <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I20" s="14">
+        <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B21" s="15">
-        <f>IFERROR(B$43/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C21" s="15">
-        <f>IFERROR(C$43/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D21" s="15">
-        <f>IFERROR(D$43/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E21" s="15">
-        <f>IFERROR(E$43/E$39,"n/a")</f>
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
+        </is>
+      </c>
+      <c r="B21" s="14">
+        <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D21" s="14">
+        <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E21" s="14">
+        <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F21" s="14">
+        <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G21" s="14">
+        <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H21" s="14">
+        <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I21" s="14">
+        <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
-        </is>
-      </c>
-      <c r="B22" s="15">
-        <f>IFERROR(B$42/B$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C22" s="15">
-        <f>IFERROR(C$42/C$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D22" s="15">
-        <f>IFERROR(D$42/D$39,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E22" s="15">
-        <f>IFERROR(E$42/E$39,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23"/>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>5. Chu kỳ hoạt động vốn lưu động</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Số ngày phải trả (DPO)</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C23" s="16">
+        <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
+        <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E23" s="16">
+        <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G23" s="16">
+        <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H23" s="16">
+        <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I23" s="16">
+        <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>4. Chi phí &amp; khả năng trả lãi</t>
-        </is>
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Số ngày phải thu (DSO)</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C24" s="16">
+        <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G24" s="16">
+        <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I24" s="16">
+        <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>Chi phí bán hàng, quản lý/LN gộp</t>
-        </is>
-      </c>
-      <c r="B25" s="14">
-        <f>IFERROR((ABS(B$49)+ABS(B$50))/B$48,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C25" s="14">
-        <f>IFERROR((ABS(C$49)+ABS(C$50))/C$48,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D25" s="14">
-        <f>IFERROR((ABS(D$49)+ABS(D$50))/D$48,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
-        <f>IFERROR((ABS(E$49)+ABS(E$50))/E$48,"n/a")</f>
+          <t>Số ngày tồn kho (DIO)</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C25" s="16">
+        <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I25" s="16">
+        <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
-        </is>
-      </c>
-      <c r="B26" s="14">
-        <f>IFERROR(ABS(B$52)/B$51,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C26" s="14">
-        <f>IFERROR(ABS(C$52)/C$51,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D26" s="14">
-        <f>IFERROR(ABS(D$52)/D$51,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E26" s="14">
-        <f>IFERROR(ABS(E$52)/E$51,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>6. Cơ cấu tài sản</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Tiền và tương đương tiền/Tài sản</t>
+        </is>
+      </c>
+      <c r="B27" s="14">
+        <f>IFERROR(B$51/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C27" s="14">
+        <f>IFERROR(C$51/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D27" s="14">
+        <f>IFERROR(D$51/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E27" s="14">
+        <f>IFERROR(E$51/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F27" s="14">
+        <f>IFERROR(F$51/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G27" s="14">
+        <f>IFERROR(G$51/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H27" s="14">
+        <f>IFERROR(H$51/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I27" s="14">
+        <f>IFERROR(I$51/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>5. Chu kỳ hoạt động vốn lưu động</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Số ngày phải trả (DPO)</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C29" s="16">
-        <f>IFERROR(((C$56+B$56)/2)/ABS(C$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D29" s="16">
-        <f>IFERROR(((D$56+C$56)/2)/ABS(D$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E29" s="16">
-        <f>IFERROR(((E$56+D$56)/2)/ABS(E$47)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Hàng tồn kho/Tài sản</t>
+        </is>
+      </c>
+      <c r="B28" s="14">
+        <f>IFERROR(B$50/B$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="C28" s="14">
+        <f>IFERROR(C$50/C$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="D28" s="14">
+        <f>IFERROR(D$50/D$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="E28" s="14">
+        <f>IFERROR(E$50/E$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="F28" s="14">
+        <f>IFERROR(F$50/F$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="G28" s="14">
+        <f>IFERROR(G$50/G$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="H28" s="14">
+        <f>IFERROR(H$50/H$33,"n/a")</f>
+        <v/>
+      </c>
+      <c r="I28" s="14">
+        <f>IFERROR(I$50/I$33,"n/a")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Số ngày phải thu (DSO)</t>
-        </is>
-      </c>
-      <c r="B30" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C30" s="16">
-        <f>IFERROR(((C$55+B$55)/2)/C$46*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D30" s="16">
-        <f>IFERROR(((D$55+C$55)/2)/D$46*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E30" s="16">
-        <f>IFERROR(((E$55+D$55)/2)/E$46*365,"n/a")</f>
-        <v/>
-      </c>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="n"/>
+      <c r="C30" s="19" t="n"/>
+      <c r="D30" s="19" t="n"/>
+      <c r="E30" s="19" t="n"/>
+      <c r="F30" s="19" t="n"/>
+      <c r="G30" s="19" t="n"/>
+      <c r="H30" s="19" t="n"/>
+      <c r="I30" s="19" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Số ngày tồn kho (DIO)</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="C31" s="16">
-        <f>IFERROR(((C$57+B$57)/2)/ABS(C$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D31" s="16">
-        <f>IFERROR(((D$57+C$57)/2)/ABS(D$47)*365,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E31" s="16">
-        <f>IFERROR(((E$57+D$57)/2)/ABS(E$47)*365,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32"/>
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Khoản mục</t>
+        </is>
+      </c>
+      <c r="B31" s="10">
+        <f>'balance_sheet'!B1</f>
+        <v/>
+      </c>
+      <c r="C31" s="10">
+        <f>'balance_sheet'!C1</f>
+        <v/>
+      </c>
+      <c r="D31" s="10">
+        <f>'balance_sheet'!D1</f>
+        <v/>
+      </c>
+      <c r="E31" s="10">
+        <f>'balance_sheet'!E1</f>
+        <v/>
+      </c>
+      <c r="F31" s="10">
+        <f>'balance_sheet'!F1</f>
+        <v/>
+      </c>
+      <c r="G31" s="10">
+        <f>'balance_sheet'!G1</f>
+        <v/>
+      </c>
+      <c r="H31" s="10">
+        <f>'balance_sheet'!H1</f>
+        <v/>
+      </c>
+      <c r="I31" s="10">
+        <f>'balance_sheet'!I1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Vốn chủ sở hữu</t>
+        </is>
+      </c>
+      <c r="B32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I32" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>6. Cơ cấu tài sản</t>
-        </is>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TÀI SẢN</t>
+        </is>
+      </c>
+      <c r="B33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền/Tài sản</t>
-        </is>
-      </c>
-      <c r="B34" s="14">
-        <f>IFERROR(B$58/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C34" s="14">
-        <f>IFERROR(C$58/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D34" s="14">
-        <f>IFERROR(D$58/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E34" s="14">
-        <f>IFERROR(E$58/E$40,"n/a")</f>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>NỢ PHẢI TRẢ</t>
+        </is>
+      </c>
+      <c r="B34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I34" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho/Tài sản</t>
-        </is>
-      </c>
-      <c r="B35" s="14">
-        <f>IFERROR(B$57/B$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="C35" s="14">
-        <f>IFERROR(C$57/C$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="D35" s="14">
-        <f>IFERROR(D$57/D$40,"n/a")</f>
-        <v/>
-      </c>
-      <c r="E35" s="14">
-        <f>IFERROR(E$57/E$40,"n/a")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Nợ ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Nợ dài hạn</t>
+        </is>
+      </c>
+      <c r="B36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I36" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Vay ngắn hạn</t>
+        </is>
+      </c>
+      <c r="B37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I37" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Khoản mục</t>
-        </is>
-      </c>
-      <c r="B38" s="10">
-        <f>'balance_sheet'!E1</f>
-        <v/>
-      </c>
-      <c r="C38" s="10">
-        <f>'balance_sheet'!D1</f>
-        <v/>
-      </c>
-      <c r="D38" s="10">
-        <f>'balance_sheet'!C1</f>
-        <v/>
-      </c>
-      <c r="E38" s="10">
-        <f>'balance_sheet'!B1</f>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Vay dài hạn</t>
+        </is>
+      </c>
+      <c r="B38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I38" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Vốn chủ sở hữu</t>
+          <t>Doanh thu thuần</t>
         </is>
       </c>
       <c r="B39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E39" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I39" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>TỔNG CỘNG TÀI SẢN</t>
+          <t>Giá vốn hàng bán</t>
         </is>
       </c>
       <c r="B40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E40" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I40" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NỢ PHẢI TRẢ</t>
+          <t>Lợi nhuận gộp</t>
         </is>
       </c>
       <c r="B41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E41" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I41" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>Nợ ngắn hạn</t>
+          <t>Chi phí bán hàng</t>
         </is>
       </c>
       <c r="B42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E42" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I42" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>Nợ dài hạn</t>
+          <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
       <c r="B43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E43" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I43" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>Vay ngắn hạn</t>
+          <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
       <c r="B44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E44" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I44" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>Vay dài hạn</t>
+          <t>Chi phí lãi vay</t>
         </is>
       </c>
       <c r="B45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E45" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I45" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>Doanh thu thuần</t>
+          <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
       <c r="B46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E46" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I46" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>Giá vốn hàng bán</t>
+          <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
       <c r="B47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E47" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I47" s="17">
+        <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Lợi nhuận gộp</t>
+          <t>Phải thu khách hàng</t>
         </is>
       </c>
       <c r="B48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E48" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I48" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Chi phí bán hàng</t>
+          <t>Phải trả người bán</t>
         </is>
       </c>
       <c r="B49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E49" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>Chi phí quản lý doanh nghiệp</t>
+          <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
       <c r="B50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E50" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
+          <t>Tiền và tương đương tiền</t>
         </is>
       </c>
       <c r="B51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="C51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="D51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
       <c r="E51" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>Chi phí lãi vay</t>
-        </is>
-      </c>
-      <c r="B52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Lãi/(lỗ) thuần sau thuế</t>
-        </is>
-      </c>
-      <c r="B53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
-        </is>
-      </c>
-      <c r="B54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="17">
-        <f>IFERROR(INDEX(income_statement!$B:$E,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$38,income_statement!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>Phải thu khách hàng</t>
-        </is>
-      </c>
-      <c r="B55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>Phải trả người bán</t>
-        </is>
-      </c>
-      <c r="B56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>Hàng tồn kho, ròng</t>
-        </is>
-      </c>
-      <c r="B57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Tiền và tương đương tiền</t>
-        </is>
-      </c>
-      <c r="B58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="C58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$38,balance_sheet!$B$1:$E$1,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E58" s="17">
-        <f>IFERROR(INDEX(balance_sheet!$B:$E,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$38,balance_sheet!$B$1:$E$1,0)),"")</f>
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="17">
+        <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
   </mergeCells>
+  <conditionalFormatting sqref="B5:I5">
+    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B6:I6">
+    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:I7">
+    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:I8">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B10:I10">
+    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B11:I11">
+    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B13:I13">
+    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:I16">
+    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
+      <formula>1</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
+      <formula>0.3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B21:I21">
+    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
+      <formula>0.5</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/financials/FRT/FRT_financials.xlsx
+++ b/financials/FRT/FRT_financials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="income_statement" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="cash_flow" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="chi_so_tai_chinh" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0 &quot;ngày&quot;"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,20 +53,7 @@
     </font>
     <font>
       <name val="Tahoma"/>
-      <i val="1"/>
-      <color rgb="00808080"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Tahoma"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <color theme="1"/>
       <sz val="11"/>
     </font>
     <font>
@@ -151,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -162,44 +149,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00C6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -6588,353 +6554,353 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>I. CHỈ SỐ TÀI CHÍNH</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
+      <c r="B2" s="7" t="n"/>
+      <c r="C2" s="7" t="n"/>
+      <c r="D2" s="7" t="n"/>
+      <c r="E2" s="7" t="n"/>
+      <c r="F2" s="7" t="n"/>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="7" t="n"/>
+      <c r="I2" s="7" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Chỉ tiêu</t>
         </is>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C3" s="10">
+      <c r="C3" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E3" s="10">
+      <c r="E3" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F3" s="10">
+      <c r="F3" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>1. Khả năng sinh lời</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>ROE (LNST CĐ Cty mẹ / VCSH bình quân)</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <f>IFERROR(C$47/((C$32+B$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="13">
         <f>IFERROR(D$47/((D$32+C$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="13">
         <f>IFERROR(E$47/((E$32+D$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <f>IFERROR(F$47/((F$32+E$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <f>IFERROR(G$47/((G$32+F$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <f>IFERROR(H$47/((H$32+G$32)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <f>IFERROR(I$47/((I$32+H$32)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>ROA (LNST / Tổng tài sản bình quân)</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <f>IFERROR(C$46/((C$33+B$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="13">
         <f>IFERROR(D$46/((D$33+C$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <f>IFERROR(E$46/((E$33+D$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <f>IFERROR(F$46/((F$33+E$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <f>IFERROR(G$46/((G$33+F$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <f>IFERROR(H$46/((H$33+G$33)/2),"n/a")</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <f>IFERROR(I$46/((I$33+H$33)/2),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng LN Cổ đông Cty mẹ</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C7" s="14">
+      <c r="C7" s="13">
         <f>IFERROR((C$47-B$47)/ABS(B$47),"n/a")</f>
         <v/>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="13">
         <f>IFERROR((D$47-C$47)/ABS(C$47),"n/a")</f>
         <v/>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="13">
         <f>IFERROR((E$47-D$47)/ABS(D$47),"n/a")</f>
         <v/>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="13">
         <f>IFERROR((F$47-E$47)/ABS(E$47),"n/a")</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <f>IFERROR((G$47-F$47)/ABS(F$47),"n/a")</f>
         <v/>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <f>IFERROR((H$47-G$47)/ABS(G$47),"n/a")</f>
         <v/>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <f>IFERROR((I$47-H$47)/ABS(H$47),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Tăng trưởng Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C8" s="14">
+      <c r="C8" s="13">
         <f>IFERROR((C$39-B$39)/ABS(B$39),"n/a")</f>
         <v/>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="13">
         <f>IFERROR((D$39-C$39)/ABS(C$39),"n/a")</f>
         <v/>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="13">
         <f>IFERROR((E$39-D$39)/ABS(D$39),"n/a")</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="13">
         <f>IFERROR((F$39-E$39)/ABS(E$39),"n/a")</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <f>IFERROR((G$39-F$39)/ABS(F$39),"n/a")</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <f>IFERROR((H$39-G$39)/ABS(G$39),"n/a")</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <f>IFERROR((I$39-H$39)/ABS(H$39),"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>2. Biên lợi nhuận</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <f>IFERROR(B$41/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C10" s="14">
+      <c r="C10" s="13">
         <f>IFERROR(C$41/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="13">
         <f>IFERROR(D$41/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="13">
         <f>IFERROR(E$41/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="13">
         <f>IFERROR(F$41/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <f>IFERROR(G$41/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <f>IFERROR(H$41/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <f>IFERROR(I$41/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>Biên lợi nhuận ròng</t>
         </is>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <f>IFERROR(B$46/B$39,"n/a")</f>
         <v/>
       </c>
-      <c r="C11" s="14">
+      <c r="C11" s="13">
         <f>IFERROR(C$46/C$39,"n/a")</f>
         <v/>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="13">
         <f>IFERROR(D$46/D$39,"n/a")</f>
         <v/>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="13">
         <f>IFERROR(E$46/E$39,"n/a")</f>
         <v/>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="13">
         <f>IFERROR(F$46/F$39,"n/a")</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <f>IFERROR(G$46/G$39,"n/a")</f>
         <v/>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <f>IFERROR(H$46/H$39,"n/a")</f>
         <v/>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <f>IFERROR(I$46/I$39,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>3. Đòn bẩy tài chính</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>D/E (Nợ vay / Vốn chủ sở hữu)</t>
         </is>
       </c>
-      <c r="B13" s="15">
+      <c r="B13" s="14">
         <f>IFERROR((B$37+B$38)/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="14">
         <f>IFERROR((C$37+C$38)/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D13" s="15">
+      <c r="D13" s="14">
         <f>IFERROR((D$37+D$38)/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E13" s="15">
+      <c r="E13" s="14">
         <f>IFERROR((E$37+E$38)/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="14">
         <f>IFERROR((F$37+F$38)/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="14">
         <f>IFERROR((G$37+G$38)/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H13" s="15">
+      <c r="H13" s="14">
         <f>IFERROR((H$37+H$38)/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="14">
         <f>IFERROR((I$37+I$38)/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6945,35 +6911,35 @@
           <t xml:space="preserve">     - Nợ vay dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="14">
         <f>IFERROR(B$38/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="14">
         <f>IFERROR(C$38/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="14">
         <f>IFERROR(D$38/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E14" s="15">
+      <c r="E14" s="14">
         <f>IFERROR(E$38/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="14">
         <f>IFERROR(F$38/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="14">
         <f>IFERROR(G$38/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H14" s="15">
+      <c r="H14" s="14">
         <f>IFERROR(H$38/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="14">
         <f>IFERROR(I$38/I$32,"n/a")</f>
         <v/>
       </c>
@@ -6984,74 +6950,74 @@
           <t xml:space="preserve">     - Nợ vay ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B15" s="15">
+      <c r="B15" s="14">
         <f>IFERROR(B$37/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="14">
         <f>IFERROR(C$37/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="14">
         <f>IFERROR(D$37/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="14">
         <f>IFERROR(E$37/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="14">
         <f>IFERROR(F$37/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G15" s="15">
+      <c r="G15" s="14">
         <f>IFERROR(G$37/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H15" s="15">
+      <c r="H15" s="14">
         <f>IFERROR(H$37/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <f>IFERROR(I$37/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t>Nợ phải trả/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B16" s="15">
+      <c r="B16" s="14">
         <f>IFERROR(B$34/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="14">
         <f>IFERROR(C$34/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="14">
         <f>IFERROR(D$34/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="14">
         <f>IFERROR(E$34/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="14">
         <f>IFERROR(F$34/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="14">
         <f>IFERROR(G$34/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="14">
         <f>IFERROR(H$34/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="14">
         <f>IFERROR(I$34/I$32,"n/a")</f>
         <v/>
       </c>
@@ -7062,35 +7028,35 @@
           <t xml:space="preserve">     - Nợ dài hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="14">
         <f>IFERROR(B$36/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C17" s="15">
+      <c r="C17" s="14">
         <f>IFERROR(C$36/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D17" s="15">
+      <c r="D17" s="14">
         <f>IFERROR(D$36/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="14">
         <f>IFERROR(E$36/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="14">
         <f>IFERROR(F$36/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G17" s="15">
+      <c r="G17" s="14">
         <f>IFERROR(G$36/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="14">
         <f>IFERROR(H$36/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="14">
         <f>IFERROR(I$36/I$32,"n/a")</f>
         <v/>
       </c>
@@ -7101,387 +7067,387 @@
           <t xml:space="preserve">     - Nợ ngắn hạn/Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="14">
         <f>IFERROR(B$35/B$32,"n/a")</f>
         <v/>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="14">
         <f>IFERROR(C$35/C$32,"n/a")</f>
         <v/>
       </c>
-      <c r="D18" s="15">
+      <c r="D18" s="14">
         <f>IFERROR(D$35/D$32,"n/a")</f>
         <v/>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="14">
         <f>IFERROR(E$35/E$32,"n/a")</f>
         <v/>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="14">
         <f>IFERROR(F$35/F$32,"n/a")</f>
         <v/>
       </c>
-      <c r="G18" s="15">
+      <c r="G18" s="14">
         <f>IFERROR(G$35/G$32,"n/a")</f>
         <v/>
       </c>
-      <c r="H18" s="15">
+      <c r="H18" s="14">
         <f>IFERROR(H$35/H$32,"n/a")</f>
         <v/>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="14">
         <f>IFERROR(I$35/I$32,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>4. Chi phí &amp; khả năng trả lãi</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Chi phí bán hàng, quản lý/LN gộp</t>
         </is>
       </c>
-      <c r="B20" s="14">
+      <c r="B20" s="13">
         <f>IFERROR((ABS(B$42)+ABS(B$43))/B$41,"n/a")</f>
         <v/>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13">
         <f>IFERROR((ABS(C$42)+ABS(C$43))/C$41,"n/a")</f>
         <v/>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13">
         <f>IFERROR((ABS(D$42)+ABS(D$43))/D$41,"n/a")</f>
         <v/>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="13">
         <f>IFERROR((ABS(E$42)+ABS(E$43))/E$41,"n/a")</f>
         <v/>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="13">
         <f>IFERROR((ABS(F$42)+ABS(F$43))/F$41,"n/a")</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="13">
         <f>IFERROR((ABS(G$42)+ABS(G$43))/G$41,"n/a")</f>
         <v/>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="13">
         <f>IFERROR((ABS(H$42)+ABS(H$43))/H$41,"n/a")</f>
         <v/>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <f>IFERROR((ABS(I$42)+ABS(I$43))/I$41,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Chi phí lãi vay/LN từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B21" s="14">
+      <c r="B21" s="13">
         <f>IFERROR(ABS(B$45)/B$44,"n/a")</f>
         <v/>
       </c>
-      <c r="C21" s="14">
+      <c r="C21" s="13">
         <f>IFERROR(ABS(C$45)/C$44,"n/a")</f>
         <v/>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="13">
         <f>IFERROR(ABS(D$45)/D$44,"n/a")</f>
         <v/>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="13">
         <f>IFERROR(ABS(E$45)/E$44,"n/a")</f>
         <v/>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="13">
         <f>IFERROR(ABS(F$45)/F$44,"n/a")</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="13">
         <f>IFERROR(ABS(G$45)/G$44,"n/a")</f>
         <v/>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="13">
         <f>IFERROR(ABS(H$45)/H$44,"n/a")</f>
         <v/>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <f>IFERROR(ABS(I$45)/I$44,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>5. Chu kỳ hoạt động vốn lưu động</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải trả (DPO)</t>
         </is>
       </c>
-      <c r="B23" s="13" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C23" s="16">
+      <c r="C23" s="15">
         <f>IFERROR(((C$49+B$49)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="15">
         <f>IFERROR(((D$49+C$49)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="15">
         <f>IFERROR(((E$49+D$49)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F23" s="16">
+      <c r="F23" s="15">
         <f>IFERROR(((F$49+E$49)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="15">
         <f>IFERROR(((G$49+F$49)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="15">
         <f>IFERROR(((H$49+G$49)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="15">
         <f>IFERROR(((I$49+H$49)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>Số ngày phải thu (DSO)</t>
         </is>
       </c>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C24" s="16">
+      <c r="C24" s="15">
         <f>IFERROR(((C$48+B$48)/2)/C$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="15">
         <f>IFERROR(((D$48+C$48)/2)/D$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="15">
         <f>IFERROR(((E$48+D$48)/2)/E$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F24" s="16">
+      <c r="F24" s="15">
         <f>IFERROR(((F$48+E$48)/2)/F$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="15">
         <f>IFERROR(((G$48+F$48)/2)/G$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="15">
         <f>IFERROR(((H$48+G$48)/2)/H$39*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="15">
         <f>IFERROR(((I$48+H$48)/2)/I$39*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>Số ngày tồn kho (DIO)</t>
         </is>
       </c>
-      <c r="B25" s="13" t="inlineStr">
+      <c r="B25" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="C25" s="16">
+      <c r="C25" s="15">
         <f>IFERROR(((C$50+B$50)/2)/ABS(C$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="15">
         <f>IFERROR(((D$50+C$50)/2)/ABS(D$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="15">
         <f>IFERROR(((E$50+D$50)/2)/ABS(E$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="F25" s="16">
+      <c r="F25" s="15">
         <f>IFERROR(((F$50+E$50)/2)/ABS(F$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="15">
         <f>IFERROR(((G$50+F$50)/2)/ABS(G$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="15">
         <f>IFERROR(((H$50+G$50)/2)/ABS(H$40)*365,"n/a")</f>
         <v/>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="15">
         <f>IFERROR(((I$50+H$50)/2)/ABS(I$40)*365,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>6. Cơ cấu tài sản</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>Tiền và tương đương tiền/Tài sản</t>
         </is>
       </c>
-      <c r="B27" s="14">
+      <c r="B27" s="13">
         <f>IFERROR(B$51/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13">
         <f>IFERROR(C$51/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13">
         <f>IFERROR(D$51/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="13">
         <f>IFERROR(E$51/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="13">
         <f>IFERROR(F$51/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="13">
         <f>IFERROR(G$51/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="13">
         <f>IFERROR(H$51/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="13">
         <f>IFERROR(I$51/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>Hàng tồn kho/Tài sản</t>
         </is>
       </c>
-      <c r="B28" s="14">
+      <c r="B28" s="13">
         <f>IFERROR(B$50/B$33,"n/a")</f>
         <v/>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13">
         <f>IFERROR(C$50/C$33,"n/a")</f>
         <v/>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13">
         <f>IFERROR(D$50/D$33,"n/a")</f>
         <v/>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="13">
         <f>IFERROR(E$50/E$33,"n/a")</f>
         <v/>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="13">
         <f>IFERROR(F$50/F$33,"n/a")</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="13">
         <f>IFERROR(G$50/G$33,"n/a")</f>
         <v/>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="13">
         <f>IFERROR(H$50/H$33,"n/a")</f>
         <v/>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="13">
         <f>IFERROR(I$50/I$33,"n/a")</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>II. DỮ LIỆU TRÍCH XUẤT (tự động dò theo tên khoản mục)</t>
         </is>
       </c>
-      <c r="B30" s="19" t="n"/>
-      <c r="C30" s="19" t="n"/>
-      <c r="D30" s="19" t="n"/>
-      <c r="E30" s="19" t="n"/>
-      <c r="F30" s="19" t="n"/>
-      <c r="G30" s="19" t="n"/>
-      <c r="H30" s="19" t="n"/>
-      <c r="I30" s="19" t="n"/>
+      <c r="B30" s="7" t="n"/>
+      <c r="C30" s="7" t="n"/>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
+      <c r="F30" s="7" t="n"/>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="7" t="n"/>
+      <c r="I30" s="7" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>Khoản mục</t>
         </is>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <f>'balance_sheet'!B1</f>
         <v/>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="9">
         <f>'balance_sheet'!C1</f>
         <v/>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="9">
         <f>'balance_sheet'!D1</f>
         <v/>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="9">
         <f>'balance_sheet'!E1</f>
         <v/>
       </c>
-      <c r="F31" s="10">
+      <c r="F31" s="9">
         <f>'balance_sheet'!F1</f>
         <v/>
       </c>
-      <c r="G31" s="10">
+      <c r="G31" s="9">
         <f>'balance_sheet'!G1</f>
         <v/>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="9">
         <f>'balance_sheet'!H1</f>
         <v/>
       </c>
-      <c r="I31" s="10">
+      <c r="I31" s="9">
         <f>'balance_sheet'!I1</f>
         <v/>
       </c>
@@ -7492,35 +7458,35 @@
           <t>Vốn chủ sở hữu</t>
         </is>
       </c>
-      <c r="B32" s="17">
+      <c r="B32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vốn chủ sở hữu",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7531,35 +7497,35 @@
           <t>TỔNG CỘNG TÀI SẢN</t>
         </is>
       </c>
-      <c r="B33" s="17">
+      <c r="B33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("TỔNG CỘNG TÀI SẢN",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7570,35 +7536,35 @@
           <t>NỢ PHẢI TRẢ</t>
         </is>
       </c>
-      <c r="B34" s="17">
+      <c r="B34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I34" s="17">
+      <c r="I34" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("NỢ PHẢI TRẢ",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7609,35 +7575,35 @@
           <t>Nợ ngắn hạn</t>
         </is>
       </c>
-      <c r="B35" s="17">
+      <c r="B35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7648,35 +7614,35 @@
           <t>Nợ dài hạn</t>
         </is>
       </c>
-      <c r="B36" s="17">
+      <c r="B36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I36" s="17">
+      <c r="I36" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Nợ dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7687,35 +7653,35 @@
           <t>Vay ngắn hạn</t>
         </is>
       </c>
-      <c r="B37" s="17">
+      <c r="B37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I37" s="17">
+      <c r="I37" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay ngắn hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7726,35 +7692,35 @@
           <t>Vay dài hạn</t>
         </is>
       </c>
-      <c r="B38" s="17">
+      <c r="B38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C38" s="17">
+      <c r="C38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D38" s="17">
+      <c r="D38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E38" s="17">
+      <c r="E38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F38" s="17">
+      <c r="F38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G38" s="17">
+      <c r="G38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H38" s="17">
+      <c r="H38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I38" s="17">
+      <c r="I38" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Vay dài hạn",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7765,35 +7731,35 @@
           <t>Doanh thu thuần</t>
         </is>
       </c>
-      <c r="B39" s="17">
+      <c r="B39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C39" s="17">
+      <c r="C39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D39" s="17">
+      <c r="D39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E39" s="17">
+      <c r="E39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F39" s="17">
+      <c r="F39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G39" s="17">
+      <c r="G39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H39" s="17">
+      <c r="H39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I39" s="17">
+      <c r="I39" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Doanh thu thuần",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7804,35 +7770,35 @@
           <t>Giá vốn hàng bán</t>
         </is>
       </c>
-      <c r="B40" s="17">
+      <c r="B40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C40" s="17">
+      <c r="C40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D40" s="17">
+      <c r="D40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E40" s="17">
+      <c r="E40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F40" s="17">
+      <c r="F40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G40" s="17">
+      <c r="G40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H40" s="17">
+      <c r="H40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I40" s="17">
+      <c r="I40" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Giá vốn hàng bán",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7843,35 +7809,35 @@
           <t>Lợi nhuận gộp</t>
         </is>
       </c>
-      <c r="B41" s="17">
+      <c r="B41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C41" s="17">
+      <c r="C41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D41" s="17">
+      <c r="D41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E41" s="17">
+      <c r="E41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F41" s="17">
+      <c r="F41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G41" s="17">
+      <c r="G41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H41" s="17">
+      <c r="H41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I41" s="17">
+      <c r="I41" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận gộp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7882,35 +7848,35 @@
           <t>Chi phí bán hàng</t>
         </is>
       </c>
-      <c r="B42" s="17">
+      <c r="B42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C42" s="17">
+      <c r="C42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D42" s="17">
+      <c r="D42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E42" s="17">
+      <c r="E42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F42" s="17">
+      <c r="F42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G42" s="17">
+      <c r="G42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H42" s="17">
+      <c r="H42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I42" s="17">
+      <c r="I42" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí bán hàng",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7921,35 +7887,35 @@
           <t>Chi phí quản lý doanh nghiệp</t>
         </is>
       </c>
-      <c r="B43" s="17">
+      <c r="B43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C43" s="17">
+      <c r="C43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D43" s="17">
+      <c r="D43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E43" s="17">
+      <c r="E43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F43" s="17">
+      <c r="F43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G43" s="17">
+      <c r="G43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H43" s="17">
+      <c r="H43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I43" s="17">
+      <c r="I43" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí quản lý doanh nghiệp",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7960,35 +7926,35 @@
           <t>Lãi/(lỗ) từ hoạt động kinh doanh</t>
         </is>
       </c>
-      <c r="B44" s="17">
+      <c r="B44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D44" s="17">
+      <c r="D44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E44" s="17">
+      <c r="E44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F44" s="17">
+      <c r="F44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G44" s="17">
+      <c r="G44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H44" s="17">
+      <c r="H44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I44" s="17">
+      <c r="I44" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) từ hoạt động kinh doanh",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -7999,35 +7965,35 @@
           <t>Chi phí lãi vay</t>
         </is>
       </c>
-      <c r="B45" s="17">
+      <c r="B45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C45" s="17">
+      <c r="C45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D45" s="17">
+      <c r="D45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E45" s="17">
+      <c r="E45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F45" s="17">
+      <c r="F45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G45" s="17">
+      <c r="G45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H45" s="17">
+      <c r="H45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I45" s="17">
+      <c r="I45" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Chi phí lãi vay",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8038,35 +8004,35 @@
           <t>Lãi/(lỗ) thuần sau thuế</t>
         </is>
       </c>
-      <c r="B46" s="17">
+      <c r="B46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H46" s="17">
+      <c r="H46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I46" s="17">
+      <c r="I46" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lãi/(lỗ) thuần sau thuế",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8077,35 +8043,35 @@
           <t>Lợi nhuận của Cổ đông của Công ty mẹ</t>
         </is>
       </c>
-      <c r="B47" s="17">
+      <c r="B47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(B$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C47" s="17">
+      <c r="C47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(C$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D47" s="17">
+      <c r="D47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(D$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E47" s="17">
+      <c r="E47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(E$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F47" s="17">
+      <c r="F47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(F$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G47" s="17">
+      <c r="G47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(G$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H47" s="17">
+      <c r="H47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(H$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I47" s="17">
+      <c r="I47" s="16">
         <f>IFERROR(INDEX(income_statement!$B:$I,MATCH("Lợi nhuận của Cổ đông của Công ty mẹ",income_statement!$A:$A,0),MATCH(I$31,income_statement!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8116,35 +8082,35 @@
           <t>Phải thu khách hàng</t>
         </is>
       </c>
-      <c r="B48" s="17">
+      <c r="B48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C48" s="17">
+      <c r="C48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D48" s="17">
+      <c r="D48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E48" s="17">
+      <c r="E48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F48" s="17">
+      <c r="F48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G48" s="17">
+      <c r="G48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H48" s="17">
+      <c r="H48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I48" s="17">
+      <c r="I48" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải thu khách hàng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8155,35 +8121,35 @@
           <t>Phải trả người bán</t>
         </is>
       </c>
-      <c r="B49" s="17">
+      <c r="B49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C49" s="17">
+      <c r="C49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D49" s="17">
+      <c r="D49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E49" s="17">
+      <c r="E49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F49" s="17">
+      <c r="F49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G49" s="17">
+      <c r="G49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H49" s="17">
+      <c r="H49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="17">
+      <c r="I49" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Phải trả người bán",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8194,35 +8160,35 @@
           <t>Hàng tồn kho, ròng</t>
         </is>
       </c>
-      <c r="B50" s="17">
+      <c r="B50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D50" s="17">
+      <c r="D50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E50" s="17">
+      <c r="E50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F50" s="17">
+      <c r="F50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G50" s="17">
+      <c r="G50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H50" s="17">
+      <c r="H50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I50" s="17">
+      <c r="I50" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Hàng tồn kho, ròng",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8233,35 +8199,35 @@
           <t>Tiền và tương đương tiền</t>
         </is>
       </c>
-      <c r="B51" s="17">
+      <c r="B51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(B$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="C51" s="17">
+      <c r="C51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(C$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="D51" s="17">
+      <c r="D51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(D$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="E51" s="17">
+      <c r="E51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(E$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="F51" s="17">
+      <c r="F51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(F$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="G51" s="17">
+      <c r="G51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(G$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="H51" s="17">
+      <c r="H51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(H$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
-      <c r="I51" s="17">
+      <c r="I51" s="16">
         <f>IFERROR(INDEX(balance_sheet!$B:$I,MATCH("Tiền và tương đương tiền",balance_sheet!$A:$A,0),MATCH(I$31,balance_sheet!$B$1:$I$1,0)),"")</f>
         <v/>
       </c>
@@ -8270,78 +8236,6 @@
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:I5">
-    <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B6:I6">
-    <cfRule type="cellIs" priority="3" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:I7">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="6" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B8:I8">
-    <cfRule type="cellIs" priority="7" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="8" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B10:I10">
-    <cfRule type="cellIs" priority="9" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="10" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B11:I11">
-    <cfRule type="cellIs" priority="11" operator="greaterThan" dxfId="0">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="12" operator="lessThan" dxfId="1">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B13:I13">
-    <cfRule type="cellIs" priority="13" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="14" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B16:I16">
-    <cfRule type="cellIs" priority="15" operator="greaterThan" dxfId="1">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="16" operator="lessThan" dxfId="0">
-      <formula>0.3</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B21:I21">
-    <cfRule type="cellIs" priority="17" operator="greaterThan" dxfId="1">
-      <formula>0.5</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="18" operator="lessThan" dxfId="0">
-      <formula>0.15</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>